--- a/Översikt UPPVIDINGE.xlsx
+++ b/Översikt UPPVIDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45174</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>44972</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>44972</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45442</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45789</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>46119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>46183</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>44980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>46183</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>44607</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45789</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>46119</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>46149</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>46119</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>45995</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44859</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>46066</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>46276</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>46183</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>45366</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>45313</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44972</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>45158</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>46066</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>44939</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>45604</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>45195</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>46247</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>45450</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>45840</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>44979</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>44833</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>45517</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45404</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>45604</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>44937</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>45688</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>45205</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>45103</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>45320</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>45604</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>46169</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>46051</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>45117</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>45568</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>46205</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>46218</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>44972</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44972</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>44484</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>45789</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>44734</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>44827</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>44690</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>44788</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>45623</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         <v>44858</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>44984</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>44663</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>45982</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>44757</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>45939</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>44676</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>44550</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>45981</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>46154</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>45320</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>44858</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>46051</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>45105</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>45435</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>46185</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>46162</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>45897</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>46100</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>44950</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>46247</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>46247</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>46247</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         <v>46255</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>44998</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>45517</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>45688</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>45534</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>45820</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>45825</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>45826</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>45840</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>45440</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>44972</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>45810</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>44865</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>44887</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>44887</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>44524</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>44483</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>44613</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>44487</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>44536</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>44552</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>44574</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>44510</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>44461</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>44812</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>44859</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>44574</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>44859</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>44676</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>44859</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>44859</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>44749</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44574</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>44602</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12881,7 +12881,7 @@
         <v>44580</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>44602</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
         <v>44859</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>44795</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>44757</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>44887</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>44588</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>44845</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>44552</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>44483</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>44483</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13699,7 +13699,7 @@
         <v>44475</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13772,7 +13772,7 @@
         <v>44503</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>44510</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>44803</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>44887</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>44610</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>44609</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>44795</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>44795</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>44582</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>44601</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>44858</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>44711</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>44522</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14721,7 +14721,7 @@
         <v>44837</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>44859</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>44607</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>44607</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>44490</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         <v>44887</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>44887</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
         <v>44676</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>44475</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>44574</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>44466</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15529,7 +15529,7 @@
         <v>44603</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>44602</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44524</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>44721</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>44683</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>44686</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>44459</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>44729</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>44705</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>44602</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>44592</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>45736</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16410,7 +16410,7 @@
         <v>44922</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16483,7 +16483,7 @@
         <v>45229</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16556,7 +16556,7 @@
         <v>45389</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>45338</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>45338</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16785,7 +16785,7 @@
         <v>45338</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>45338</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16941,7 +16941,7 @@
         <v>45156</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17014,7 +17014,7 @@
         <v>45089</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>44610</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17160,7 +17160,7 @@
         <v>45098</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>45770</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17306,7 +17306,7 @@
         <v>44524</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17379,7 +17379,7 @@
         <v>45181</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17452,7 +17452,7 @@
         <v>45385</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>44789</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>45674</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>45697</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>45398</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
         <v>45384</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
         <v>45389</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17973,7 +17973,7 @@
         <v>45338</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>45118</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18124,7 +18124,7 @@
         <v>45428</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18197,7 +18197,7 @@
         <v>45590</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>45428</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>45664</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>45668</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18489,7 +18489,7 @@
         <v>45320</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>45471</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>45348</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>45714</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>44942</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18854,7 +18854,7 @@
         <v>45408</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
         <v>45544</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>45226</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>45229</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>45745</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>44757</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
         <v>45223</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>45233</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19443,7 +19443,7 @@
         <v>44524</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>44985</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>45273</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>45245</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>45153</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>44566</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>44459</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>45278</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>45041</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>45041</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>44924</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20251,7 +20251,7 @@
         <v>45348</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>45622</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>45440</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20470,7 +20470,7 @@
         <v>45469</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>45174</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>44924</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>44984</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>45082</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>45757</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20913,7 +20913,7 @@
         <v>45459</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>45428</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21059,7 +21059,7 @@
         <v>45369</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21132,7 +21132,7 @@
         <v>45085</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
         <v>45230</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>44945</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>45636</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>44734</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>44734</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>45583</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>45336</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>44942</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44942</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>45107</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>45770</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         <v>45688</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22091,7 +22091,7 @@
         <v>45547</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44951</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>45547</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>45230</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45093</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>44917</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>45973</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>45428</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         <v>45428</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>45428</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>45716</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>45887</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>44497</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>45734</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>45804</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>45877</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>44470</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>44984</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>45279</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>45349</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>45749</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23634,7 +23634,7 @@
         <v>45666</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         <v>44638</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>44865</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>44902</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>44603</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>44503</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>45637</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45204</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>45897</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>44552</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>45389</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>44757</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>45028</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>45229</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>45688</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>45552</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>44994</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>46010</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24958,7 +24958,7 @@
         <v>45232</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>45915</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>45112</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>45685</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         <v>45208</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>45642</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>45459</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>45894</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>45338</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>45338</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>45428</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>45923</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>45597</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>45901</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45901</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>45873</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>44711</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>45428</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45840</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>45567</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>45749</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>45338</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>45801</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         <v>45842</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>45838</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>45910</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>46133</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>46009</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>45910</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27110,7 +27110,7 @@
         <v>45910</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45910</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>45729</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>44659</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>45013</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>44971</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>44971</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>44533</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>45455</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>45091</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27850,7 +27850,7 @@
         <v>45923</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27923,7 +27923,7 @@
         <v>45923</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27996,7 +27996,7 @@
         <v>44881</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28069,7 +28069,7 @@
         <v>45229</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>45764</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>45225</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28293,7 +28293,7 @@
         <v>45317</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28371,7 +28371,7 @@
         <v>45041</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>45933</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28517,7 +28517,7 @@
         <v>45146</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>45357</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>45716</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>45716</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28819,7 +28819,7 @@
         <v>45934</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>45934</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>45934</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>45341</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>45233</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29189,7 +29189,7 @@
         <v>45940</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29262,7 +29262,7 @@
         <v>46139</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>45118</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29408,7 +29408,7 @@
         <v>45149</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29481,7 +29481,7 @@
         <v>45169</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>45720</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29627,7 +29627,7 @@
         <v>46149</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>45273</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29773,7 +29773,7 @@
         <v>45273</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>45945</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44887</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>45085</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>44882</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30138,7 +30138,7 @@
         <v>45407</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>45154</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>45530</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>45012</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>45642</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>45324</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>44946</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45957</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45085</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>45369</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>46153</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>46153</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31014,7 +31014,7 @@
         <v>44599</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31087,7 +31087,7 @@
         <v>45960</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31165,7 +31165,7 @@
         <v>44757</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>44757</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31321,7 +31321,7 @@
         <v>45960</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>45001</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>45264</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31545,7 +31545,7 @@
         <v>45561</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>45604</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>45604</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>45764</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31847,7 +31847,7 @@
         <v>45747</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>45968</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>45190</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32066,7 +32066,7 @@
         <v>45427</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32139,7 +32139,7 @@
         <v>45146</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>44524</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>45972</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32358,7 +32358,7 @@
         <v>45973</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>45428</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>45009</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32577,7 +32577,7 @@
         <v>45275</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>45981</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32728,7 +32728,7 @@
         <v>45708</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>45981</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         <v>45981</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32957,7 +32957,7 @@
         <v>44697</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>44897</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>45607</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33181,7 +33181,7 @@
         <v>45985</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>45985</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>45985</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>46156</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33478,7 +33478,7 @@
         <v>46156</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33556,7 +33556,7 @@
         <v>46156</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33634,7 +33634,7 @@
         <v>46156</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>44915</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         <v>44790</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33863,7 +33863,7 @@
         <v>46156</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33941,7 +33941,7 @@
         <v>45941</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34019,7 +34019,7 @@
         <v>45677</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34092,7 +34092,7 @@
         <v>45989</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34165,7 +34165,7 @@
         <v>45941</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34243,7 +34243,7 @@
         <v>45454</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34316,7 +34316,7 @@
         <v>45590</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34389,7 +34389,7 @@
         <v>45989</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>45988</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>45057</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34608,7 +34608,7 @@
         <v>45973</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34681,7 +34681,7 @@
         <v>45610</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34754,7 +34754,7 @@
         <v>45960</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34832,7 +34832,7 @@
         <v>45404</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>45165</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>45336</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35051,7 +35051,7 @@
         <v>45722</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>46162</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35197,7 +35197,7 @@
         <v>45568</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35275,7 +35275,7 @@
         <v>45391</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>46163</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35426,7 +35426,7 @@
         <v>45475</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35499,7 +35499,7 @@
         <v>45960</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35577,7 +35577,7 @@
         <v>45995</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35650,7 +35650,7 @@
         <v>45639</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>46162</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35796,7 +35796,7 @@
         <v>46163</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35874,7 +35874,7 @@
         <v>45995</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35947,7 +35947,7 @@
         <v>45995</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>45688</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36098,7 +36098,7 @@
         <v>45995</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36176,7 +36176,7 @@
         <v>45999</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36249,7 +36249,7 @@
         <v>44523</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>46000</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36395,7 +36395,7 @@
         <v>45279</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>46000</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36541,7 +36541,7 @@
         <v>46167</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36619,7 +36619,7 @@
         <v>45069</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36692,7 +36692,7 @@
         <v>46002</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36770,7 +36770,7 @@
         <v>45440</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>46002</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36921,7 +36921,7 @@
         <v>46007</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36994,7 +36994,7 @@
         <v>45181</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>45389</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>45190</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37213,7 +37213,7 @@
         <v>45575</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37286,7 +37286,7 @@
         <v>46013</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37359,7 +37359,7 @@
         <v>46013</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>44468</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37505,7 +37505,7 @@
         <v>46169</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37578,7 +37578,7 @@
         <v>45098</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>46106</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>46106</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>45019</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37880,7 +37880,7 @@
         <v>46027</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>46029</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38026,7 +38026,7 @@
         <v>45140</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>46029</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38172,7 +38172,7 @@
         <v>45769</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>46174</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38323,7 +38323,7 @@
         <v>46034</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38396,7 +38396,7 @@
         <v>46174</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38474,7 +38474,7 @@
         <v>46033</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38547,7 +38547,7 @@
         <v>44496</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38620,7 +38620,7 @@
         <v>45155</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38693,7 +38693,7 @@
         <v>46174</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38771,7 +38771,7 @@
         <v>46174</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>46174</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>46040</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39000,7 +39000,7 @@
         <v>45350</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39073,7 +39073,7 @@
         <v>45348</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39146,7 +39146,7 @@
         <v>46174</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39224,7 +39224,7 @@
         <v>45434</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39297,7 +39297,7 @@
         <v>44552</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39370,7 +39370,7 @@
         <v>45629</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>44971</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39521,7 +39521,7 @@
         <v>46041</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>44757</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>46048</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>46048</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>45049</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>46050</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39969,7 +39969,7 @@
         <v>45140</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40042,7 +40042,7 @@
         <v>46050</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40120,7 +40120,7 @@
         <v>45308</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40193,7 +40193,7 @@
         <v>46052</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40271,7 +40271,7 @@
         <v>46132</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40344,7 +40344,7 @@
         <v>46052</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40422,7 +40422,7 @@
         <v>46052</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40500,7 +40500,7 @@
         <v>46177</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40578,7 +40578,7 @@
         <v>46176</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>46052</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         <v>46177</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>46177</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40885,7 +40885,7 @@
         <v>46177</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>46177</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41041,7 +41041,7 @@
         <v>46176</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41114,7 +41114,7 @@
         <v>46052</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41192,7 +41192,7 @@
         <v>46052</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>46052</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41343,7 +41343,7 @@
         <v>45093</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41416,7 +41416,7 @@
         <v>45595</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41489,7 +41489,7 @@
         <v>45174</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41562,7 +41562,7 @@
         <v>46177</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>46057</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
         <v>46177</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>46058</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41864,7 +41864,7 @@
         <v>46058</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41942,7 +41942,7 @@
         <v>45547</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42015,7 +42015,7 @@
         <v>45547</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42088,7 +42088,7 @@
         <v>46177</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42166,7 +42166,7 @@
         <v>46062</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>45355</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42312,7 +42312,7 @@
         <v>46069</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>46058</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42468,7 +42468,7 @@
         <v>46071</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42541,7 +42541,7 @@
         <v>45615</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42614,7 +42614,7 @@
         <v>46071</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42687,7 +42687,7 @@
         <v>45085</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>46071</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         <v>46181</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42906,7 +42906,7 @@
         <v>46071</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42979,7 +42979,7 @@
         <v>46181</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43052,7 +43052,7 @@
         <v>46181</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43125,7 +43125,7 @@
         <v>46071</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43198,7 +43198,7 @@
         <v>45113</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43271,7 +43271,7 @@
         <v>45351</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>45642</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43422,7 +43422,7 @@
         <v>45706</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43495,7 +43495,7 @@
         <v>46183</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43568,7 +43568,7 @@
         <v>45224</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43646,7 +43646,7 @@
         <v>45211</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43719,7 +43719,7 @@
         <v>45154</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43792,7 +43792,7 @@
         <v>46185</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43865,7 +43865,7 @@
         <v>46086</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45162</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44011,7 +44011,7 @@
         <v>45547</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44084,7 +44084,7 @@
         <v>45164</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44157,7 +44157,7 @@
         <v>45596</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44230,7 +44230,7 @@
         <v>46185</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44308,7 +44308,7 @@
         <v>45615</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44381,7 +44381,7 @@
         <v>46185</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44454,7 +44454,7 @@
         <v>46185</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45375</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44600,7 +44600,7 @@
         <v>45454</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44673,7 +44673,7 @@
         <v>46093</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>46093</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44829,7 +44829,7 @@
         <v>46093</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44907,7 +44907,7 @@
         <v>44858</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44980,7 +44980,7 @@
         <v>45404</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45053,7 +45053,7 @@
         <v>46093</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45131,7 +45131,7 @@
         <v>46093</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>46093</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45287,7 +45287,7 @@
         <v>46093</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>46191</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45438,7 +45438,7 @@
         <v>46027</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45511,7 +45511,7 @@
         <v>46191</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45584,7 +45584,7 @@
         <v>45476</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45657,7 +45657,7 @@
         <v>46196</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>46195</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45808,7 +45808,7 @@
         <v>46101</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45886,7 +45886,7 @@
         <v>46101</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45964,7 +45964,7 @@
         <v>46101</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46042,7 +46042,7 @@
         <v>46106</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46120,7 +46120,7 @@
         <v>46106</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46198,7 +46198,7 @@
         <v>46106</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46276,7 +46276,7 @@
         <v>46106</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>46106</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46432,7 +46432,7 @@
         <v>44592</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46505,7 +46505,7 @@
         <v>45546</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46578,7 +46578,7 @@
         <v>45082</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46651,7 +46651,7 @@
         <v>45604</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>45604</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>45604</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46885,7 +46885,7 @@
         <v>44838</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46958,7 +46958,7 @@
         <v>45204</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47031,7 +47031,7 @@
         <v>45692</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47104,7 +47104,7 @@
         <v>45568</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>46242</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>46242</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>45091</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47406,7 +47406,7 @@
         <v>45118</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47479,7 +47479,7 @@
         <v>45005</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
         <v>46114</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47630,7 +47630,7 @@
         <v>46114</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>45705</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>46114</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47859,7 +47859,7 @@
         <v>44994</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
         <v>46114</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48010,7 +48010,7 @@
         <v>46114</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48088,7 +48088,7 @@
         <v>46114</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48166,7 +48166,7 @@
         <v>46199</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>45597</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48317,7 +48317,7 @@
         <v>45370</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48390,7 +48390,7 @@
         <v>46242</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48463,7 +48463,7 @@
         <v>45434</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         <v>46122</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48609,7 +48609,7 @@
         <v>45770</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48682,7 +48682,7 @@
         <v>45223</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48755,7 +48755,7 @@
         <v>45372</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48828,7 +48828,7 @@
         <v>45547</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48901,7 +48901,7 @@
         <v>45201</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48974,7 +48974,7 @@
         <v>45184</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49047,7 +49047,7 @@
         <v>46203</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49125,7 +49125,7 @@
         <v>46203</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49203,7 +49203,7 @@
         <v>46203</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49281,7 +49281,7 @@
         <v>46203</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49359,7 +49359,7 @@
         <v>46203</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49437,7 +49437,7 @@
         <v>46203</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49515,7 +49515,7 @@
         <v>45211</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>46132</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49661,7 +49661,7 @@
         <v>44923</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49734,7 +49734,7 @@
         <v>46203</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49812,7 +49812,7 @@
         <v>45103</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49885,7 +49885,7 @@
         <v>46132</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49958,7 +49958,7 @@
         <v>46205</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50036,7 +50036,7 @@
         <v>46205</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50114,7 +50114,7 @@
         <v>46203</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50192,7 +50192,7 @@
         <v>46203</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50270,7 +50270,7 @@
         <v>46203</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50348,7 +50348,7 @@
         <v>46205</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>45338</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50504,7 +50504,7 @@
         <v>46203</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50582,7 +50582,7 @@
         <v>46203</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50660,7 +50660,7 @@
         <v>46203</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50738,7 +50738,7 @@
         <v>44844</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50811,7 +50811,7 @@
         <v>46135</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50884,7 +50884,7 @@
         <v>45590</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50957,7 +50957,7 @@
         <v>45219</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51030,7 +51030,7 @@
         <v>46205</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51108,7 +51108,7 @@
         <v>46205</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51186,7 +51186,7 @@
         <v>45824</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51259,7 +51259,7 @@
         <v>45218</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51332,7 +51332,7 @@
         <v>46205</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51410,7 +51410,7 @@
         <v>45028</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51488,7 +51488,7 @@
         <v>45474</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51561,7 +51561,7 @@
         <v>45288</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>45105</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45842</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51785,7 +51785,7 @@
         <v>46139</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51858,7 +51858,7 @@
         <v>45386</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51936,7 +51936,7 @@
         <v>45688</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52014,7 +52014,7 @@
         <v>45544</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52087,7 +52087,7 @@
         <v>45747</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52165,7 +52165,7 @@
         <v>45155</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52238,7 +52238,7 @@
         <v>46203</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52316,7 +52316,7 @@
         <v>46203</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52394,7 +52394,7 @@
         <v>46203</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52472,7 +52472,7 @@
         <v>46203</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52550,7 +52550,7 @@
         <v>45749</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52628,7 +52628,7 @@
         <v>46206</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52701,7 +52701,7 @@
         <v>46206</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52774,7 +52774,7 @@
         <v>45354</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52847,7 +52847,7 @@
         <v>45243</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52920,7 +52920,7 @@
         <v>45597</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52998,7 +52998,7 @@
         <v>44844</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53071,7 +53071,7 @@
         <v>46206</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53144,7 +53144,7 @@
         <v>44908</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53222,7 +53222,7 @@
         <v>45372</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53295,7 +53295,7 @@
         <v>46206</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53368,7 +53368,7 @@
         <v>45196</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53441,7 +53441,7 @@
         <v>44833</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53519,7 +53519,7 @@
         <v>45244</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53592,7 +53592,7 @@
         <v>46253</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53665,7 +53665,7 @@
         <v>46253</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53738,7 +53738,7 @@
         <v>46210</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53811,7 +53811,7 @@
         <v>45063</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53884,7 +53884,7 @@
         <v>45245</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53957,7 +53957,7 @@
         <v>45692</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54030,7 +54030,7 @@
         <v>46253</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54103,7 +54103,7 @@
         <v>46209</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54176,7 +54176,7 @@
         <v>46253</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54249,7 +54249,7 @@
         <v>45260</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54322,7 +54322,7 @@
         <v>44592</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54395,7 +54395,7 @@
         <v>44593</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54468,7 +54468,7 @@
         <v>45230</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54546,7 +54546,7 @@
         <v>45075</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54619,7 +54619,7 @@
         <v>44939</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54692,7 +54692,7 @@
         <v>45692</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54765,7 +54765,7 @@
         <v>45702</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54838,7 +54838,7 @@
         <v>45338</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54916,7 +54916,7 @@
         <v>44937</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54989,7 +54989,7 @@
         <v>44937</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55062,7 +55062,7 @@
         <v>45195</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55135,7 +55135,7 @@
         <v>45146</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55208,7 +55208,7 @@
         <v>45146</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55281,7 +55281,7 @@
         <v>46260</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55354,7 +55354,7 @@
         <v>45460</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55427,7 +55427,7 @@
         <v>46260</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55500,7 +55500,7 @@
         <v>46260</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55573,7 +55573,7 @@
         <v>45561</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55646,7 +55646,7 @@
         <v>46218</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55719,7 +55719,7 @@
         <v>45764</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55797,7 +55797,7 @@
         <v>44593</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55870,7 +55870,7 @@
         <v>45181</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55948,7 +55948,7 @@
         <v>46218</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56021,7 +56021,7 @@
         <v>46260</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56094,7 +56094,7 @@
         <v>45279</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56167,7 +56167,7 @@
         <v>45153</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56240,7 +56240,7 @@
         <v>45244</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56313,7 +56313,7 @@
         <v>45154</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56386,7 +56386,7 @@
         <v>46262</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56464,7 +56464,7 @@
         <v>44998</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56557,7 +56557,7 @@
         <v>46220</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56630,7 +56630,7 @@
         <v>46220</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56703,7 +56703,7 @@
         <v>45057</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56776,7 +56776,7 @@
         <v>45427</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56849,7 +56849,7 @@
         <v>46266</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56922,7 +56922,7 @@
         <v>44610</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56995,7 +56995,7 @@
         <v>45649</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57068,7 +57068,7 @@
         <v>44998</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57146,7 +57146,7 @@
         <v>44496</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57219,7 +57219,7 @@
         <v>46226</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57292,7 +57292,7 @@
         <v>45600</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57365,7 +57365,7 @@
         <v>45601</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57438,7 +57438,7 @@
         <v>45273</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57511,7 +57511,7 @@
         <v>45391</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>46247</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57662,7 +57662,7 @@
         <v>45516</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57735,7 +57735,7 @@
         <v>44526</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57813,7 +57813,7 @@
         <v>46274</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         <v>45476</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57959,7 +57959,7 @@
         <v>45502</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58037,7 +58037,7 @@
         <v>45488</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58110,7 +58110,7 @@
         <v>45786</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58183,7 +58183,7 @@
         <v>46237</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58256,7 +58256,7 @@
         <v>45604</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58329,7 +58329,7 @@
         <v>45552</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58402,7 +58402,7 @@
         <v>46237</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58480,7 +58480,7 @@
         <v>45742</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58553,7 +58553,7 @@
         <v>46238</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58626,7 +58626,7 @@
         <v>46237</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58699,7 +58699,7 @@
         <v>46280</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58772,7 +58772,7 @@
         <v>46237</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58850,7 +58850,7 @@
         <v>46237</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58928,7 +58928,7 @@
         <v>46261</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59001,7 +59001,7 @@
         <v>46241</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59074,7 +59074,7 @@
         <v>46241</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59147,7 +59147,7 @@
         <v>46241</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59220,7 +59220,7 @@
         <v>45709</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59298,7 +59298,7 @@
         <v>46240</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59371,7 +59371,7 @@
         <v>45720</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59444,7 +59444,7 @@
         <v>45801</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59517,7 +59517,7 @@
         <v>45801</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59590,7 +59590,7 @@
         <v>45800</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59663,7 +59663,7 @@
         <v>45804</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59736,7 +59736,7 @@
         <v>45805</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59809,7 +59809,7 @@
         <v>45804</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59882,7 +59882,7 @@
         <v>45764</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59960,7 +59960,7 @@
         <v>45764</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60038,7 +60038,7 @@
         <v>45807</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60111,7 +60111,7 @@
         <v>45818</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60184,7 +60184,7 @@
         <v>45777</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60262,7 +60262,7 @@
         <v>45819</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60340,7 +60340,7 @@
         <v>45819</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60413,7 +60413,7 @@
         <v>45644</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60486,7 +60486,7 @@
         <v>45826</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60559,7 +60559,7 @@
         <v>45826</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60632,7 +60632,7 @@
         <v>45826</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60705,7 +60705,7 @@
         <v>45832</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60783,7 +60783,7 @@
         <v>45230</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60861,7 +60861,7 @@
         <v>45295</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60939,7 +60939,7 @@
         <v>45114</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61012,7 +61012,7 @@
         <v>45842</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61085,7 +61085,7 @@
         <v>45865</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61158,7 +61158,7 @@
         <v>45792</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61231,7 +61231,7 @@
         <v>44489</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61309,7 +61309,7 @@
         <v>44726</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61382,7 +61382,7 @@
         <v>44916</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61455,7 +61455,7 @@
         <v>45161</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61533,7 +61533,7 @@
         <v>45476</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61606,7 +61606,7 @@
         <v>44963</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61679,7 +61679,7 @@
         <v>44916</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61752,7 +61752,7 @@
         <v>45140</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61825,7 +61825,7 @@
         <v>44462</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61898,7 +61898,7 @@
         <v>44837</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61971,7 +61971,7 @@
         <v>45161</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62049,7 +62049,7 @@
         <v>44893</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62122,7 +62122,7 @@
         <v>44916</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62195,7 +62195,7 @@
         <v>44726</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62268,7 +62268,7 @@
         <v>45411</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62341,7 +62341,7 @@
         <v>45791</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62414,7 +62414,7 @@
         <v>45910</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62487,7 +62487,7 @@
         <v>46030</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62560,7 +62560,7 @@
         <v>46051</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62633,7 +62633,7 @@
         <v>46275</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62706,7 +62706,7 @@
         <v>46280</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>

--- a/Översikt UPPVIDINGE.xlsx
+++ b/Översikt UPPVIDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45174</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>44972</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>44972</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45442</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45789</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>46119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>46183</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>44980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>46183</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>44607</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45789</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>46119</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>46149</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>46119</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>45995</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44859</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>46066</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>46276</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>46183</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>45313</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>45366</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44972</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>46066</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>45158</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>44939</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>45840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>45604</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>46247</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>45195</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>45450</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>44979</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>46051</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>45604</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45205</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>45103</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
         <v>45568</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>46169</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>45688</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>46205</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>45517</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>45404</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>45117</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>46218</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>44937</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>45320</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>45604</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>44833</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>44972</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44972</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>44484</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>45789</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>44734</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>44827</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>44690</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>44788</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>44950</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         <v>44550</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>45534</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>46051</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>45435</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>45623</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>45939</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>46100</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>45981</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>45820</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>45982</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>45826</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>45825</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>44676</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         <v>46154</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>45840</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>45320</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>44984</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>46185</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>45897</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>44858</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>44998</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>44663</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>46255</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>44757</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>45688</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>46162</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>44858</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>46247</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>46247</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>46247</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>45105</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>45517</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>45440</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>44972</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>45810</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>44865</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>44887</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>44887</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>44524</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>44613</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>44483</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>44487</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>44574</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>44536</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>44510</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>44812</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>44552</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>44859</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>44574</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>44859</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>44676</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>44859</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>44859</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>44749</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>44574</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44602</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>44580</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12881,7 +12881,7 @@
         <v>44602</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>44859</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
         <v>44795</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>44757</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>44887</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>44588</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>44845</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>44552</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>44483</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>44483</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>44475</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13699,7 +13699,7 @@
         <v>44503</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13772,7 +13772,7 @@
         <v>44510</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>44803</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>44887</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>44610</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>44609</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>44795</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>44795</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>44582</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>44601</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>44858</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>44711</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>44522</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>44837</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14721,7 +14721,7 @@
         <v>44859</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>44607</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>44607</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>44887</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>44490</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         <v>44887</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>44676</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
         <v>44475</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>44574</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>44466</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>44603</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15529,7 +15529,7 @@
         <v>44602</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>44524</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44721</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>44683</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>44686</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>44729</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>44705</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>44602</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>44592</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>45341</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
         <v>45091</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>45041</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>45041</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>45697</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>45338</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>45338</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>45338</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         <v>44833</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>45190</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         <v>45391</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17019,7 +17019,7 @@
         <v>45338</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>45338</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>44757</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>44757</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>45471</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>45389</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>45440</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>45140</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>45386</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45140</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44552</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>45279</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>44790</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>45208</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>45154</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18144,7 +18144,7 @@
         <v>46029</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>46029</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18290,7 +18290,7 @@
         <v>45544</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>44497</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>45428</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>45428</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>45428</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>45428</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>45544</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>45349</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>44902</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>46033</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>45112</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>45887</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>46034</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>45389</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>45336</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19385,7 +19385,7 @@
         <v>45428</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>45894</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
         <v>45089</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>46041</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>46040</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>44592</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         <v>45901</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19896,7 +19896,7 @@
         <v>46048</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>46048</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>45840</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>45428</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>45567</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>45720</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>45901</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>45674</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>46050</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>46050</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>45049</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>46052</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>46052</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>46052</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>46052</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>46052</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>44599</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>45910</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>45910</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>46052</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>46052</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>45910</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>45838</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>45476</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>45800</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>45910</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45801</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21912,7 +21912,7 @@
         <v>46058</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>45098</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>46057</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>46058</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
         <v>45804</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22282,7 +22282,7 @@
         <v>45604</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22360,7 +22360,7 @@
         <v>45604</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>45552</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>45923</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22584,7 +22584,7 @@
         <v>45747</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>45923</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>45804</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>45113</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>46069</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>45013</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>46071</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>45801</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>46071</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>46071</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         <v>46071</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>46071</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         <v>44942</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>45692</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>45233</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23684,7 +23684,7 @@
         <v>45211</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>45146</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
         <v>45649</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23903,7 +23903,7 @@
         <v>44942</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>45320</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24049,7 +24049,7 @@
         <v>44592</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>45688</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>45688</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>45408</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>45338</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24429,7 +24429,7 @@
         <v>45338</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>45805</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>45764</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24658,7 +24658,7 @@
         <v>45807</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>44985</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>45934</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>45934</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>45933</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>46086</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>45404</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>45934</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>45636</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>45702</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>46093</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>46093</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>46093</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>46093</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>46093</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25778,7 +25778,7 @@
         <v>46093</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>46093</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>45389</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>45940</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>45223</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>44945</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         <v>45945</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>45063</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>45770</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>45770</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>46106</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>46106</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>46106</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>46106</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26830,7 +26830,7 @@
         <v>45957</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>45278</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         <v>45009</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44923</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>45629</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>46114</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>46114</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>46114</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>46114</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>46114</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27590,7 +27590,7 @@
         <v>46114</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>45273</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>45960</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27819,7 +27819,7 @@
         <v>45960</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>45597</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>46122</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>45093</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>45317</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>44984</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>44984</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28345,7 +28345,7 @@
         <v>44971</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>45968</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>45075</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>44496</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>44971</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>45973</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28783,7 +28783,7 @@
         <v>45354</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>45460</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>45777</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>46132</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>45041</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>46132</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29226,7 +29226,7 @@
         <v>45547</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>44523</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29372,7 +29372,7 @@
         <v>45981</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29450,7 +29450,7 @@
         <v>45981</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>45981</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>45475</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>46010</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>45985</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>45985</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>45219</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>45181</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>45985</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30122,7 +30122,7 @@
         <v>45973</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30195,7 +30195,7 @@
         <v>45988</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30268,7 +30268,7 @@
         <v>45357</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>45642</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>45941</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>45615</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>45941</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>45804</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30721,7 +30721,7 @@
         <v>46135</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>45877</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>45989</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30940,7 +30940,7 @@
         <v>45288</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31018,7 +31018,7 @@
         <v>45734</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>45824</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>45897</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>45923</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31310,7 +31310,7 @@
         <v>45973</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>45989</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>45842</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>45960</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>45960</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>45118</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>45749</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45666</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>45995</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>45995</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>45995</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32128,7 +32128,7 @@
         <v>45995</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>45999</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>45818</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32347,7 +32347,7 @@
         <v>45201</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>45028</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>46000</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32571,7 +32571,7 @@
         <v>45692</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>44924</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32717,7 +32717,7 @@
         <v>46002</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>46000</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32868,7 +32868,7 @@
         <v>46002</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>45873</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>46133</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33092,7 +33092,7 @@
         <v>45474</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>45637</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33238,7 +33238,7 @@
         <v>45819</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33316,7 +33316,7 @@
         <v>46007</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>45819</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33462,7 +33462,7 @@
         <v>45224</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>44757</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33618,7 +33618,7 @@
         <v>46139</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>45842</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33764,7 +33764,7 @@
         <v>45204</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33837,7 +33837,7 @@
         <v>46013</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33910,7 +33910,7 @@
         <v>46013</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33983,7 +33983,7 @@
         <v>45155</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34056,7 +34056,7 @@
         <v>45273</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34129,7 +34129,7 @@
         <v>45273</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34202,7 +34202,7 @@
         <v>45747</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34280,7 +34280,7 @@
         <v>45915</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34353,7 +34353,7 @@
         <v>45622</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34426,7 +34426,7 @@
         <v>45233</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34499,7 +34499,7 @@
         <v>45644</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34572,7 +34572,7 @@
         <v>45745</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34645,7 +34645,7 @@
         <v>45749</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>45028</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
         <v>45244</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>45826</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>45826</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35015,7 +35015,7 @@
         <v>45801</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35088,7 +35088,7 @@
         <v>45826</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>44881</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35234,7 +35234,7 @@
         <v>44924</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>45012</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>45716</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>44844</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>45706</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35604,7 +35604,7 @@
         <v>45085</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45583</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35750,7 +35750,7 @@
         <v>45149</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>44882</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>44971</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>46149</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36042,7 +36042,7 @@
         <v>45705</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36115,7 +36115,7 @@
         <v>45082</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36188,7 +36188,7 @@
         <v>46153</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36261,7 +36261,7 @@
         <v>46153</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36334,7 +36334,7 @@
         <v>45181</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36412,7 +36412,7 @@
         <v>46156</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>45407</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>45385</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>44937</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>44937</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36787,7 +36787,7 @@
         <v>46156</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>46156</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36943,7 +36943,7 @@
         <v>46156</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37021,7 +37021,7 @@
         <v>46156</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37099,7 +37099,7 @@
         <v>45677</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>44917</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>45547</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>45547</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37391,7 +37391,7 @@
         <v>44838</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>45093</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45596</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>45295</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37688,7 +37688,7 @@
         <v>46162</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37761,7 +37761,7 @@
         <v>45716</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37839,7 +37839,7 @@
         <v>45590</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>45369</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37985,7 +37985,7 @@
         <v>45230</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38063,7 +38063,7 @@
         <v>44524</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>44503</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>46163</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38287,7 +38287,7 @@
         <v>45114</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38360,7 +38360,7 @@
         <v>45348</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38433,7 +38433,7 @@
         <v>45348</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>45001</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>46163</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>45082</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>44496</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>46167</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38881,7 +38881,7 @@
         <v>45561</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>45568</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39032,7 +39032,7 @@
         <v>46169</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>46106</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39183,7 +39183,7 @@
         <v>46106</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39261,7 +39261,7 @@
         <v>45842</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39334,7 +39334,7 @@
         <v>45792</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39407,7 +39407,7 @@
         <v>45865</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>45454</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39553,7 +39553,7 @@
         <v>46174</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39631,7 +39631,7 @@
         <v>45348</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39704,7 +39704,7 @@
         <v>46174</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39782,7 +39782,7 @@
         <v>44998</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>46174</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>46174</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40016,7 +40016,7 @@
         <v>46174</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>45103</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40167,7 +40167,7 @@
         <v>46174</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40245,7 +40245,7 @@
         <v>45181</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40318,7 +40318,7 @@
         <v>46176</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40391,7 +40391,7 @@
         <v>46177</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40469,7 +40469,7 @@
         <v>46177</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40547,7 +40547,7 @@
         <v>46176</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>45469</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>46132</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>46177</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40844,7 +40844,7 @@
         <v>45428</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40917,7 +40917,7 @@
         <v>46177</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40995,7 +40995,7 @@
         <v>46177</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>46177</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
         <v>46177</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>46177</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>46058</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         <v>46181</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>45153</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41531,7 +41531,7 @@
         <v>45530</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>46181</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>45720</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>46181</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>45229</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41896,7 +41896,7 @@
         <v>46183</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41969,7 +41969,7 @@
         <v>45389</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>46185</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>46185</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>46185</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42266,7 +42266,7 @@
         <v>46185</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42339,7 +42339,7 @@
         <v>45162</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42412,7 +42412,7 @@
         <v>45154</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         <v>44524</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42563,7 +42563,7 @@
         <v>44524</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>45146</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>46191</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
         <v>45590</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45118</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45355</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>46191</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43074,7 +43074,7 @@
         <v>45370</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>46027</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>46195</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>46196</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>45610</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>44659</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>46199</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43590,7 +43590,7 @@
         <v>44610</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>46203</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>46203</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43819,7 +43819,7 @@
         <v>46203</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>46203</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43975,7 +43975,7 @@
         <v>46203</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44053,7 +44053,7 @@
         <v>46203</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>46203</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>46203</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44287,7 +44287,7 @@
         <v>46203</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44365,7 +44365,7 @@
         <v>46203</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44443,7 +44443,7 @@
         <v>46203</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44521,7 +44521,7 @@
         <v>46203</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>46203</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>46203</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>46203</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>46203</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44911,7 +44911,7 @@
         <v>46203</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44989,7 +44989,7 @@
         <v>45685</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45062,7 +45062,7 @@
         <v>45642</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45140,7 +45140,7 @@
         <v>44470</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>46205</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45291,7 +45291,7 @@
         <v>45597</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45369,7 +45369,7 @@
         <v>46205</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45447,7 +45447,7 @@
         <v>46205</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45525,7 +45525,7 @@
         <v>44844</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45598,7 +45598,7 @@
         <v>46205</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>46205</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45754,7 +45754,7 @@
         <v>44757</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45832,7 +45832,7 @@
         <v>45229</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45905,7 +45905,7 @@
         <v>46205</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45983,7 +45983,7 @@
         <v>45279</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46056,7 +46056,7 @@
         <v>45372</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46129,7 +46129,7 @@
         <v>45440</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46202,7 +46202,7 @@
         <v>46206</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>46206</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46348,7 +46348,7 @@
         <v>46206</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46421,7 +46421,7 @@
         <v>46206</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46494,7 +46494,7 @@
         <v>45169</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46567,7 +46567,7 @@
         <v>45218</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46640,7 +46640,7 @@
         <v>45729</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46713,7 +46713,7 @@
         <v>45372</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46786,7 +46786,7 @@
         <v>44593</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46859,7 +46859,7 @@
         <v>45196</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
         <v>45404</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47005,7 +47005,7 @@
         <v>45597</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47083,7 +47083,7 @@
         <v>46209</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47156,7 +47156,7 @@
         <v>45547</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47229,7 +47229,7 @@
         <v>46210</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47302,7 +47302,7 @@
         <v>45223</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47375,7 +47375,7 @@
         <v>46253</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>44566</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>46253</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45664</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47667,7 +47667,7 @@
         <v>45057</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47740,7 +47740,7 @@
         <v>46253</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>46253</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47886,7 +47886,7 @@
         <v>45211</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47959,7 +47959,7 @@
         <v>45688</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         <v>45107</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48110,7 +48110,7 @@
         <v>45195</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48183,7 +48183,7 @@
         <v>45757</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48261,7 +48261,7 @@
         <v>45184</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48334,7 +48334,7 @@
         <v>45085</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48407,7 +48407,7 @@
         <v>45459</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48480,7 +48480,7 @@
         <v>46260</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>46260</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48626,7 +48626,7 @@
         <v>45153</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45174</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48772,7 +48772,7 @@
         <v>46260</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48845,7 +48845,7 @@
         <v>45230</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48923,7 +48923,7 @@
         <v>46260</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48996,7 +48996,7 @@
         <v>46218</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49069,7 +49069,7 @@
         <v>46262</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>46218</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49220,7 +49220,7 @@
         <v>44757</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>45769</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49371,7 +49371,7 @@
         <v>45155</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49444,7 +49444,7 @@
         <v>45243</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>44915</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49590,7 +49590,7 @@
         <v>46266</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49663,7 +49663,7 @@
         <v>46220</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>46220</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49809,7 +49809,7 @@
         <v>45336</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49882,7 +49882,7 @@
         <v>44858</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49955,7 +49955,7 @@
         <v>45230</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50033,7 +50033,7 @@
         <v>45351</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50106,7 +50106,7 @@
         <v>46226</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50179,7 +50179,7 @@
         <v>45264</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50252,7 +50252,7 @@
         <v>44939</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50325,7 +50325,7 @@
         <v>46274</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>46247</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50476,7 +50476,7 @@
         <v>45324</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50549,7 +50549,7 @@
         <v>45279</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50622,7 +50622,7 @@
         <v>44603</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50695,7 +50695,7 @@
         <v>46237</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>45146</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50846,7 +50846,7 @@
         <v>45146</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50919,7 +50919,7 @@
         <v>46237</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50992,7 +50992,7 @@
         <v>46237</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51065,7 +51065,7 @@
         <v>46237</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51143,7 +51143,7 @@
         <v>46237</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>46280</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51294,7 +51294,7 @@
         <v>45764</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51367,7 +51367,7 @@
         <v>45308</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51440,7 +51440,7 @@
         <v>45547</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51513,7 +51513,7 @@
         <v>45547</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51586,7 +51586,7 @@
         <v>45764</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51664,7 +51664,7 @@
         <v>45736</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51742,7 +51742,7 @@
         <v>45770</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51815,7 +51815,7 @@
         <v>44922</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51888,7 +51888,7 @@
         <v>46240</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51961,7 +51961,7 @@
         <v>46242</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52034,7 +52034,7 @@
         <v>46242</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52107,7 +52107,7 @@
         <v>46242</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52180,7 +52180,7 @@
         <v>45972</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52253,7 +52253,7 @@
         <v>46261</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52326,7 +52326,7 @@
         <v>45338</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52404,7 +52404,7 @@
         <v>46241</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52477,7 +52477,7 @@
         <v>46241</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52550,7 +52550,7 @@
         <v>46241</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52623,7 +52623,7 @@
         <v>44897</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52696,7 +52696,7 @@
         <v>46238</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52769,7 +52769,7 @@
         <v>44951</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52842,7 +52842,7 @@
         <v>44946</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>46287</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>45561</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53061,7 +53061,7 @@
         <v>44552</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53134,7 +53134,7 @@
         <v>44533</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53207,7 +53207,7 @@
         <v>46287</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53280,7 +53280,7 @@
         <v>46139</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53353,7 +53353,7 @@
         <v>44638</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53426,7 +53426,7 @@
         <v>45230</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53504,7 +53504,7 @@
         <v>44887</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53577,7 +53577,7 @@
         <v>44468</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53650,7 +53650,7 @@
         <v>45398</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53723,7 +53723,7 @@
         <v>45607</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53796,7 +53796,7 @@
         <v>45595</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53869,7 +53869,7 @@
         <v>45688</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53942,7 +53942,7 @@
         <v>45546</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54015,7 +54015,7 @@
         <v>45226</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54088,7 +54088,7 @@
         <v>45455</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54166,7 +54166,7 @@
         <v>45232</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54239,7 +54239,7 @@
         <v>45568</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54317,7 +54317,7 @@
         <v>45275</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54390,7 +54390,7 @@
         <v>45245</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54463,7 +54463,7 @@
         <v>44711</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54536,7 +54536,7 @@
         <v>44994</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54609,7 +54609,7 @@
         <v>45174</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54682,7 +54682,7 @@
         <v>44908</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54760,7 +54760,7 @@
         <v>44697</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54838,7 +54838,7 @@
         <v>45069</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54911,7 +54911,7 @@
         <v>45668</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54984,7 +54984,7 @@
         <v>45260</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55057,7 +55057,7 @@
         <v>44865</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55130,7 +55130,7 @@
         <v>45156</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55203,7 +55203,7 @@
         <v>45369</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55276,7 +55276,7 @@
         <v>45434</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>45375</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55422,7 +55422,7 @@
         <v>45427</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55495,7 +55495,7 @@
         <v>45225</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55568,7 +55568,7 @@
         <v>45350</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55641,7 +55641,7 @@
         <v>44998</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55734,7 +55734,7 @@
         <v>45428</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55807,7 +55807,7 @@
         <v>45454</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55880,7 +55880,7 @@
         <v>45118</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55953,7 +55953,7 @@
         <v>44593</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56026,7 +56026,7 @@
         <v>45105</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56099,7 +56099,7 @@
         <v>45164</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56172,7 +56172,7 @@
         <v>45615</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56245,7 +56245,7 @@
         <v>45244</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56318,7 +56318,7 @@
         <v>45749</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56396,7 +56396,7 @@
         <v>45764</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56474,7 +56474,7 @@
         <v>45459</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56547,7 +56547,7 @@
         <v>45005</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56620,7 +56620,7 @@
         <v>45098</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56693,7 +56693,7 @@
         <v>45590</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56766,7 +56766,7 @@
         <v>45604</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56844,7 +56844,7 @@
         <v>45604</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56922,7 +56922,7 @@
         <v>45604</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57000,7 +57000,7 @@
         <v>45190</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57073,7 +57073,7 @@
         <v>45708</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57146,7 +57146,7 @@
         <v>45692</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57219,7 +57219,7 @@
         <v>45204</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57292,7 +57292,7 @@
         <v>45229</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57365,7 +57365,7 @@
         <v>45091</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57443,7 +57443,7 @@
         <v>45085</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57516,7 +57516,7 @@
         <v>44994</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57589,7 +57589,7 @@
         <v>44610</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57662,7 +57662,7 @@
         <v>44942</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57735,7 +57735,7 @@
         <v>44789</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57808,7 +57808,7 @@
         <v>45085</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57881,7 +57881,7 @@
         <v>45427</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57954,7 +57954,7 @@
         <v>45338</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58032,7 +58032,7 @@
         <v>45338</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58110,7 +58110,7 @@
         <v>45716</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58188,7 +58188,7 @@
         <v>45019</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58261,7 +58261,7 @@
         <v>45642</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58334,7 +58334,7 @@
         <v>45714</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58407,7 +58407,7 @@
         <v>45575</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58480,7 +58480,7 @@
         <v>45057</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58553,7 +58553,7 @@
         <v>45154</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58626,7 +58626,7 @@
         <v>45722</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58699,7 +58699,7 @@
         <v>45434</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58772,7 +58772,7 @@
         <v>45229</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58845,7 +58845,7 @@
         <v>44734</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58918,7 +58918,7 @@
         <v>44734</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58991,7 +58991,7 @@
         <v>45165</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59064,7 +59064,7 @@
         <v>45245</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59137,7 +59137,7 @@
         <v>45639</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59210,7 +59210,7 @@
         <v>45428</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59283,7 +59283,7 @@
         <v>45384</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59356,7 +59356,7 @@
         <v>45391</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59429,7 +59429,7 @@
         <v>45600</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59502,7 +59502,7 @@
         <v>45273</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59575,7 +59575,7 @@
         <v>45601</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59648,7 +59648,7 @@
         <v>45516</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59721,7 +59721,7 @@
         <v>44526</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59799,7 +59799,7 @@
         <v>45488</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59872,7 +59872,7 @@
         <v>45502</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59950,7 +59950,7 @@
         <v>45742</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60023,7 +60023,7 @@
         <v>45476</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60096,7 +60096,7 @@
         <v>45786</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60169,7 +60169,7 @@
         <v>45552</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60242,7 +60242,7 @@
         <v>45604</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60315,7 +60315,7 @@
         <v>44726</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60388,7 +60388,7 @@
         <v>44726</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60461,7 +60461,7 @@
         <v>44489</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60539,7 +60539,7 @@
         <v>44916</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60612,7 +60612,7 @@
         <v>45161</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60690,7 +60690,7 @@
         <v>45476</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60763,7 +60763,7 @@
         <v>44963</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60836,7 +60836,7 @@
         <v>44916</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60909,7 +60909,7 @@
         <v>45140</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60982,7 +60982,7 @@
         <v>44837</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61055,7 +61055,7 @@
         <v>45161</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61133,7 +61133,7 @@
         <v>44893</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61206,7 +61206,7 @@
         <v>44916</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61279,7 +61279,7 @@
         <v>45411</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61352,7 +61352,7 @@
         <v>45791</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61425,7 +61425,7 @@
         <v>45910</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61498,7 +61498,7 @@
         <v>46030</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61571,7 +61571,7 @@
         <v>46051</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61644,7 +61644,7 @@
         <v>46275</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61717,7 +61717,7 @@
         <v>46280</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>

--- a/Översikt UPPVIDINGE.xlsx
+++ b/Översikt UPPVIDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45174</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>44972</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>44972</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45442</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45789</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>46119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>46183</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>44980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>46183</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>44607</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45789</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>46119</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>46149</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>46119</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>45995</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44859</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>46066</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>46276</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>46183</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>45313</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>45366</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44972</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>46066</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>45158</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>44939</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>45840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>45604</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>46247</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>45195</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>45450</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>44979</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>46051</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>45604</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45205</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>45103</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
         <v>45568</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>46169</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>45688</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>46205</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>45517</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>45404</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>45117</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>46218</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>44937</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>45320</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>45604</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>44833</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>44972</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44972</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>44484</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>45789</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>44734</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>44827</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>44690</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>44788</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>44950</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         <v>44550</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>45534</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>46051</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>45435</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>45623</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>45939</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>46100</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>45981</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>45820</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>45982</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>45826</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>45825</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>44676</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         <v>46154</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>45840</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>45320</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>44984</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>46185</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>45897</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>44858</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>44998</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>44663</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>46255</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>44757</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>45688</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>46162</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>44858</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>46247</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>46247</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>46247</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>45105</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>45517</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>45440</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>44972</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>45810</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>44865</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>44887</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>44887</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>44524</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>44613</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>44483</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>44487</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>44574</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>44536</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>44510</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>44812</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>44552</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>44859</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>44574</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>44859</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>44676</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>44859</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>44859</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>44749</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>44574</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44602</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>44580</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12881,7 +12881,7 @@
         <v>44602</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>44859</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
         <v>44795</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>44757</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>44887</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>44588</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>44845</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>44552</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>44483</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>44483</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>44475</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13699,7 +13699,7 @@
         <v>44503</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13772,7 +13772,7 @@
         <v>44510</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>44803</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>44887</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>44610</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>44609</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>44795</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>44795</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>44582</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>44601</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>44858</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>44711</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>44522</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>44837</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14721,7 +14721,7 @@
         <v>44859</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>44607</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>44607</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>44887</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>44490</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         <v>44887</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>44676</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
         <v>44475</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>44574</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>44466</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>44603</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15529,7 +15529,7 @@
         <v>44602</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>44524</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44721</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>44683</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>44686</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>44729</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>44705</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>44602</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>44592</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>45341</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
         <v>45091</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>45041</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>45041</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>45697</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>45338</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>45338</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>45338</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         <v>44833</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>45190</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         <v>45391</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17019,7 +17019,7 @@
         <v>45338</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>45338</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>44757</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>44757</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>45471</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>45389</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>45440</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>45140</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>45386</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45140</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44552</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>45279</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>44790</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>45208</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>45154</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18144,7 +18144,7 @@
         <v>46029</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>46029</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18290,7 +18290,7 @@
         <v>45544</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>44497</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>45428</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>45428</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>45428</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>45428</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>45544</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>45349</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>44902</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>46033</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>45112</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>45887</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>46034</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>45389</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>45336</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19385,7 +19385,7 @@
         <v>45428</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>45894</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
         <v>45089</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>46041</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>46040</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>44592</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         <v>45901</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19896,7 +19896,7 @@
         <v>46048</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>46048</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>45840</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>45428</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>45567</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>45720</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>45901</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>45674</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>46050</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>46050</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>45049</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>46052</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>46052</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>46052</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>46052</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>46052</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>44599</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>45910</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>45910</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>46052</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>46052</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>45910</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>45838</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>45476</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>45800</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>45910</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45801</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21912,7 +21912,7 @@
         <v>46058</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>45098</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>46057</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>46058</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
         <v>45804</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22282,7 +22282,7 @@
         <v>45604</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22360,7 +22360,7 @@
         <v>45604</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>45552</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>45923</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22584,7 +22584,7 @@
         <v>45747</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>45923</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>45804</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>45113</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>46069</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>45013</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>46071</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>45801</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>46071</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>46071</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         <v>46071</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>46071</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         <v>44942</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>45692</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>45233</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23684,7 +23684,7 @@
         <v>45211</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>45146</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
         <v>45649</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23903,7 +23903,7 @@
         <v>44942</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>45320</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24049,7 +24049,7 @@
         <v>44592</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>45688</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>45688</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>45408</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>45338</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24429,7 +24429,7 @@
         <v>45338</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>45805</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>45764</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24658,7 +24658,7 @@
         <v>45807</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>44985</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>45934</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>45934</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>45933</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>46086</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>45404</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>45934</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>45636</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>45702</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>46093</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>46093</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>46093</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>46093</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>46093</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25778,7 +25778,7 @@
         <v>46093</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>46093</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>45389</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>45940</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>45223</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>44945</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         <v>45945</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>45063</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>45770</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>45770</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>46106</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>46106</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>46106</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>46106</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26830,7 +26830,7 @@
         <v>45957</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>45278</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         <v>45009</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44923</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>45629</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>46114</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>46114</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>46114</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>46114</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>46114</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27590,7 +27590,7 @@
         <v>46114</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>45273</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>45960</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27819,7 +27819,7 @@
         <v>45960</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>45597</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>46122</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>45093</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>45317</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>44984</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>44984</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28345,7 +28345,7 @@
         <v>44971</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>45968</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>45075</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>44496</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>44971</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>45973</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28783,7 +28783,7 @@
         <v>45354</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>45460</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>45777</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>46132</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>45041</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>46132</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29226,7 +29226,7 @@
         <v>45547</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>44523</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29372,7 +29372,7 @@
         <v>45981</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29450,7 +29450,7 @@
         <v>45981</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>45981</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>45475</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>46010</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>45985</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>45985</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>45219</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>45181</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>45985</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30122,7 +30122,7 @@
         <v>45973</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30195,7 +30195,7 @@
         <v>45988</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30268,7 +30268,7 @@
         <v>45357</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>45642</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>45941</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>45615</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>45941</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>45804</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30721,7 +30721,7 @@
         <v>46135</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>45877</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>45989</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30940,7 +30940,7 @@
         <v>45288</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31018,7 +31018,7 @@
         <v>45734</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>45824</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>45897</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>45923</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31310,7 +31310,7 @@
         <v>45973</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>45989</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>45842</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>45960</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>45960</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>45118</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>45749</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45666</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>45995</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>45995</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>45995</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32128,7 +32128,7 @@
         <v>45995</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>45999</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>45818</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32347,7 +32347,7 @@
         <v>45201</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>45028</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>46000</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32571,7 +32571,7 @@
         <v>45692</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>44924</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32717,7 +32717,7 @@
         <v>46002</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>46000</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32868,7 +32868,7 @@
         <v>46002</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>45873</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         <v>46133</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33092,7 +33092,7 @@
         <v>45474</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>45637</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33238,7 +33238,7 @@
         <v>45819</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33316,7 +33316,7 @@
         <v>46007</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>45819</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33462,7 +33462,7 @@
         <v>45224</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>44757</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33618,7 +33618,7 @@
         <v>46139</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>45842</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33764,7 +33764,7 @@
         <v>45204</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33837,7 +33837,7 @@
         <v>46013</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33910,7 +33910,7 @@
         <v>46013</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33983,7 +33983,7 @@
         <v>45155</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34056,7 +34056,7 @@
         <v>45273</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34129,7 +34129,7 @@
         <v>45273</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34202,7 +34202,7 @@
         <v>45747</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34280,7 +34280,7 @@
         <v>45915</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34353,7 +34353,7 @@
         <v>45622</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34426,7 +34426,7 @@
         <v>45233</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34499,7 +34499,7 @@
         <v>45644</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34572,7 +34572,7 @@
         <v>45745</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34645,7 +34645,7 @@
         <v>45749</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>45028</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
         <v>45244</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>45826</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>45826</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35015,7 +35015,7 @@
         <v>45801</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35088,7 +35088,7 @@
         <v>45826</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>44881</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35234,7 +35234,7 @@
         <v>44924</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>45012</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>45716</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>44844</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>45706</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35604,7 +35604,7 @@
         <v>45085</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45583</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35750,7 +35750,7 @@
         <v>45149</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>44882</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>44971</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>46149</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36042,7 +36042,7 @@
         <v>45705</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36115,7 +36115,7 @@
         <v>45082</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36188,7 +36188,7 @@
         <v>46153</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36261,7 +36261,7 @@
         <v>46153</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36334,7 +36334,7 @@
         <v>45181</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36412,7 +36412,7 @@
         <v>46156</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>45407</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>45385</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>44937</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>44937</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36787,7 +36787,7 @@
         <v>46156</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>46156</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36943,7 +36943,7 @@
         <v>46156</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37021,7 +37021,7 @@
         <v>46156</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37099,7 +37099,7 @@
         <v>45677</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>44917</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>45547</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>45547</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37391,7 +37391,7 @@
         <v>44838</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>45093</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45596</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>45295</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37688,7 +37688,7 @@
         <v>46162</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37761,7 +37761,7 @@
         <v>45716</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37839,7 +37839,7 @@
         <v>45590</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37912,7 +37912,7 @@
         <v>45369</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37985,7 +37985,7 @@
         <v>45230</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38063,7 +38063,7 @@
         <v>44524</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>44503</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>46163</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38287,7 +38287,7 @@
         <v>45114</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38360,7 +38360,7 @@
         <v>45348</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38433,7 +38433,7 @@
         <v>45348</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>45001</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>46163</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>45082</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>44496</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>46167</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38881,7 +38881,7 @@
         <v>45561</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>45568</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39032,7 +39032,7 @@
         <v>46169</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>46106</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39183,7 +39183,7 @@
         <v>46106</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39261,7 +39261,7 @@
         <v>45842</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39334,7 +39334,7 @@
         <v>45792</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39407,7 +39407,7 @@
         <v>45865</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>45454</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39553,7 +39553,7 @@
         <v>46174</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39631,7 +39631,7 @@
         <v>45348</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39704,7 +39704,7 @@
         <v>46174</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39782,7 +39782,7 @@
         <v>44998</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>46174</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>46174</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40016,7 +40016,7 @@
         <v>46174</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>45103</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40167,7 +40167,7 @@
         <v>46174</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40245,7 +40245,7 @@
         <v>45181</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40318,7 +40318,7 @@
         <v>46176</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40391,7 +40391,7 @@
         <v>46177</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40469,7 +40469,7 @@
         <v>46177</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40547,7 +40547,7 @@
         <v>46176</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>45469</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>46132</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>46177</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40844,7 +40844,7 @@
         <v>45428</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40917,7 +40917,7 @@
         <v>46177</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40995,7 +40995,7 @@
         <v>46177</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>46177</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
         <v>46177</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>46177</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>46058</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         <v>46181</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>45153</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41531,7 +41531,7 @@
         <v>45530</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>46181</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>45720</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>46181</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>45229</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41896,7 +41896,7 @@
         <v>46183</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41969,7 +41969,7 @@
         <v>45389</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>46185</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>46185</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>46185</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42266,7 +42266,7 @@
         <v>46185</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42339,7 +42339,7 @@
         <v>45162</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42412,7 +42412,7 @@
         <v>45154</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         <v>44524</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42563,7 +42563,7 @@
         <v>44524</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>45146</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>46191</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
         <v>45590</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45118</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45355</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>46191</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43074,7 +43074,7 @@
         <v>45370</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>46027</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>46195</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>46196</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>45610</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>44659</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>46199</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43590,7 +43590,7 @@
         <v>44610</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>46203</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>46203</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43819,7 +43819,7 @@
         <v>46203</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>46203</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43975,7 +43975,7 @@
         <v>46203</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44053,7 +44053,7 @@
         <v>46203</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>46203</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>46203</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44287,7 +44287,7 @@
         <v>46203</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44365,7 +44365,7 @@
         <v>46203</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44443,7 +44443,7 @@
         <v>46203</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44521,7 +44521,7 @@
         <v>46203</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>46203</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>46203</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>46203</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>46203</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44911,7 +44911,7 @@
         <v>46203</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44989,7 +44989,7 @@
         <v>45685</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45062,7 +45062,7 @@
         <v>45642</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45140,7 +45140,7 @@
         <v>44470</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>46205</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45291,7 +45291,7 @@
         <v>45597</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45369,7 +45369,7 @@
         <v>46205</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45447,7 +45447,7 @@
         <v>46205</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45525,7 +45525,7 @@
         <v>44844</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45598,7 +45598,7 @@
         <v>46205</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>46205</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45754,7 +45754,7 @@
         <v>44757</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45832,7 +45832,7 @@
         <v>45229</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45905,7 +45905,7 @@
         <v>46205</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45983,7 +45983,7 @@
         <v>45279</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46056,7 +46056,7 @@
         <v>45372</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46129,7 +46129,7 @@
         <v>45440</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46202,7 +46202,7 @@
         <v>46206</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>46206</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46348,7 +46348,7 @@
         <v>46206</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46421,7 +46421,7 @@
         <v>46206</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46494,7 +46494,7 @@
         <v>45169</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46567,7 +46567,7 @@
         <v>45218</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46640,7 +46640,7 @@
         <v>45729</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46713,7 +46713,7 @@
         <v>45372</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46786,7 +46786,7 @@
         <v>44593</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46859,7 +46859,7 @@
         <v>45196</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
         <v>45404</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47005,7 +47005,7 @@
         <v>45597</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47083,7 +47083,7 @@
         <v>46209</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47156,7 +47156,7 @@
         <v>45547</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47229,7 +47229,7 @@
         <v>46210</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47302,7 +47302,7 @@
         <v>45223</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47375,7 +47375,7 @@
         <v>46253</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>44566</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>46253</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45664</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47667,7 +47667,7 @@
         <v>45057</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47740,7 +47740,7 @@
         <v>46253</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>46253</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47886,7 +47886,7 @@
         <v>45211</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47959,7 +47959,7 @@
         <v>45688</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         <v>45107</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48110,7 +48110,7 @@
         <v>45195</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48183,7 +48183,7 @@
         <v>45757</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48261,7 +48261,7 @@
         <v>45184</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48334,7 +48334,7 @@
         <v>45085</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48407,7 +48407,7 @@
         <v>45459</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48480,7 +48480,7 @@
         <v>46260</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>46260</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48626,7 +48626,7 @@
         <v>45153</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45174</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48772,7 +48772,7 @@
         <v>46260</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48845,7 +48845,7 @@
         <v>45230</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48923,7 +48923,7 @@
         <v>46260</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48996,7 +48996,7 @@
         <v>46218</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49069,7 +49069,7 @@
         <v>46262</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>46218</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49220,7 +49220,7 @@
         <v>44757</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>45769</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49371,7 +49371,7 @@
         <v>45155</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49444,7 +49444,7 @@
         <v>45243</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>44915</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49590,7 +49590,7 @@
         <v>46266</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49663,7 +49663,7 @@
         <v>46220</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>46220</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49809,7 +49809,7 @@
         <v>45336</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49882,7 +49882,7 @@
         <v>44858</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49955,7 +49955,7 @@
         <v>45230</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50033,7 +50033,7 @@
         <v>45351</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50106,7 +50106,7 @@
         <v>46226</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50179,7 +50179,7 @@
         <v>45264</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50252,7 +50252,7 @@
         <v>44939</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50325,7 +50325,7 @@
         <v>46274</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>46247</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50476,7 +50476,7 @@
         <v>45324</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50549,7 +50549,7 @@
         <v>45279</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50622,7 +50622,7 @@
         <v>44603</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50695,7 +50695,7 @@
         <v>46237</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>45146</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50846,7 +50846,7 @@
         <v>45146</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50919,7 +50919,7 @@
         <v>46237</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50992,7 +50992,7 @@
         <v>46237</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51065,7 +51065,7 @@
         <v>46237</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51143,7 +51143,7 @@
         <v>46237</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>46280</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51294,7 +51294,7 @@
         <v>45764</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51367,7 +51367,7 @@
         <v>45308</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51440,7 +51440,7 @@
         <v>45547</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51513,7 +51513,7 @@
         <v>45547</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51586,7 +51586,7 @@
         <v>45764</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51664,7 +51664,7 @@
         <v>45736</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51742,7 +51742,7 @@
         <v>45770</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51815,7 +51815,7 @@
         <v>44922</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51888,7 +51888,7 @@
         <v>46240</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51961,7 +51961,7 @@
         <v>46242</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52034,7 +52034,7 @@
         <v>46242</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52107,7 +52107,7 @@
         <v>46242</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52180,7 +52180,7 @@
         <v>45972</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52253,7 +52253,7 @@
         <v>46261</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52326,7 +52326,7 @@
         <v>45338</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52404,7 +52404,7 @@
         <v>46241</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52477,7 +52477,7 @@
         <v>46241</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52550,7 +52550,7 @@
         <v>46241</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52623,7 +52623,7 @@
         <v>44897</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52696,7 +52696,7 @@
         <v>46238</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52769,7 +52769,7 @@
         <v>44951</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52842,7 +52842,7 @@
         <v>44946</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>46287</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>45561</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53061,7 +53061,7 @@
         <v>44552</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53134,7 +53134,7 @@
         <v>44533</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53207,7 +53207,7 @@
         <v>46287</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53280,7 +53280,7 @@
         <v>46139</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53353,7 +53353,7 @@
         <v>44638</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53426,7 +53426,7 @@
         <v>45230</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53504,7 +53504,7 @@
         <v>44887</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53577,7 +53577,7 @@
         <v>44468</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53650,7 +53650,7 @@
         <v>45398</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53723,7 +53723,7 @@
         <v>45607</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53796,7 +53796,7 @@
         <v>45595</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53869,7 +53869,7 @@
         <v>45688</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53942,7 +53942,7 @@
         <v>45546</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54015,7 +54015,7 @@
         <v>45226</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54088,7 +54088,7 @@
         <v>45455</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54166,7 +54166,7 @@
         <v>45232</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54239,7 +54239,7 @@
         <v>45568</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54317,7 +54317,7 @@
         <v>45275</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54390,7 +54390,7 @@
         <v>45245</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54463,7 +54463,7 @@
         <v>44711</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54536,7 +54536,7 @@
         <v>44994</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54609,7 +54609,7 @@
         <v>45174</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54682,7 +54682,7 @@
         <v>44908</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54760,7 +54760,7 @@
         <v>44697</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54838,7 +54838,7 @@
         <v>45069</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54911,7 +54911,7 @@
         <v>45668</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54984,7 +54984,7 @@
         <v>45260</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55057,7 +55057,7 @@
         <v>44865</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55130,7 +55130,7 @@
         <v>45156</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55203,7 +55203,7 @@
         <v>45369</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55276,7 +55276,7 @@
         <v>45434</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>45375</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55422,7 +55422,7 @@
         <v>45427</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55495,7 +55495,7 @@
         <v>45225</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55568,7 +55568,7 @@
         <v>45350</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55641,7 +55641,7 @@
         <v>44998</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55734,7 +55734,7 @@
         <v>45428</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55807,7 +55807,7 @@
         <v>45454</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55880,7 +55880,7 @@
         <v>45118</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55953,7 +55953,7 @@
         <v>44593</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56026,7 +56026,7 @@
         <v>45105</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56099,7 +56099,7 @@
         <v>45164</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56172,7 +56172,7 @@
         <v>45615</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56245,7 +56245,7 @@
         <v>45244</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56318,7 +56318,7 @@
         <v>45749</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56396,7 +56396,7 @@
         <v>45764</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56474,7 +56474,7 @@
         <v>45459</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56547,7 +56547,7 @@
         <v>45005</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56620,7 +56620,7 @@
         <v>45098</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56693,7 +56693,7 @@
         <v>45590</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56766,7 +56766,7 @@
         <v>45604</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56844,7 +56844,7 @@
         <v>45604</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56922,7 +56922,7 @@
         <v>45604</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57000,7 +57000,7 @@
         <v>45190</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57073,7 +57073,7 @@
         <v>45708</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57146,7 +57146,7 @@
         <v>45692</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57219,7 +57219,7 @@
         <v>45204</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57292,7 +57292,7 @@
         <v>45229</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57365,7 +57365,7 @@
         <v>45091</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57443,7 +57443,7 @@
         <v>45085</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57516,7 +57516,7 @@
         <v>44994</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57589,7 +57589,7 @@
         <v>44610</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57662,7 +57662,7 @@
         <v>44942</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57735,7 +57735,7 @@
         <v>44789</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57808,7 +57808,7 @@
         <v>45085</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57881,7 +57881,7 @@
         <v>45427</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57954,7 +57954,7 @@
         <v>45338</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58032,7 +58032,7 @@
         <v>45338</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58110,7 +58110,7 @@
         <v>45716</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58188,7 +58188,7 @@
         <v>45019</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58261,7 +58261,7 @@
         <v>45642</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58334,7 +58334,7 @@
         <v>45714</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58407,7 +58407,7 @@
         <v>45575</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58480,7 +58480,7 @@
         <v>45057</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58553,7 +58553,7 @@
         <v>45154</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58626,7 +58626,7 @@
         <v>45722</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58699,7 +58699,7 @@
         <v>45434</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58772,7 +58772,7 @@
         <v>45229</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58845,7 +58845,7 @@
         <v>44734</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58918,7 +58918,7 @@
         <v>44734</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58991,7 +58991,7 @@
         <v>45165</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59064,7 +59064,7 @@
         <v>45245</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59137,7 +59137,7 @@
         <v>45639</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59210,7 +59210,7 @@
         <v>45428</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59283,7 +59283,7 @@
         <v>45384</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59356,7 +59356,7 @@
         <v>45391</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59429,7 +59429,7 @@
         <v>45600</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59502,7 +59502,7 @@
         <v>45273</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59575,7 +59575,7 @@
         <v>45601</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59648,7 +59648,7 @@
         <v>45516</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59721,7 +59721,7 @@
         <v>44526</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59799,7 +59799,7 @@
         <v>45488</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59872,7 +59872,7 @@
         <v>45502</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59950,7 +59950,7 @@
         <v>45742</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60023,7 +60023,7 @@
         <v>45476</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60096,7 +60096,7 @@
         <v>45786</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60169,7 +60169,7 @@
         <v>45552</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60242,7 +60242,7 @@
         <v>45604</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60315,7 +60315,7 @@
         <v>44726</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60388,7 +60388,7 @@
         <v>44726</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60461,7 +60461,7 @@
         <v>44489</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60539,7 +60539,7 @@
         <v>44916</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60612,7 +60612,7 @@
         <v>45161</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60690,7 +60690,7 @@
         <v>45476</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60763,7 +60763,7 @@
         <v>44963</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60836,7 +60836,7 @@
         <v>44916</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60909,7 +60909,7 @@
         <v>45140</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60982,7 +60982,7 @@
         <v>44837</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61055,7 +61055,7 @@
         <v>45161</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61133,7 +61133,7 @@
         <v>44893</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61206,7 +61206,7 @@
         <v>44916</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61279,7 +61279,7 @@
         <v>45411</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61352,7 +61352,7 @@
         <v>45791</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61425,7 +61425,7 @@
         <v>45910</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61498,7 +61498,7 @@
         <v>46030</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61571,7 +61571,7 @@
         <v>46051</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61644,7 +61644,7 @@
         <v>46275</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61717,7 +61717,7 @@
         <v>46280</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>

--- a/Översikt UPPVIDINGE.xlsx
+++ b/Översikt UPPVIDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45174</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>44972</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>44972</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45442</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45789</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>46119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>46183</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>44980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>46183</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>44607</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45789</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>46119</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>46149</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>46119</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>45995</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44859</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>46066</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>46276</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>46183</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>45366</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>45313</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44972</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>46066</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>45158</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>44939</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>45840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>45604</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>45195</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>46247</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>45450</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>44979</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>44833</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>45517</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45404</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>45688</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>45604</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>46051</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>44937</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>45205</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>45103</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>45320</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>46169</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>45604</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>46205</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>46218</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>45117</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>45568</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>46297</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>44972</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>44972</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44484</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>45789</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>44734</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44827</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>44690</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>44788</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>45534</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>46051</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>45939</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>45623</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44858</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>44984</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>44663</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>46100</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>45981</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>45820</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>45825</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>45826</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>44757</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>45840</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>45982</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>44676</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>46154</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>44550</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>45320</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>46185</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>45897</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>44858</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>45105</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>45435</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>45688</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>46247</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>46247</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>46247</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>46162</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         <v>44950</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>46255</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         <v>44998</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
         <v>45517</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>45440</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>44972</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>45810</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>44865</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>44887</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>44887</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>44524</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>44613</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>44483</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>44487</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>44552</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>44536</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>44574</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>44510</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>44812</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>44859</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>44574</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>44859</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         <v>44676</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>44859</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>44859</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>44749</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>44574</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>44602</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>44580</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>44602</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>44859</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>44795</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>44757</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>44887</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>44588</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>44845</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>44552</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44483</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44483</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>44475</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>44503</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>44510</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>44803</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>44887</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>44609</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>44610</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>44795</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>44795</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>44582</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>44601</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>44858</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>44711</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>44522</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>44837</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
         <v>44859</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>44887</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14973,7 +14973,7 @@
         <v>44887</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>44490</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>44676</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>44607</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>44607</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>44475</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>44574</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>44603</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>44602</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>44524</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>44721</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>44683</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>44686</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>44729</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>44705</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>44602</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>44592</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>45736</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45674</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>45338</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>45338</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>45338</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>45338</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>45156</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>45098</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>45770</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>44524</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>45181</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>44922</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>45229</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>45389</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>44610</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>45089</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>45697</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>45385</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>44789</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         <v>45389</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>45398</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>45384</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45428</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45428</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>45118</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>45338</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45488</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>45590</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>45664</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>45786</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>45604</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45552</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>45742</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>45668</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>45320</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>45348</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>45714</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>46002</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>46002</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>45471</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>46007</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>45887</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>44497</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>45544</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>44942</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>45408</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>46013</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>46013</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>44902</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>45226</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>45229</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>46029</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>44757</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>45894</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>46029</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>45745</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>45223</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>46034</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45901</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>45901</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>46033</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>45428</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>45840</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20873,7 +20873,7 @@
         <v>45567</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>46040</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>45838</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>45910</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>45233</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>46041</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>45910</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>44524</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>45910</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21535,7 +21535,7 @@
         <v>45910</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>45245</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>45153</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>45720</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21827,7 +21827,7 @@
         <v>46048</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>46048</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21973,7 +21973,7 @@
         <v>46050</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>45801</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22124,7 +22124,7 @@
         <v>46050</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45801</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>44985</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45800</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>45804</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>45273</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45805</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>46052</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>45804</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>45764</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>45807</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>46052</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>46052</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>46052</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>45923</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>45923</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
         <v>46052</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>46052</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23473,7 +23473,7 @@
         <v>44566</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>46057</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>46058</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23692,7 +23692,7 @@
         <v>46058</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>45278</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23843,7 +23843,7 @@
         <v>45933</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>45348</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>45934</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24062,7 +24062,7 @@
         <v>45934</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>46069</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>45934</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>45041</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24359,7 +24359,7 @@
         <v>45041</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>44924</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>46071</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>46071</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>45469</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         <v>46071</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>46071</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>45940</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>45440</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>45622</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>44924</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25162,7 +25162,7 @@
         <v>45174</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         <v>45957</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>45757</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25386,7 +25386,7 @@
         <v>46086</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>44984</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>45459</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>45428</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>45369</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>45082</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>45960</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25902,7 +25902,7 @@
         <v>45085</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25975,7 +25975,7 @@
         <v>45960</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>44945</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>45230</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>46093</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>46093</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>46093</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>46093</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>46093</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>46093</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>46093</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>45636</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>44734</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>44734</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>45968</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>45583</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>45336</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>44942</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27261,7 +27261,7 @@
         <v>44942</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>45230</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>45973</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>46106</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>45107</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>46106</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27714,7 +27714,7 @@
         <v>45818</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>45981</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27865,7 +27865,7 @@
         <v>45777</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>45981</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>45981</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>45819</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28177,7 +28177,7 @@
         <v>45819</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28250,7 +28250,7 @@
         <v>44951</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>45770</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>45985</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>45985</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28542,7 +28542,7 @@
         <v>45985</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>46114</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>46114</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28771,7 +28771,7 @@
         <v>45547</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>45547</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>46114</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28995,7 +28995,7 @@
         <v>45941</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         <v>46114</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>46114</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29229,7 +29229,7 @@
         <v>46114</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>45688</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>45644</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29458,7 +29458,7 @@
         <v>45989</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29531,7 +29531,7 @@
         <v>45941</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>45093</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>45597</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>45989</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>44917</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>45988</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29979,7 +29979,7 @@
         <v>45973</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>45428</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30125,7 +30125,7 @@
         <v>45428</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30198,7 +30198,7 @@
         <v>46122</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30271,7 +30271,7 @@
         <v>45428</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30344,7 +30344,7 @@
         <v>45960</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>45716</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30500,7 +30500,7 @@
         <v>45960</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30578,7 +30578,7 @@
         <v>45995</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30651,7 +30651,7 @@
         <v>45826</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30724,7 +30724,7 @@
         <v>45995</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30797,7 +30797,7 @@
         <v>44984</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30870,7 +30870,7 @@
         <v>45995</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>45995</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45999</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>45826</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>44638</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>44865</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>45826</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>46000</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>46000</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>44603</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>46132</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>44503</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>46132</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>45637</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>45028</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>45552</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32043,7 +32043,7 @@
         <v>44994</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>45232</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32189,7 +32189,7 @@
         <v>46135</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32262,7 +32262,7 @@
         <v>45219</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>45824</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32408,7 +32408,7 @@
         <v>45338</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32486,7 +32486,7 @@
         <v>45338</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32564,7 +32564,7 @@
         <v>45474</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>45288</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32715,7 +32715,7 @@
         <v>45842</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32788,7 +32788,7 @@
         <v>46139</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>45230</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         <v>45428</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33012,7 +33012,7 @@
         <v>45295</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
         <v>45747</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33168,7 +33168,7 @@
         <v>45597</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>45973</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>44711</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33392,7 +33392,7 @@
         <v>45749</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33470,7 +33470,7 @@
         <v>45338</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>45734</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33621,7 +33621,7 @@
         <v>45804</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33694,7 +33694,7 @@
         <v>45114</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33767,7 +33767,7 @@
         <v>45877</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33840,7 +33840,7 @@
         <v>45749</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>45666</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>45729</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34059,7 +34059,7 @@
         <v>44659</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>45013</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34205,7 +34205,7 @@
         <v>45204</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34278,7 +34278,7 @@
         <v>45897</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>44971</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34424,7 +34424,7 @@
         <v>44971</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>44533</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34570,7 +34570,7 @@
         <v>46010</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34648,7 +34648,7 @@
         <v>45455</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>45091</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>45915</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>45642</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>44881</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35028,7 +35028,7 @@
         <v>45923</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>45229</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35174,7 +35174,7 @@
         <v>45873</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>45225</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35320,7 +35320,7 @@
         <v>45317</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35398,7 +35398,7 @@
         <v>45041</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>45801</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>45842</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>45146</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35690,7 +35690,7 @@
         <v>45357</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35763,7 +35763,7 @@
         <v>45842</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35836,7 +35836,7 @@
         <v>45716</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>45716</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>46133</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>45341</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36143,7 +36143,7 @@
         <v>45865</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         <v>45233</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36289,7 +36289,7 @@
         <v>45792</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36362,7 +36362,7 @@
         <v>45118</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>45169</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36508,7 +36508,7 @@
         <v>45720</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36581,7 +36581,7 @@
         <v>45273</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36654,7 +36654,7 @@
         <v>45273</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36727,7 +36727,7 @@
         <v>44887</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36800,7 +36800,7 @@
         <v>45085</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36873,7 +36873,7 @@
         <v>44882</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36946,7 +36946,7 @@
         <v>45407</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37019,7 +37019,7 @@
         <v>45154</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37092,7 +37092,7 @@
         <v>45530</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37165,7 +37165,7 @@
         <v>45012</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>45642</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37311,7 +37311,7 @@
         <v>45324</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37384,7 +37384,7 @@
         <v>44946</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37457,7 +37457,7 @@
         <v>45149</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37530,7 +37530,7 @@
         <v>46149</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37603,7 +37603,7 @@
         <v>45085</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37676,7 +37676,7 @@
         <v>45369</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>44599</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>46153</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>44757</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37973,7 +37973,7 @@
         <v>44757</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38051,7 +38051,7 @@
         <v>45001</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>45264</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>45561</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38270,7 +38270,7 @@
         <v>45604</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
         <v>45604</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38426,7 +38426,7 @@
         <v>45764</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38499,7 +38499,7 @@
         <v>46156</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>46156</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38655,7 +38655,7 @@
         <v>45747</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38728,7 +38728,7 @@
         <v>46156</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38806,7 +38806,7 @@
         <v>46156</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>46156</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38962,7 +38962,7 @@
         <v>45677</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39035,7 +39035,7 @@
         <v>45190</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>45427</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>45146</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39254,7 +39254,7 @@
         <v>44524</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39327,7 +39327,7 @@
         <v>45428</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39400,7 +39400,7 @@
         <v>46162</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39473,7 +39473,7 @@
         <v>46163</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39551,7 +39551,7 @@
         <v>45009</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39624,7 +39624,7 @@
         <v>46163</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39702,7 +39702,7 @@
         <v>45275</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39775,7 +39775,7 @@
         <v>46167</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39853,7 +39853,7 @@
         <v>45708</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>44697</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40004,7 +40004,7 @@
         <v>44897</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45607</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40150,7 +40150,7 @@
         <v>46169</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40223,7 +40223,7 @@
         <v>46106</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40301,7 +40301,7 @@
         <v>44915</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>44790</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>46174</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45454</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40603,7 +40603,7 @@
         <v>46174</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40681,7 +40681,7 @@
         <v>46174</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40759,7 +40759,7 @@
         <v>46174</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45590</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40910,7 +40910,7 @@
         <v>46174</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40988,7 +40988,7 @@
         <v>46174</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>45057</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>45610</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41212,7 +41212,7 @@
         <v>45279</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41285,7 +41285,7 @@
         <v>45349</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41358,7 +41358,7 @@
         <v>46132</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41431,7 +41431,7 @@
         <v>46177</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41509,7 +41509,7 @@
         <v>46176</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>46177</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41660,7 +41660,7 @@
         <v>46177</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41738,7 +41738,7 @@
         <v>46177</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41816,7 +41816,7 @@
         <v>46177</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>46176</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41967,7 +41967,7 @@
         <v>44552</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>45389</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>44757</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42191,7 +42191,7 @@
         <v>45404</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42264,7 +42264,7 @@
         <v>45229</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42337,7 +42337,7 @@
         <v>45165</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>46177</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>46177</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45112</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>45685</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>45208</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42785,7 +42785,7 @@
         <v>45336</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42858,7 +42858,7 @@
         <v>46177</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>45722</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43009,7 +43009,7 @@
         <v>45568</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>45391</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>46058</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43238,7 +43238,7 @@
         <v>45475</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>46181</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>46181</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>46181</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45639</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
         <v>45688</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>46183</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43754,7 +43754,7 @@
         <v>46185</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>44523</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>46185</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>45279</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>46185</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44124,7 +44124,7 @@
         <v>46185</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44197,7 +44197,7 @@
         <v>45069</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>45440</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>46027</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>45181</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>45389</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>46191</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44635,7 +44635,7 @@
         <v>45190</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44708,7 +44708,7 @@
         <v>46196</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44786,7 +44786,7 @@
         <v>45575</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44859,7 +44859,7 @@
         <v>46195</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44932,7 +44932,7 @@
         <v>45098</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45005,7 +45005,7 @@
         <v>45019</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45078,7 +45078,7 @@
         <v>46199</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>46203</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45229,7 +45229,7 @@
         <v>46203</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45307,7 +45307,7 @@
         <v>46203</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>46203</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         <v>46203</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45541,7 +45541,7 @@
         <v>46203</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45619,7 +45619,7 @@
         <v>45140</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45692,7 +45692,7 @@
         <v>46203</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45770,7 +45770,7 @@
         <v>46205</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45848,7 +45848,7 @@
         <v>46205</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>46203</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>46203</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>46203</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>46205</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>46203</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46316,7 +46316,7 @@
         <v>46203</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>46203</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46472,7 +46472,7 @@
         <v>45769</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46545,7 +46545,7 @@
         <v>46205</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46623,7 +46623,7 @@
         <v>46205</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46701,7 +46701,7 @@
         <v>46205</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46779,7 +46779,7 @@
         <v>46203</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46857,7 +46857,7 @@
         <v>46203</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46935,7 +46935,7 @@
         <v>46203</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47013,7 +47013,7 @@
         <v>46203</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>46206</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47164,7 +47164,7 @@
         <v>46206</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47237,7 +47237,7 @@
         <v>45597</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47315,7 +47315,7 @@
         <v>44496</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47388,7 +47388,7 @@
         <v>46206</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47461,7 +47461,7 @@
         <v>45155</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>46206</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47607,7 +47607,7 @@
         <v>46210</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         <v>45350</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47753,7 +47753,7 @@
         <v>45348</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>46209</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47899,7 +47899,7 @@
         <v>45434</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47972,7 +47972,7 @@
         <v>44552</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48045,7 +48045,7 @@
         <v>45629</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48123,7 +48123,7 @@
         <v>44971</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48196,7 +48196,7 @@
         <v>44757</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>45049</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48347,7 +48347,7 @@
         <v>45140</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48420,7 +48420,7 @@
         <v>45308</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48493,7 +48493,7 @@
         <v>46260</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48566,7 +48566,7 @@
         <v>46260</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48639,7 +48639,7 @@
         <v>46260</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48712,7 +48712,7 @@
         <v>46218</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48785,7 +48785,7 @@
         <v>45093</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48858,7 +48858,7 @@
         <v>45595</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>46218</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>46260</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49077,7 +49077,7 @@
         <v>45174</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49150,7 +49150,7 @@
         <v>46262</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49228,7 +49228,7 @@
         <v>46220</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49301,7 +49301,7 @@
         <v>46220</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49374,7 +49374,7 @@
         <v>45547</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>45547</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49520,7 +49520,7 @@
         <v>45355</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49593,7 +49593,7 @@
         <v>46266</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49666,7 +49666,7 @@
         <v>45615</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49739,7 +49739,7 @@
         <v>45085</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49812,7 +49812,7 @@
         <v>45113</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49885,7 +49885,7 @@
         <v>46226</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49958,7 +49958,7 @@
         <v>45351</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50031,7 +50031,7 @@
         <v>45642</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50109,7 +50109,7 @@
         <v>45706</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50182,7 +50182,7 @@
         <v>45224</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>46274</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50333,7 +50333,7 @@
         <v>45211</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50406,7 +50406,7 @@
         <v>45154</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50479,7 +50479,7 @@
         <v>46237</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50552,7 +50552,7 @@
         <v>45162</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50625,7 +50625,7 @@
         <v>45547</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50698,7 +50698,7 @@
         <v>45164</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>46237</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50849,7 +50849,7 @@
         <v>45596</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>46237</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50995,7 +50995,7 @@
         <v>45615</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>46280</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>46237</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51219,7 +51219,7 @@
         <v>46237</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45375</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51370,7 +51370,7 @@
         <v>45454</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51443,7 +51443,7 @@
         <v>44858</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51516,7 +51516,7 @@
         <v>45404</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51589,7 +51589,7 @@
         <v>46240</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         <v>45476</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51735,7 +51735,7 @@
         <v>45972</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51808,7 +51808,7 @@
         <v>46242</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>44592</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51954,7 +51954,7 @@
         <v>45546</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52027,7 +52027,7 @@
         <v>45082</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52100,7 +52100,7 @@
         <v>46287</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>46241</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52246,7 +52246,7 @@
         <v>46241</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52319,7 +52319,7 @@
         <v>46287</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>45604</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52470,7 +52470,7 @@
         <v>45604</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52548,7 +52548,7 @@
         <v>45604</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52626,7 +52626,7 @@
         <v>46241</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52699,7 +52699,7 @@
         <v>46242</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52772,7 +52772,7 @@
         <v>44838</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52845,7 +52845,7 @@
         <v>46261</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52918,7 +52918,7 @@
         <v>45204</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52991,7 +52991,7 @@
         <v>45692</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53064,7 +53064,7 @@
         <v>46242</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53137,7 +53137,7 @@
         <v>45568</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53215,7 +53215,7 @@
         <v>45091</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53293,7 +53293,7 @@
         <v>45118</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53366,7 +53366,7 @@
         <v>45005</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53439,7 +53439,7 @@
         <v>45705</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53512,7 +53512,7 @@
         <v>44994</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53585,7 +53585,7 @@
         <v>45370</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53658,7 +53658,7 @@
         <v>45434</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53731,7 +53731,7 @@
         <v>46139</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>45770</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53877,7 +53877,7 @@
         <v>45223</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53950,7 +53950,7 @@
         <v>45372</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54023,7 +54023,7 @@
         <v>45547</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54096,7 +54096,7 @@
         <v>45201</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54169,7 +54169,7 @@
         <v>45184</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54242,7 +54242,7 @@
         <v>45688</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54315,7 +54315,7 @@
         <v>45211</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54388,7 +54388,7 @@
         <v>44923</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54461,7 +54461,7 @@
         <v>45103</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54534,7 +54534,7 @@
         <v>45338</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54612,7 +54612,7 @@
         <v>44844</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54685,7 +54685,7 @@
         <v>45590</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54758,7 +54758,7 @@
         <v>46247</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54836,7 +54836,7 @@
         <v>46294</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54909,7 +54909,7 @@
         <v>46293</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54982,7 +54982,7 @@
         <v>46293</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55055,7 +55055,7 @@
         <v>46295</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55128,7 +55128,7 @@
         <v>46293</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55201,7 +55201,7 @@
         <v>46293</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55274,7 +55274,7 @@
         <v>46293</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55347,7 +55347,7 @@
         <v>45218</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55420,7 +55420,7 @@
         <v>45028</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55498,7 +55498,7 @@
         <v>46293</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55571,7 +55571,7 @@
         <v>46293</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55644,7 +55644,7 @@
         <v>46293</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55717,7 +55717,7 @@
         <v>45105</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55790,7 +55790,7 @@
         <v>46293</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55863,7 +55863,7 @@
         <v>46295</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55936,7 +55936,7 @@
         <v>45386</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56014,7 +56014,7 @@
         <v>45688</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56092,7 +56092,7 @@
         <v>46295</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56165,7 +56165,7 @@
         <v>46293</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56238,7 +56238,7 @@
         <v>46293</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56311,7 +56311,7 @@
         <v>46293</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56384,7 +56384,7 @@
         <v>45544</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56457,7 +56457,7 @@
         <v>46293</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56530,7 +56530,7 @@
         <v>46293</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56603,7 +56603,7 @@
         <v>46293</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56676,7 +56676,7 @@
         <v>45155</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56749,7 +56749,7 @@
         <v>45749</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>46253</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56900,7 +56900,7 @@
         <v>45354</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56973,7 +56973,7 @@
         <v>45243</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57046,7 +57046,7 @@
         <v>46296</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57119,7 +57119,7 @@
         <v>44844</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57192,7 +57192,7 @@
         <v>46153</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57265,7 +57265,7 @@
         <v>45459</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57338,7 +57338,7 @@
         <v>46253</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57411,7 +57411,7 @@
         <v>44908</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57489,7 +57489,7 @@
         <v>46238</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57562,7 +57562,7 @@
         <v>46253</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57635,7 +57635,7 @@
         <v>46191</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57708,7 +57708,7 @@
         <v>46253</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57781,7 +57781,7 @@
         <v>45372</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57854,7 +57854,7 @@
         <v>45196</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57927,7 +57927,7 @@
         <v>44833</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58005,7 +58005,7 @@
         <v>45244</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58078,7 +58078,7 @@
         <v>45063</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58151,7 +58151,7 @@
         <v>45245</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58224,7 +58224,7 @@
         <v>45692</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58297,7 +58297,7 @@
         <v>45260</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58370,7 +58370,7 @@
         <v>44592</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58443,7 +58443,7 @@
         <v>44593</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58516,7 +58516,7 @@
         <v>45230</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58594,7 +58594,7 @@
         <v>45075</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58667,7 +58667,7 @@
         <v>44939</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58740,7 +58740,7 @@
         <v>45692</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58813,7 +58813,7 @@
         <v>45702</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58886,7 +58886,7 @@
         <v>45338</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58964,7 +58964,7 @@
         <v>44937</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59037,7 +59037,7 @@
         <v>44937</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59110,7 +59110,7 @@
         <v>45195</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59183,7 +59183,7 @@
         <v>45146</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59256,7 +59256,7 @@
         <v>45146</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59329,7 +59329,7 @@
         <v>45460</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59402,7 +59402,7 @@
         <v>45561</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59475,7 +59475,7 @@
         <v>45764</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59553,7 +59553,7 @@
         <v>44593</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59626,7 +59626,7 @@
         <v>45181</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59704,7 +59704,7 @@
         <v>45279</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59777,7 +59777,7 @@
         <v>45153</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59850,7 +59850,7 @@
         <v>45244</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59923,7 +59923,7 @@
         <v>45154</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59996,7 +59996,7 @@
         <v>44998</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60089,7 +60089,7 @@
         <v>45057</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60162,7 +60162,7 @@
         <v>45427</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60235,7 +60235,7 @@
         <v>44610</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60308,7 +60308,7 @@
         <v>45649</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60381,7 +60381,7 @@
         <v>44998</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60459,7 +60459,7 @@
         <v>44496</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60532,7 +60532,7 @@
         <v>45600</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60605,7 +60605,7 @@
         <v>45601</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60678,7 +60678,7 @@
         <v>45273</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60751,7 +60751,7 @@
         <v>45391</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60824,7 +60824,7 @@
         <v>45516</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60897,7 +60897,7 @@
         <v>44526</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60975,7 +60975,7 @@
         <v>45476</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61048,7 +61048,7 @@
         <v>45502</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61126,7 +61126,7 @@
         <v>44489</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61204,7 +61204,7 @@
         <v>44726</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61277,7 +61277,7 @@
         <v>44916</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61350,7 +61350,7 @@
         <v>45161</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61428,7 +61428,7 @@
         <v>45476</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61501,7 +61501,7 @@
         <v>44963</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61574,7 +61574,7 @@
         <v>44916</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61647,7 +61647,7 @@
         <v>45140</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61720,7 +61720,7 @@
         <v>44837</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61793,7 +61793,7 @@
         <v>45161</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61871,7 +61871,7 @@
         <v>44893</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61944,7 +61944,7 @@
         <v>44916</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62017,7 +62017,7 @@
         <v>44726</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62090,7 +62090,7 @@
         <v>45411</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62163,7 +62163,7 @@
         <v>45791</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62236,7 +62236,7 @@
         <v>45910</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62309,7 +62309,7 @@
         <v>46030</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62382,7 +62382,7 @@
         <v>46051</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62455,7 +62455,7 @@
         <v>46275</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62528,7 +62528,7 @@
         <v>46280</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>

--- a/Översikt UPPVIDINGE.xlsx
+++ b/Översikt UPPVIDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45174</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>44972</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>44972</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45442</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45789</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>46119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>46183</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>44980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>46183</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>44607</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45789</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>46119</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>46149</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>46119</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>45995</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44859</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>46066</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>46276</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>46183</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>45366</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>45313</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44972</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>46066</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>45158</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>44939</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>45840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>45604</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>45195</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>46247</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>45450</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>44979</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>44833</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>45517</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45404</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>45688</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>45604</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>46051</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>44937</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>45205</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>45103</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>45320</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>46169</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>45604</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>46205</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>46218</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>45117</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>45568</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>46297</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>44972</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>44972</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44484</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>45789</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>44734</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44827</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>44690</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>44788</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>45534</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>46051</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>45939</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>45623</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44858</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>44984</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>44663</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>46100</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>45981</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>45820</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>45825</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>45826</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>44757</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>45840</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>45982</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>44676</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>46154</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>44550</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>45320</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>46185</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>45897</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>44858</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>45105</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>45435</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>45688</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>46247</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>46247</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>46247</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>46162</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         <v>44950</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>46255</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         <v>44998</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
         <v>45517</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>45440</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>44972</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>45810</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>44865</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>44887</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>44887</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>44524</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>44613</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>44483</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>44487</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>44552</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>44536</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>44574</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>44510</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>44812</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>44859</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>44574</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>44859</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         <v>44676</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>44859</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>44859</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>44749</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>44574</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>44602</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>44580</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>44602</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>44859</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>44795</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>44757</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>44887</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>44588</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>44845</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>44552</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44483</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44483</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>44475</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>44503</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>44510</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>44803</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>44887</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>44609</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>44610</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>44795</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>44795</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>44582</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>44601</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>44858</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>44711</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>44522</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>44837</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
         <v>44859</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>44887</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14973,7 +14973,7 @@
         <v>44887</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>44490</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>44676</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>44607</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>44607</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>44475</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>44574</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>44603</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>44602</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>44524</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>44721</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>44683</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>44686</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>44729</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>44705</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>44602</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>44592</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>45736</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45674</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>45338</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>45338</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>45338</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>45338</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>45156</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>45098</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>45770</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>44524</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>45181</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>44922</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>45229</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>45389</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>44610</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>45089</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>45697</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>45385</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>44789</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         <v>45389</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>45398</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>45384</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45428</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45428</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>45118</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>45338</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45488</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>45590</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>45664</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>45786</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>45604</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45552</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>45742</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>45668</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>45320</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>45348</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>45714</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>46002</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>46002</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>45471</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>46007</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>45887</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>44497</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>45544</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>44942</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>45408</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>46013</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>46013</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>44902</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>45226</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>45229</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>46029</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>44757</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>45894</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>46029</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>45745</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>45223</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>46034</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45901</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>45901</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>46033</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>45428</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>45840</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20873,7 +20873,7 @@
         <v>45567</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>46040</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>45838</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>45910</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>45233</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>46041</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>45910</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>44524</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>45910</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21535,7 +21535,7 @@
         <v>45910</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>45245</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>45153</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>45720</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21827,7 +21827,7 @@
         <v>46048</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>46048</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21973,7 +21973,7 @@
         <v>46050</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>45801</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22124,7 +22124,7 @@
         <v>46050</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45801</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>44985</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45800</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>45804</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>45273</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45805</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>46052</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>45804</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>45764</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>45807</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>46052</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>46052</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>46052</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>45923</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>45923</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
         <v>46052</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>46052</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23473,7 +23473,7 @@
         <v>44566</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>46057</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>46058</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23692,7 +23692,7 @@
         <v>46058</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>45278</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23843,7 +23843,7 @@
         <v>45933</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>45348</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>45934</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24062,7 +24062,7 @@
         <v>45934</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>46069</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>45934</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>45041</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24359,7 +24359,7 @@
         <v>45041</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>44924</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>46071</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>46071</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>45469</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         <v>46071</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>46071</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>45940</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>45440</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>45622</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>44924</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25162,7 +25162,7 @@
         <v>45174</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         <v>45957</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>45757</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25386,7 +25386,7 @@
         <v>46086</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>44984</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>45459</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>45428</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>45369</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>45082</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>45960</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25902,7 +25902,7 @@
         <v>45085</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25975,7 +25975,7 @@
         <v>45960</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>44945</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>45230</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>46093</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>46093</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>46093</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>46093</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>46093</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>46093</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>46093</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>45636</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>44734</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>44734</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>45968</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>45583</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>45336</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>44942</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27261,7 +27261,7 @@
         <v>44942</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>45230</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>45973</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>46106</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>45107</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>46106</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27714,7 +27714,7 @@
         <v>45818</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>45981</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27865,7 +27865,7 @@
         <v>45777</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>45981</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>45981</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>45819</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28177,7 +28177,7 @@
         <v>45819</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28250,7 +28250,7 @@
         <v>44951</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>45770</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>45985</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>45985</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28542,7 +28542,7 @@
         <v>45985</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>46114</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>46114</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28771,7 +28771,7 @@
         <v>45547</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>45547</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>46114</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28995,7 +28995,7 @@
         <v>45941</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         <v>46114</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>46114</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29229,7 +29229,7 @@
         <v>46114</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>45688</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>45644</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29458,7 +29458,7 @@
         <v>45989</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29531,7 +29531,7 @@
         <v>45941</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>45093</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>45597</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>45989</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>44917</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>45988</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29979,7 +29979,7 @@
         <v>45973</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>45428</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30125,7 +30125,7 @@
         <v>45428</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30198,7 +30198,7 @@
         <v>46122</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30271,7 +30271,7 @@
         <v>45428</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30344,7 +30344,7 @@
         <v>45960</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>45716</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30500,7 +30500,7 @@
         <v>45960</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30578,7 +30578,7 @@
         <v>45995</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30651,7 +30651,7 @@
         <v>45826</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30724,7 +30724,7 @@
         <v>45995</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30797,7 +30797,7 @@
         <v>44984</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30870,7 +30870,7 @@
         <v>45995</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>45995</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45999</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>45826</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>44638</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>44865</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>45826</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>46000</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>46000</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>44603</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>46132</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>44503</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>46132</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>45637</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>45028</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>45552</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32043,7 +32043,7 @@
         <v>44994</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>45232</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32189,7 +32189,7 @@
         <v>46135</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32262,7 +32262,7 @@
         <v>45219</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>45824</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32408,7 +32408,7 @@
         <v>45338</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32486,7 +32486,7 @@
         <v>45338</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32564,7 +32564,7 @@
         <v>45474</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>45288</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32715,7 +32715,7 @@
         <v>45842</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32788,7 +32788,7 @@
         <v>46139</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>45230</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         <v>45428</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33012,7 +33012,7 @@
         <v>45295</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
         <v>45747</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33168,7 +33168,7 @@
         <v>45597</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>45973</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>44711</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33392,7 +33392,7 @@
         <v>45749</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33470,7 +33470,7 @@
         <v>45338</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>45734</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33621,7 +33621,7 @@
         <v>45804</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33694,7 +33694,7 @@
         <v>45114</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33767,7 +33767,7 @@
         <v>45877</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33840,7 +33840,7 @@
         <v>45749</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>45666</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>45729</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34059,7 +34059,7 @@
         <v>44659</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>45013</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34205,7 +34205,7 @@
         <v>45204</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34278,7 +34278,7 @@
         <v>45897</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>44971</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34424,7 +34424,7 @@
         <v>44971</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>44533</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34570,7 +34570,7 @@
         <v>46010</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34648,7 +34648,7 @@
         <v>45455</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>45091</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>45915</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>45642</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>44881</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35028,7 +35028,7 @@
         <v>45923</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>45229</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35174,7 +35174,7 @@
         <v>45873</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>45225</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35320,7 +35320,7 @@
         <v>45317</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35398,7 +35398,7 @@
         <v>45041</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>45801</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>45842</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>45146</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35690,7 +35690,7 @@
         <v>45357</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35763,7 +35763,7 @@
         <v>45842</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35836,7 +35836,7 @@
         <v>45716</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>45716</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>46133</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>45341</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36143,7 +36143,7 @@
         <v>45865</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         <v>45233</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36289,7 +36289,7 @@
         <v>45792</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36362,7 +36362,7 @@
         <v>45118</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>45169</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36508,7 +36508,7 @@
         <v>45720</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36581,7 +36581,7 @@
         <v>45273</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36654,7 +36654,7 @@
         <v>45273</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36727,7 +36727,7 @@
         <v>44887</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36800,7 +36800,7 @@
         <v>45085</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36873,7 +36873,7 @@
         <v>44882</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36946,7 +36946,7 @@
         <v>45407</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37019,7 +37019,7 @@
         <v>45154</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37092,7 +37092,7 @@
         <v>45530</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37165,7 +37165,7 @@
         <v>45012</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>45642</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37311,7 +37311,7 @@
         <v>45324</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37384,7 +37384,7 @@
         <v>44946</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37457,7 +37457,7 @@
         <v>45149</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37530,7 +37530,7 @@
         <v>46149</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37603,7 +37603,7 @@
         <v>45085</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37676,7 +37676,7 @@
         <v>45369</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>44599</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>46153</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>44757</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37973,7 +37973,7 @@
         <v>44757</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38051,7 +38051,7 @@
         <v>45001</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>45264</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>45561</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38270,7 +38270,7 @@
         <v>45604</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
         <v>45604</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38426,7 +38426,7 @@
         <v>45764</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38499,7 +38499,7 @@
         <v>46156</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>46156</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38655,7 +38655,7 @@
         <v>45747</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38728,7 +38728,7 @@
         <v>46156</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38806,7 +38806,7 @@
         <v>46156</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>46156</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38962,7 +38962,7 @@
         <v>45677</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39035,7 +39035,7 @@
         <v>45190</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>45427</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>45146</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39254,7 +39254,7 @@
         <v>44524</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39327,7 +39327,7 @@
         <v>45428</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39400,7 +39400,7 @@
         <v>46162</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39473,7 +39473,7 @@
         <v>46163</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39551,7 +39551,7 @@
         <v>45009</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39624,7 +39624,7 @@
         <v>46163</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39702,7 +39702,7 @@
         <v>45275</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39775,7 +39775,7 @@
         <v>46167</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39853,7 +39853,7 @@
         <v>45708</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>44697</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40004,7 +40004,7 @@
         <v>44897</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45607</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40150,7 +40150,7 @@
         <v>46169</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40223,7 +40223,7 @@
         <v>46106</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40301,7 +40301,7 @@
         <v>44915</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>44790</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>46174</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45454</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40603,7 +40603,7 @@
         <v>46174</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40681,7 +40681,7 @@
         <v>46174</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40759,7 +40759,7 @@
         <v>46174</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45590</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40910,7 +40910,7 @@
         <v>46174</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40988,7 +40988,7 @@
         <v>46174</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>45057</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>45610</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41212,7 +41212,7 @@
         <v>45279</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41285,7 +41285,7 @@
         <v>45349</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41358,7 +41358,7 @@
         <v>46132</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41431,7 +41431,7 @@
         <v>46177</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41509,7 +41509,7 @@
         <v>46176</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>46177</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41660,7 +41660,7 @@
         <v>46177</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41738,7 +41738,7 @@
         <v>46177</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41816,7 +41816,7 @@
         <v>46177</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>46176</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41967,7 +41967,7 @@
         <v>44552</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>45389</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>44757</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42191,7 +42191,7 @@
         <v>45404</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42264,7 +42264,7 @@
         <v>45229</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42337,7 +42337,7 @@
         <v>45165</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>46177</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>46177</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45112</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>45685</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>45208</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42785,7 +42785,7 @@
         <v>45336</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42858,7 +42858,7 @@
         <v>46177</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>45722</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43009,7 +43009,7 @@
         <v>45568</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>45391</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>46058</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43238,7 +43238,7 @@
         <v>45475</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>46181</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>46181</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>46181</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45639</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
         <v>45688</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>46183</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43754,7 +43754,7 @@
         <v>46185</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>44523</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>46185</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>45279</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>46185</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44124,7 +44124,7 @@
         <v>46185</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44197,7 +44197,7 @@
         <v>45069</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>45440</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>46027</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>45181</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>45389</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>46191</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44635,7 +44635,7 @@
         <v>45190</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44708,7 +44708,7 @@
         <v>46196</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44786,7 +44786,7 @@
         <v>45575</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44859,7 +44859,7 @@
         <v>46195</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44932,7 +44932,7 @@
         <v>45098</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45005,7 +45005,7 @@
         <v>45019</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45078,7 +45078,7 @@
         <v>46199</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>46203</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45229,7 +45229,7 @@
         <v>46203</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45307,7 +45307,7 @@
         <v>46203</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>46203</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         <v>46203</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45541,7 +45541,7 @@
         <v>46203</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45619,7 +45619,7 @@
         <v>45140</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45692,7 +45692,7 @@
         <v>46203</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45770,7 +45770,7 @@
         <v>46205</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45848,7 +45848,7 @@
         <v>46205</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>46203</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>46203</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>46203</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>46205</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>46203</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46316,7 +46316,7 @@
         <v>46203</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>46203</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46472,7 +46472,7 @@
         <v>45769</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46545,7 +46545,7 @@
         <v>46205</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46623,7 +46623,7 @@
         <v>46205</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46701,7 +46701,7 @@
         <v>46205</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46779,7 +46779,7 @@
         <v>46203</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46857,7 +46857,7 @@
         <v>46203</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46935,7 +46935,7 @@
         <v>46203</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47013,7 +47013,7 @@
         <v>46203</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>46206</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47164,7 +47164,7 @@
         <v>46206</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47237,7 +47237,7 @@
         <v>45597</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47315,7 +47315,7 @@
         <v>44496</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47388,7 +47388,7 @@
         <v>46206</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47461,7 +47461,7 @@
         <v>45155</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>46206</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47607,7 +47607,7 @@
         <v>46210</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         <v>45350</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47753,7 +47753,7 @@
         <v>45348</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>46209</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47899,7 +47899,7 @@
         <v>45434</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47972,7 +47972,7 @@
         <v>44552</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48045,7 +48045,7 @@
         <v>45629</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48123,7 +48123,7 @@
         <v>44971</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48196,7 +48196,7 @@
         <v>44757</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>45049</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48347,7 +48347,7 @@
         <v>45140</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48420,7 +48420,7 @@
         <v>45308</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48493,7 +48493,7 @@
         <v>46260</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48566,7 +48566,7 @@
         <v>46260</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48639,7 +48639,7 @@
         <v>46260</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48712,7 +48712,7 @@
         <v>46218</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48785,7 +48785,7 @@
         <v>45093</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48858,7 +48858,7 @@
         <v>45595</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>46218</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>46260</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49077,7 +49077,7 @@
         <v>45174</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49150,7 +49150,7 @@
         <v>46262</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49228,7 +49228,7 @@
         <v>46220</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49301,7 +49301,7 @@
         <v>46220</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49374,7 +49374,7 @@
         <v>45547</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49447,7 +49447,7 @@
         <v>45547</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49520,7 +49520,7 @@
         <v>45355</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49593,7 +49593,7 @@
         <v>46266</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49666,7 +49666,7 @@
         <v>45615</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49739,7 +49739,7 @@
         <v>45085</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49812,7 +49812,7 @@
         <v>45113</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49885,7 +49885,7 @@
         <v>46226</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49958,7 +49958,7 @@
         <v>45351</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50031,7 +50031,7 @@
         <v>45642</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50109,7 +50109,7 @@
         <v>45706</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50182,7 +50182,7 @@
         <v>45224</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>46274</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50333,7 +50333,7 @@
         <v>45211</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50406,7 +50406,7 @@
         <v>45154</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50479,7 +50479,7 @@
         <v>46237</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50552,7 +50552,7 @@
         <v>45162</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50625,7 +50625,7 @@
         <v>45547</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50698,7 +50698,7 @@
         <v>45164</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>46237</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50849,7 +50849,7 @@
         <v>45596</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>46237</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50995,7 +50995,7 @@
         <v>45615</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>46280</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>46237</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51219,7 +51219,7 @@
         <v>46237</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45375</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51370,7 +51370,7 @@
         <v>45454</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51443,7 +51443,7 @@
         <v>44858</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51516,7 +51516,7 @@
         <v>45404</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51589,7 +51589,7 @@
         <v>46240</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         <v>45476</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51735,7 +51735,7 @@
         <v>45972</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51808,7 +51808,7 @@
         <v>46242</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>44592</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51954,7 +51954,7 @@
         <v>45546</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52027,7 +52027,7 @@
         <v>45082</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52100,7 +52100,7 @@
         <v>46287</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>46241</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52246,7 +52246,7 @@
         <v>46241</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52319,7 +52319,7 @@
         <v>46287</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>45604</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52470,7 +52470,7 @@
         <v>45604</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52548,7 +52548,7 @@
         <v>45604</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52626,7 +52626,7 @@
         <v>46241</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52699,7 +52699,7 @@
         <v>46242</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52772,7 +52772,7 @@
         <v>44838</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52845,7 +52845,7 @@
         <v>46261</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52918,7 +52918,7 @@
         <v>45204</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52991,7 +52991,7 @@
         <v>45692</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53064,7 +53064,7 @@
         <v>46242</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53137,7 +53137,7 @@
         <v>45568</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53215,7 +53215,7 @@
         <v>45091</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53293,7 +53293,7 @@
         <v>45118</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53366,7 +53366,7 @@
         <v>45005</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53439,7 +53439,7 @@
         <v>45705</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53512,7 +53512,7 @@
         <v>44994</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53585,7 +53585,7 @@
         <v>45370</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53658,7 +53658,7 @@
         <v>45434</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53731,7 +53731,7 @@
         <v>46139</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>45770</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53877,7 +53877,7 @@
         <v>45223</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53950,7 +53950,7 @@
         <v>45372</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54023,7 +54023,7 @@
         <v>45547</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54096,7 +54096,7 @@
         <v>45201</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54169,7 +54169,7 @@
         <v>45184</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54242,7 +54242,7 @@
         <v>45688</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54315,7 +54315,7 @@
         <v>45211</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54388,7 +54388,7 @@
         <v>44923</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54461,7 +54461,7 @@
         <v>45103</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54534,7 +54534,7 @@
         <v>45338</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54612,7 +54612,7 @@
         <v>44844</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54685,7 +54685,7 @@
         <v>45590</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54758,7 +54758,7 @@
         <v>46247</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54836,7 +54836,7 @@
         <v>46294</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54909,7 +54909,7 @@
         <v>46293</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54982,7 +54982,7 @@
         <v>46293</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55055,7 +55055,7 @@
         <v>46295</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55128,7 +55128,7 @@
         <v>46293</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55201,7 +55201,7 @@
         <v>46293</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55274,7 +55274,7 @@
         <v>46293</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55347,7 +55347,7 @@
         <v>45218</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55420,7 +55420,7 @@
         <v>45028</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55498,7 +55498,7 @@
         <v>46293</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55571,7 +55571,7 @@
         <v>46293</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55644,7 +55644,7 @@
         <v>46293</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55717,7 +55717,7 @@
         <v>45105</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55790,7 +55790,7 @@
         <v>46293</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55863,7 +55863,7 @@
         <v>46295</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55936,7 +55936,7 @@
         <v>45386</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56014,7 +56014,7 @@
         <v>45688</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56092,7 +56092,7 @@
         <v>46295</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56165,7 +56165,7 @@
         <v>46293</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56238,7 +56238,7 @@
         <v>46293</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56311,7 +56311,7 @@
         <v>46293</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56384,7 +56384,7 @@
         <v>45544</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56457,7 +56457,7 @@
         <v>46293</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56530,7 +56530,7 @@
         <v>46293</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56603,7 +56603,7 @@
         <v>46293</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56676,7 +56676,7 @@
         <v>45155</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56749,7 +56749,7 @@
         <v>45749</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>46253</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56900,7 +56900,7 @@
         <v>45354</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56973,7 +56973,7 @@
         <v>45243</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57046,7 +57046,7 @@
         <v>46296</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57119,7 +57119,7 @@
         <v>44844</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57192,7 +57192,7 @@
         <v>46153</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57265,7 +57265,7 @@
         <v>45459</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57338,7 +57338,7 @@
         <v>46253</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57411,7 +57411,7 @@
         <v>44908</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57489,7 +57489,7 @@
         <v>46238</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57562,7 +57562,7 @@
         <v>46253</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57635,7 +57635,7 @@
         <v>46191</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57708,7 +57708,7 @@
         <v>46253</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57781,7 +57781,7 @@
         <v>45372</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57854,7 +57854,7 @@
         <v>45196</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57927,7 +57927,7 @@
         <v>44833</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58005,7 +58005,7 @@
         <v>45244</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58078,7 +58078,7 @@
         <v>45063</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58151,7 +58151,7 @@
         <v>45245</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58224,7 +58224,7 @@
         <v>45692</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58297,7 +58297,7 @@
         <v>45260</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58370,7 +58370,7 @@
         <v>44592</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58443,7 +58443,7 @@
         <v>44593</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58516,7 +58516,7 @@
         <v>45230</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58594,7 +58594,7 @@
         <v>45075</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58667,7 +58667,7 @@
         <v>44939</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58740,7 +58740,7 @@
         <v>45692</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58813,7 +58813,7 @@
         <v>45702</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58886,7 +58886,7 @@
         <v>45338</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58964,7 +58964,7 @@
         <v>44937</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59037,7 +59037,7 @@
         <v>44937</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59110,7 +59110,7 @@
         <v>45195</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59183,7 +59183,7 @@
         <v>45146</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59256,7 +59256,7 @@
         <v>45146</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59329,7 +59329,7 @@
         <v>45460</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59402,7 +59402,7 @@
         <v>45561</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59475,7 +59475,7 @@
         <v>45764</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59553,7 +59553,7 @@
         <v>44593</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59626,7 +59626,7 @@
         <v>45181</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59704,7 +59704,7 @@
         <v>45279</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59777,7 +59777,7 @@
         <v>45153</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59850,7 +59850,7 @@
         <v>45244</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59923,7 +59923,7 @@
         <v>45154</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59996,7 +59996,7 @@
         <v>44998</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60089,7 +60089,7 @@
         <v>45057</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60162,7 +60162,7 @@
         <v>45427</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60235,7 +60235,7 @@
         <v>44610</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60308,7 +60308,7 @@
         <v>45649</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60381,7 +60381,7 @@
         <v>44998</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60459,7 +60459,7 @@
         <v>44496</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60532,7 +60532,7 @@
         <v>45600</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60605,7 +60605,7 @@
         <v>45601</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60678,7 +60678,7 @@
         <v>45273</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60751,7 +60751,7 @@
         <v>45391</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60824,7 +60824,7 @@
         <v>45516</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60897,7 +60897,7 @@
         <v>44526</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60975,7 +60975,7 @@
         <v>45476</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61048,7 +61048,7 @@
         <v>45502</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61126,7 +61126,7 @@
         <v>44489</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61204,7 +61204,7 @@
         <v>44726</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61277,7 +61277,7 @@
         <v>44916</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61350,7 +61350,7 @@
         <v>45161</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61428,7 +61428,7 @@
         <v>45476</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61501,7 +61501,7 @@
         <v>44963</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61574,7 +61574,7 @@
         <v>44916</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61647,7 +61647,7 @@
         <v>45140</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61720,7 +61720,7 @@
         <v>44837</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61793,7 +61793,7 @@
         <v>45161</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61871,7 +61871,7 @@
         <v>44893</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61944,7 +61944,7 @@
         <v>44916</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62017,7 +62017,7 @@
         <v>44726</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62090,7 +62090,7 @@
         <v>45411</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62163,7 +62163,7 @@
         <v>45791</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62236,7 +62236,7 @@
         <v>45910</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62309,7 +62309,7 @@
         <v>46030</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62382,7 +62382,7 @@
         <v>46051</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62455,7 +62455,7 @@
         <v>46275</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62528,7 +62528,7 @@
         <v>46280</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>

--- a/Översikt UPPVIDINGE.xlsx
+++ b/Översikt UPPVIDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45174</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>44972</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>44972</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45442</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45789</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>46119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>46183</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>44980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>46183</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>44607</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45789</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>46119</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>46149</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>46119</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>45995</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44859</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>46066</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>46276</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>46183</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>45313</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>45366</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44972</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>45158</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>44939</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>46066</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>45195</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>45450</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>45604</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>45840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>46247</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>44979</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>45568</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>45604</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>44833</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>45517</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>45404</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>45117</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>45604</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>45205</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>44937</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>45320</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>45103</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>46051</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>46169</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>46205</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>46218</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>46297</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>44972</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44972</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>44484</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>45789</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>44734</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>44690</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>44827</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>44788</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>45105</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         <v>44950</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>45320</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>44550</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>45517</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>44984</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>45435</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>45623</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>45534</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>44858</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>44998</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>45939</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>44663</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>45820</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>45826</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>45825</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>45840</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>44757</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>45981</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>46100</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>44858</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>45982</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>44676</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>46154</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>46185</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>45897</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>45688</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>46162</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>46247</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>46247</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>46247</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>46255</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>45440</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>44972</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>45810</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>46300</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>44865</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>44887</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>44887</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>44524</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>44483</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>44613</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>44487</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>44574</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44552</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>44536</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>44510</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>44812</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>44859</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>44574</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>44859</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>44676</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>44859</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>44859</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>44749</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>44574</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>44602</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>44580</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>44602</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>44859</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>44795</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>44757</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>44887</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>44588</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>44845</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>44582</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>44676</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>44552</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>44574</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>44503</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13777,7 +13777,7 @@
         <v>44483</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13850,7 +13850,7 @@
         <v>44837</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>44483</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>44603</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>44602</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>44859</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>44510</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14288,7 +14288,7 @@
         <v>44524</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
         <v>44721</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
         <v>44601</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>44683</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14580,7 +14580,7 @@
         <v>44686</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14653,7 +14653,7 @@
         <v>44858</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>44803</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
         <v>44887</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>44610</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14945,7 +14945,7 @@
         <v>44609</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15018,7 +15018,7 @@
         <v>44607</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15091,7 +15091,7 @@
         <v>44607</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>44711</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
         <v>44887</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>44887</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>44490</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>44795</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>44795</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>44522</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>44729</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>44705</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>44602</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>44998</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>44592</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>44882</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         <v>45428</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16211,7 +16211,7 @@
         <v>44971</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>45705</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         <v>45082</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>45454</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         <v>45118</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>45091</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>45190</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>45338</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>45338</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>45181</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>45407</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>45385</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>44937</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>44937</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45341</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>44593</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>45105</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>44917</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>45547</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>45164</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45547</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44838</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>45697</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>45041</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45041</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>44757</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18144,7 +18144,7 @@
         <v>44757</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>45093</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>45596</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>45615</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>45244</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>45716</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>45749</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>45590</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>45471</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>45338</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>45338</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45338</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45369</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>45389</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         <v>45005</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>44524</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>45098</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>44503</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>45348</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>45348</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>45140</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>45001</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>45440</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>45391</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>45590</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>44833</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>45604</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
         <v>45604</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>45604</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>45685</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>45190</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>45082</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>45708</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>44496</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>45692</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>45386</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>45561</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>45204</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>44757</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>45229</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>45279</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>45229</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>45091</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45085</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>44552</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45568</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>45140</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>45208</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>45279</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>44790</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21869,7 +21869,7 @@
         <v>44994</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>44610</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>44497</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>44942</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>45349</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>44902</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>45112</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>45887</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>45154</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>44789</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>45389</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>45454</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>45085</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>45427</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>45348</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
         <v>45544</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23037,7 +23037,7 @@
         <v>45428</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>45338</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>45338</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>44998</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>45716</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>45019</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         <v>45103</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>45428</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         <v>45428</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>45428</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
         <v>45894</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>45544</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>45901</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>45642</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>45714</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>45575</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>45840</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>45057</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>45154</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>45428</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45567</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>45722</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>45434</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>45336</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24809,7 +24809,7 @@
         <v>45229</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24882,7 +24882,7 @@
         <v>45428</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>44734</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>44734</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>45165</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>45901</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>45245</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>45181</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25393,7 +25393,7 @@
         <v>45089</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>45469</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>45639</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>45428</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45428</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>45384</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>44592</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25904,7 +25904,7 @@
         <v>45910</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25977,7 +25977,7 @@
         <v>45910</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26050,7 +26050,7 @@
         <v>45910</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>45838</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26196,7 +26196,7 @@
         <v>45391</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26269,7 +26269,7 @@
         <v>45600</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26342,7 +26342,7 @@
         <v>45153</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>45273</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26488,7 +26488,7 @@
         <v>45601</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>45516</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>45910</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>44526</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         <v>45530</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26858,7 +26858,7 @@
         <v>45674</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>45720</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>45049</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>45229</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>44599</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27228,7 +27228,7 @@
         <v>45476</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27301,7 +27301,7 @@
         <v>45389</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>45098</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>45502</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>45604</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
         <v>45604</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>45162</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27754,7 +27754,7 @@
         <v>45742</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>45154</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>45476</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27973,7 +27973,7 @@
         <v>44524</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28051,7 +28051,7 @@
         <v>44524</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28124,7 +28124,7 @@
         <v>45786</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
         <v>45146</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28270,7 +28270,7 @@
         <v>45552</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28343,7 +28343,7 @@
         <v>45552</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28416,7 +28416,7 @@
         <v>45923</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>45923</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28562,7 +28562,7 @@
         <v>45590</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         <v>45604</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28708,7 +28708,7 @@
         <v>45747</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28781,7 +28781,7 @@
         <v>45118</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28854,7 +28854,7 @@
         <v>45355</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28927,7 +28927,7 @@
         <v>45013</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29000,7 +29000,7 @@
         <v>45370</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         <v>44942</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>45692</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29219,7 +29219,7 @@
         <v>45610</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>45233</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29365,7 +29365,7 @@
         <v>45211</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29438,7 +29438,7 @@
         <v>45146</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>45649</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29584,7 +29584,7 @@
         <v>44942</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29657,7 +29657,7 @@
         <v>45320</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>44659</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29803,7 +29803,7 @@
         <v>44592</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>45688</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>45688</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>45408</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>45338</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>45338</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>44985</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>44610</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>45404</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30480,7 +30480,7 @@
         <v>45934</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30553,7 +30553,7 @@
         <v>45934</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>45933</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>45702</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30772,7 +30772,7 @@
         <v>45720</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30845,7 +30845,7 @@
         <v>45642</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30923,7 +30923,7 @@
         <v>45389</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30996,7 +30996,7 @@
         <v>45597</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>45934</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>45801</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31220,7 +31220,7 @@
         <v>44844</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>45804</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31366,7 +31366,7 @@
         <v>45372</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31439,7 +31439,7 @@
         <v>45804</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31512,7 +31512,7 @@
         <v>45801</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31585,7 +31585,7 @@
         <v>45440</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31658,7 +31658,7 @@
         <v>45223</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>45764</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31809,7 +31809,7 @@
         <v>44945</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31882,7 +31882,7 @@
         <v>45169</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>45218</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32028,7 +32028,7 @@
         <v>45729</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32101,7 +32101,7 @@
         <v>45063</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32174,7 +32174,7 @@
         <v>45372</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32247,7 +32247,7 @@
         <v>44593</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>45196</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32393,7 +32393,7 @@
         <v>45770</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32466,7 +32466,7 @@
         <v>45807</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32539,7 +32539,7 @@
         <v>45404</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32612,7 +32612,7 @@
         <v>45770</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>45940</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32758,7 +32758,7 @@
         <v>45547</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32831,7 +32831,7 @@
         <v>45223</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32904,7 +32904,7 @@
         <v>44566</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>45664</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33050,7 +33050,7 @@
         <v>45057</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33123,7 +33123,7 @@
         <v>45278</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33196,7 +33196,7 @@
         <v>45777</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33274,7 +33274,7 @@
         <v>45211</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33347,7 +33347,7 @@
         <v>45009</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
         <v>45688</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>44923</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>45629</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33649,7 +33649,7 @@
         <v>45818</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>45107</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33795,7 +33795,7 @@
         <v>45195</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>45819</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33946,7 +33946,7 @@
         <v>45819</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34019,7 +34019,7 @@
         <v>45273</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34092,7 +34092,7 @@
         <v>45757</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34170,7 +34170,7 @@
         <v>45644</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34243,7 +34243,7 @@
         <v>45826</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34316,7 +34316,7 @@
         <v>45826</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34389,7 +34389,7 @@
         <v>45093</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>45184</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>45826</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34608,7 +34608,7 @@
         <v>45085</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34681,7 +34681,7 @@
         <v>45317</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34759,7 +34759,7 @@
         <v>44984</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34832,7 +34832,7 @@
         <v>45459</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>44984</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>44971</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35051,7 +35051,7 @@
         <v>45075</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>45153</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35197,7 +35197,7 @@
         <v>45174</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>45957</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>44496</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>45960</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>45960</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>44971</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>45230</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>45354</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35796,7 +35796,7 @@
         <v>45460</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35869,7 +35869,7 @@
         <v>45041</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35942,7 +35942,7 @@
         <v>45295</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>44757</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36098,7 +36098,7 @@
         <v>45547</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36171,7 +36171,7 @@
         <v>44523</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36244,7 +36244,7 @@
         <v>45475</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36317,7 +36317,7 @@
         <v>45230</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36395,7 +36395,7 @@
         <v>45769</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>45181</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36541,7 +36541,7 @@
         <v>45968</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>45357</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>45114</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>45615</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36833,7 +36833,7 @@
         <v>45155</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36906,7 +36906,7 @@
         <v>45243</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>44915</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>45973</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37125,7 +37125,7 @@
         <v>45118</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37198,7 +37198,7 @@
         <v>45336</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>45201</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37344,7 +37344,7 @@
         <v>45842</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37417,7 +37417,7 @@
         <v>45028</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37495,7 +37495,7 @@
         <v>44858</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>45792</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37641,7 +37641,7 @@
         <v>45865</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37714,7 +37714,7 @@
         <v>45692</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37787,7 +37787,7 @@
         <v>44924</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37860,7 +37860,7 @@
         <v>45230</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>45351</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38011,7 +38011,7 @@
         <v>45264</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>45637</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38157,7 +38157,7 @@
         <v>44939</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38230,7 +38230,7 @@
         <v>45224</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>44757</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>45324</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38459,7 +38459,7 @@
         <v>45981</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38537,7 +38537,7 @@
         <v>45279</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38610,7 +38610,7 @@
         <v>45155</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38683,7 +38683,7 @@
         <v>45981</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>45273</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>45273</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38907,7 +38907,7 @@
         <v>44603</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>45622</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>45233</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39126,7 +39126,7 @@
         <v>45981</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39204,7 +39204,7 @@
         <v>45745</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39277,7 +39277,7 @@
         <v>45749</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39355,7 +39355,7 @@
         <v>45028</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39428,7 +39428,7 @@
         <v>45244</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>45146</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>45146</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>45985</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>45985</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39793,7 +39793,7 @@
         <v>44881</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         <v>45764</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39939,7 +39939,7 @@
         <v>45985</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>46106</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>44924</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40163,7 +40163,7 @@
         <v>45012</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40236,7 +40236,7 @@
         <v>45308</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40309,7 +40309,7 @@
         <v>45988</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40382,7 +40382,7 @@
         <v>45547</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>45547</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40528,7 +40528,7 @@
         <v>46106</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40606,7 +40606,7 @@
         <v>45941</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40684,7 +40684,7 @@
         <v>45716</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40762,7 +40762,7 @@
         <v>45764</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>45941</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>45736</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45989</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>45973</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>44844</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41215,7 +41215,7 @@
         <v>45770</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41288,7 +41288,7 @@
         <v>45989</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41361,7 +41361,7 @@
         <v>44922</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>46114</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>45706</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41585,7 +41585,7 @@
         <v>45960</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41663,7 +41663,7 @@
         <v>45960</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>45085</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45583</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41887,7 +41887,7 @@
         <v>46114</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41965,7 +41965,7 @@
         <v>46114</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42043,7 +42043,7 @@
         <v>46114</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42121,7 +42121,7 @@
         <v>46114</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45597</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42277,7 +42277,7 @@
         <v>46122</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42350,7 +42350,7 @@
         <v>45995</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42428,7 +42428,7 @@
         <v>45995</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42501,7 +42501,7 @@
         <v>45338</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42579,7 +42579,7 @@
         <v>45995</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>45999</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42725,7 +42725,7 @@
         <v>46000</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>44897</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42871,7 +42871,7 @@
         <v>46132</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42944,7 +42944,7 @@
         <v>44951</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43017,7 +43017,7 @@
         <v>44946</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43090,7 +43090,7 @@
         <v>46002</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>46132</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43241,7 +43241,7 @@
         <v>46000</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43314,7 +43314,7 @@
         <v>45561</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>46002</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>44552</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43538,7 +43538,7 @@
         <v>44533</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43611,7 +43611,7 @@
         <v>46010</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>45219</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43762,7 +43762,7 @@
         <v>44638</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45973</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43908,7 +43908,7 @@
         <v>45642</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43986,7 +43986,7 @@
         <v>45230</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44064,7 +44064,7 @@
         <v>46007</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>45804</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44210,7 +44210,7 @@
         <v>45877</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44283,7 +44283,7 @@
         <v>44887</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45288</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44434,7 +44434,7 @@
         <v>45734</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>45824</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45897</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44653,7 +44653,7 @@
         <v>45923</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>45398</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44799,7 +44799,7 @@
         <v>45842</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44872,7 +44872,7 @@
         <v>45749</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>46013</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>45666</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>46013</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>45607</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45237,7 +45237,7 @@
         <v>45595</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45310,7 +45310,7 @@
         <v>45546</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45226</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45456,7 +45456,7 @@
         <v>45455</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>46029</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45607,7 +45607,7 @@
         <v>45232</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45680,7 +45680,7 @@
         <v>45568</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45758,7 +45758,7 @@
         <v>46029</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45831,7 +45831,7 @@
         <v>45275</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45904,7 +45904,7 @@
         <v>45245</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45977,7 +45977,7 @@
         <v>44711</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>44994</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45873</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>46133</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46269,7 +46269,7 @@
         <v>45474</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46342,7 +46342,7 @@
         <v>46033</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46415,7 +46415,7 @@
         <v>45174</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46488,7 +46488,7 @@
         <v>44908</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46566,7 +46566,7 @@
         <v>44697</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46644,7 +46644,7 @@
         <v>45069</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46717,7 +46717,7 @@
         <v>46139</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46790,7 +46790,7 @@
         <v>45842</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46863,7 +46863,7 @@
         <v>46040</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46936,7 +46936,7 @@
         <v>45204</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47009,7 +47009,7 @@
         <v>45668</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47082,7 +47082,7 @@
         <v>45260</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47155,7 +47155,7 @@
         <v>44865</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47228,7 +47228,7 @@
         <v>45747</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47306,7 +47306,7 @@
         <v>45915</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47379,7 +47379,7 @@
         <v>45156</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47452,7 +47452,7 @@
         <v>45369</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47525,7 +47525,7 @@
         <v>46048</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>45434</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>45375</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>45801</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47817,7 +47817,7 @@
         <v>45427</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47890,7 +47890,7 @@
         <v>46050</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47968,7 +47968,7 @@
         <v>45225</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48041,7 +48041,7 @@
         <v>45350</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>46050</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48192,7 +48192,7 @@
         <v>46052</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48270,7 +48270,7 @@
         <v>46052</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48348,7 +48348,7 @@
         <v>46052</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48426,7 +48426,7 @@
         <v>46052</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48504,7 +48504,7 @@
         <v>46052</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48582,7 +48582,7 @@
         <v>46058</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48660,7 +48660,7 @@
         <v>46058</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48733,7 +48733,7 @@
         <v>45149</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48806,7 +48806,7 @@
         <v>46071</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48879,7 +48879,7 @@
         <v>46071</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>46071</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49025,7 +49025,7 @@
         <v>46156</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49103,7 +49103,7 @@
         <v>46156</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49181,7 +49181,7 @@
         <v>46086</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49254,7 +49254,7 @@
         <v>46156</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49332,7 +49332,7 @@
         <v>46156</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49410,7 +49410,7 @@
         <v>46156</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49488,7 +49488,7 @@
         <v>45677</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49561,7 +49561,7 @@
         <v>46093</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49639,7 +49639,7 @@
         <v>46093</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>46093</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49795,7 +49795,7 @@
         <v>46093</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49873,7 +49873,7 @@
         <v>46093</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49951,7 +49951,7 @@
         <v>46093</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>46093</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
         <v>46163</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>46163</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50263,7 +50263,7 @@
         <v>46167</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50341,7 +50341,7 @@
         <v>46169</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50414,7 +50414,7 @@
         <v>46106</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50492,7 +50492,7 @@
         <v>46174</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50570,7 +50570,7 @@
         <v>46174</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50648,7 +50648,7 @@
         <v>46174</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50726,7 +50726,7 @@
         <v>46174</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50804,7 +50804,7 @@
         <v>46174</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50882,7 +50882,7 @@
         <v>46174</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50960,7 +50960,7 @@
         <v>46176</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51033,7 +51033,7 @@
         <v>46177</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51111,7 +51111,7 @@
         <v>46177</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51189,7 +51189,7 @@
         <v>46176</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51262,7 +51262,7 @@
         <v>46132</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51335,7 +51335,7 @@
         <v>46177</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51413,7 +51413,7 @@
         <v>46177</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51491,7 +51491,7 @@
         <v>46177</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>46177</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51647,7 +51647,7 @@
         <v>46177</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51725,7 +51725,7 @@
         <v>46177</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51803,7 +51803,7 @@
         <v>46058</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>46181</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51954,7 +51954,7 @@
         <v>46181</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52027,7 +52027,7 @@
         <v>46181</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52100,7 +52100,7 @@
         <v>46183</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>46185</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52251,7 +52251,7 @@
         <v>46185</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52324,7 +52324,7 @@
         <v>46191</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52397,7 +52397,7 @@
         <v>46027</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52470,7 +52470,7 @@
         <v>46195</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52543,7 +52543,7 @@
         <v>46199</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52616,7 +52616,7 @@
         <v>46203</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52694,7 +52694,7 @@
         <v>46203</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52772,7 +52772,7 @@
         <v>46203</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>46203</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52928,7 +52928,7 @@
         <v>46203</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53006,7 +53006,7 @@
         <v>46203</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53084,7 +53084,7 @@
         <v>46203</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53162,7 +53162,7 @@
         <v>46203</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53240,7 +53240,7 @@
         <v>46203</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53318,7 +53318,7 @@
         <v>46203</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53396,7 +53396,7 @@
         <v>46203</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53474,7 +53474,7 @@
         <v>46203</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53552,7 +53552,7 @@
         <v>46203</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53630,7 +53630,7 @@
         <v>46203</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53708,7 +53708,7 @@
         <v>46203</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53786,7 +53786,7 @@
         <v>46203</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53864,7 +53864,7 @@
         <v>46203</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53942,7 +53942,7 @@
         <v>46205</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54020,7 +54020,7 @@
         <v>46205</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54098,7 +54098,7 @@
         <v>46205</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54176,7 +54176,7 @@
         <v>46205</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54254,7 +54254,7 @@
         <v>46205</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54332,7 +54332,7 @@
         <v>46205</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54410,7 +54410,7 @@
         <v>46206</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54483,7 +54483,7 @@
         <v>46206</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54556,7 +54556,7 @@
         <v>46206</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54629,7 +54629,7 @@
         <v>46206</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54702,7 +54702,7 @@
         <v>45597</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54780,7 +54780,7 @@
         <v>46209</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54853,7 +54853,7 @@
         <v>46210</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54926,7 +54926,7 @@
         <v>46218</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54999,7 +54999,7 @@
         <v>46218</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55072,7 +55072,7 @@
         <v>46266</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55145,7 +55145,7 @@
         <v>46220</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55218,7 +55218,7 @@
         <v>46220</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>46226</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55364,7 +55364,7 @@
         <v>46274</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55437,7 +55437,7 @@
         <v>46237</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55515,7 +55515,7 @@
         <v>46237</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55588,7 +55588,7 @@
         <v>46237</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55661,7 +55661,7 @@
         <v>46237</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55739,7 +55739,7 @@
         <v>46237</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55817,7 +55817,7 @@
         <v>46280</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55890,7 +55890,7 @@
         <v>46240</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55963,7 +55963,7 @@
         <v>46242</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56036,7 +56036,7 @@
         <v>46242</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56109,7 +56109,7 @@
         <v>46242</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56182,7 +56182,7 @@
         <v>45972</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56255,7 +56255,7 @@
         <v>46241</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56328,7 +56328,7 @@
         <v>46241</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56401,7 +56401,7 @@
         <v>46241</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56474,7 +56474,7 @@
         <v>46287</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56547,7 +56547,7 @@
         <v>46287</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56620,7 +56620,7 @@
         <v>46139</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56693,7 +56693,7 @@
         <v>45688</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56766,7 +56766,7 @@
         <v>46293</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56839,7 +56839,7 @@
         <v>46293</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56912,7 +56912,7 @@
         <v>46293</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56985,7 +56985,7 @@
         <v>46294</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57058,7 +57058,7 @@
         <v>46293</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57131,7 +57131,7 @@
         <v>46293</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57204,7 +57204,7 @@
         <v>46293</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57277,7 +57277,7 @@
         <v>46247</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57355,7 +57355,7 @@
         <v>46293</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57428,7 +57428,7 @@
         <v>46293</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57501,7 +57501,7 @@
         <v>46293</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57574,7 +57574,7 @@
         <v>46296</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57647,7 +57647,7 @@
         <v>46253</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57720,7 +57720,7 @@
         <v>46293</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57793,7 +57793,7 @@
         <v>46293</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57866,7 +57866,7 @@
         <v>46253</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57939,7 +57939,7 @@
         <v>46295</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58012,7 +58012,7 @@
         <v>46253</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58085,7 +58085,7 @@
         <v>46295</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58158,7 +58158,7 @@
         <v>46293</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58231,7 +58231,7 @@
         <v>46293</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58304,7 +58304,7 @@
         <v>46293</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58377,7 +58377,7 @@
         <v>46295</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58450,7 +58450,7 @@
         <v>46253</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58523,7 +58523,7 @@
         <v>46293</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58596,7 +58596,7 @@
         <v>46300</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58669,7 +58669,7 @@
         <v>46153</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58742,7 +58742,7 @@
         <v>45459</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58815,7 +58815,7 @@
         <v>46191</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>46300</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58961,7 +58961,7 @@
         <v>46301</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59034,7 +59034,7 @@
         <v>46185</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59107,7 +59107,7 @@
         <v>46301</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59180,7 +59180,7 @@
         <v>45800</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59253,7 +59253,7 @@
         <v>46262</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59331,7 +59331,7 @@
         <v>46260</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59404,7 +59404,7 @@
         <v>46238</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59477,7 +59477,7 @@
         <v>46260</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59550,7 +59550,7 @@
         <v>46260</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59623,7 +59623,7 @@
         <v>46149</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59696,7 +59696,7 @@
         <v>46261</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59769,7 +59769,7 @@
         <v>46162</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59842,7 +59842,7 @@
         <v>46260</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59915,7 +59915,7 @@
         <v>46041</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59988,7 +59988,7 @@
         <v>44726</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60061,7 +60061,7 @@
         <v>44726</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60134,7 +60134,7 @@
         <v>44489</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60212,7 +60212,7 @@
         <v>44916</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60285,7 +60285,7 @@
         <v>45161</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60363,7 +60363,7 @@
         <v>45476</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60436,7 +60436,7 @@
         <v>44963</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60509,7 +60509,7 @@
         <v>44916</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60582,7 +60582,7 @@
         <v>45140</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60655,7 +60655,7 @@
         <v>44837</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60728,7 +60728,7 @@
         <v>45161</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60806,7 +60806,7 @@
         <v>44893</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60879,7 +60879,7 @@
         <v>44916</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60952,7 +60952,7 @@
         <v>45411</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         <v>45791</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61098,7 +61098,7 @@
         <v>45910</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61171,7 +61171,7 @@
         <v>46030</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61244,7 +61244,7 @@
         <v>46051</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61317,7 +61317,7 @@
         <v>46275</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61390,7 +61390,7 @@
         <v>46280</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>

--- a/Översikt UPPVIDINGE.xlsx
+++ b/Översikt UPPVIDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45174</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>44972</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>44972</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45442</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45789</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>46119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>46183</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>44980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>46183</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>44607</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45789</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>46119</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>46149</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>46119</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>45995</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44859</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>46066</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>46276</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>46183</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>45313</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>45366</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44972</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>45158</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>44939</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>46066</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>45195</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>45450</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>45604</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>45840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>46247</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>44979</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>45568</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>45604</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>44833</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>45517</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>45404</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>45117</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>45604</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>45205</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>44937</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>45320</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>45103</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>46051</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>46169</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>46205</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>46218</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>46297</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>44972</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44972</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         <v>44484</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>45789</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>44734</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>44690</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>44827</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>44788</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>45105</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         <v>44950</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>45320</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>44550</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>45517</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>44984</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>45435</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>45623</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>45534</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>44858</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>44998</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>45939</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>44663</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>45820</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>45826</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>45825</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>45840</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>44757</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>45981</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>46100</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>44858</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>45982</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>44676</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>46154</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>46185</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>45897</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>45688</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>46162</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>46247</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>46247</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>46247</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>46255</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>45440</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>44972</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>45810</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>46300</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>44865</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>44887</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>44887</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>44524</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>44483</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>44613</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>44487</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>44574</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44552</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>44536</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>44510</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>44812</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>44859</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>44574</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>44859</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>44676</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>44859</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>44859</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>44749</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>44574</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>44602</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>44580</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>44602</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>44859</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>44795</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>44757</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>44887</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>44588</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>44845</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>44582</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>44676</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>44552</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>44574</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>44503</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13777,7 +13777,7 @@
         <v>44483</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13850,7 +13850,7 @@
         <v>44837</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>44483</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>44603</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>44602</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>44859</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>44510</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14288,7 +14288,7 @@
         <v>44524</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
         <v>44721</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
         <v>44601</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>44683</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14580,7 +14580,7 @@
         <v>44686</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14653,7 +14653,7 @@
         <v>44858</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>44803</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
         <v>44887</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>44610</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14945,7 +14945,7 @@
         <v>44609</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15018,7 +15018,7 @@
         <v>44607</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15091,7 +15091,7 @@
         <v>44607</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>44711</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
         <v>44887</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>44887</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>44490</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>44795</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>44795</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>44522</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>44729</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>44705</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>44602</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>44998</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>44592</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>44882</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         <v>45428</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16211,7 +16211,7 @@
         <v>44971</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>45705</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         <v>45082</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>45454</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         <v>45118</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>45091</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>45190</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>45338</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>45338</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>45181</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>45407</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>45385</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>44937</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>44937</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45341</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>44593</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>45105</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>44917</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>45547</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>45164</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45547</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44838</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>45697</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>45041</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45041</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>44757</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18144,7 +18144,7 @@
         <v>44757</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>45093</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>45596</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>45615</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>45244</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>45716</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>45749</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>45590</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>45471</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>45338</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>45338</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45338</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45369</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>45389</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         <v>45005</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>44524</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>45098</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>44503</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>45348</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>45348</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>45140</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>45001</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>45440</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>45391</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>45590</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>44833</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>45604</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
         <v>45604</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>45604</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>45685</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>45190</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>45082</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>45708</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>44496</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>45692</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>45386</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>45561</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>45204</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>44757</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>45229</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>45279</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>45229</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>45091</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45085</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>44552</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45568</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>45140</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>45208</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>45279</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>44790</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21869,7 +21869,7 @@
         <v>44994</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>44610</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>44497</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>44942</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>45349</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>44902</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>45112</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>45887</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>45154</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>44789</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>45389</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>45454</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>45085</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>45427</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>45348</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
         <v>45544</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23037,7 +23037,7 @@
         <v>45428</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>45338</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>45338</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>44998</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>45716</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>45019</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         <v>45103</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>45428</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         <v>45428</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>45428</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
         <v>45894</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>45544</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>45901</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>45642</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>45714</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>45575</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>45840</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>45057</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>45154</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>45428</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45567</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>45722</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>45434</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>45336</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24809,7 +24809,7 @@
         <v>45229</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24882,7 +24882,7 @@
         <v>45428</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>44734</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>44734</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>45165</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>45901</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>45245</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>45181</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25393,7 +25393,7 @@
         <v>45089</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>45469</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>45639</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>45428</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45428</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>45384</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>44592</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25904,7 +25904,7 @@
         <v>45910</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25977,7 +25977,7 @@
         <v>45910</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26050,7 +26050,7 @@
         <v>45910</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>45838</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26196,7 +26196,7 @@
         <v>45391</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26269,7 +26269,7 @@
         <v>45600</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26342,7 +26342,7 @@
         <v>45153</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>45273</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26488,7 +26488,7 @@
         <v>45601</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>45516</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>45910</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>44526</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         <v>45530</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26858,7 +26858,7 @@
         <v>45674</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>45720</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>45049</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>45229</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>44599</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27228,7 +27228,7 @@
         <v>45476</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27301,7 +27301,7 @@
         <v>45389</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>45098</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>45502</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>45604</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
         <v>45604</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>45162</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27754,7 +27754,7 @@
         <v>45742</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>45154</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>45476</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27973,7 +27973,7 @@
         <v>44524</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28051,7 +28051,7 @@
         <v>44524</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28124,7 +28124,7 @@
         <v>45786</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28197,7 +28197,7 @@
         <v>45146</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28270,7 +28270,7 @@
         <v>45552</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28343,7 +28343,7 @@
         <v>45552</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28416,7 +28416,7 @@
         <v>45923</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>45923</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28562,7 +28562,7 @@
         <v>45590</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         <v>45604</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28708,7 +28708,7 @@
         <v>45747</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28781,7 +28781,7 @@
         <v>45118</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28854,7 +28854,7 @@
         <v>45355</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28927,7 +28927,7 @@
         <v>45013</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29000,7 +29000,7 @@
         <v>45370</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         <v>44942</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>45692</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29219,7 +29219,7 @@
         <v>45610</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>45233</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29365,7 +29365,7 @@
         <v>45211</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29438,7 +29438,7 @@
         <v>45146</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>45649</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29584,7 +29584,7 @@
         <v>44942</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29657,7 +29657,7 @@
         <v>45320</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>44659</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29803,7 +29803,7 @@
         <v>44592</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>45688</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>45688</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>45408</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>45338</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>45338</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>44985</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>44610</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>45404</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30480,7 +30480,7 @@
         <v>45934</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30553,7 +30553,7 @@
         <v>45934</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>45933</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>45702</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30772,7 +30772,7 @@
         <v>45720</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30845,7 +30845,7 @@
         <v>45642</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30923,7 +30923,7 @@
         <v>45389</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30996,7 +30996,7 @@
         <v>45597</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>45934</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>45801</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31220,7 +31220,7 @@
         <v>44844</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>45804</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31366,7 +31366,7 @@
         <v>45372</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31439,7 +31439,7 @@
         <v>45804</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31512,7 +31512,7 @@
         <v>45801</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31585,7 +31585,7 @@
         <v>45440</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31658,7 +31658,7 @@
         <v>45223</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>45764</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31809,7 +31809,7 @@
         <v>44945</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31882,7 +31882,7 @@
         <v>45169</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>45218</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32028,7 +32028,7 @@
         <v>45729</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32101,7 +32101,7 @@
         <v>45063</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32174,7 +32174,7 @@
         <v>45372</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32247,7 +32247,7 @@
         <v>44593</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>45196</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32393,7 +32393,7 @@
         <v>45770</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32466,7 +32466,7 @@
         <v>45807</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32539,7 +32539,7 @@
         <v>45404</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32612,7 +32612,7 @@
         <v>45770</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>45940</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32758,7 +32758,7 @@
         <v>45547</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32831,7 +32831,7 @@
         <v>45223</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32904,7 +32904,7 @@
         <v>44566</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>45664</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33050,7 +33050,7 @@
         <v>45057</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33123,7 +33123,7 @@
         <v>45278</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33196,7 +33196,7 @@
         <v>45777</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33274,7 +33274,7 @@
         <v>45211</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33347,7 +33347,7 @@
         <v>45009</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
         <v>45688</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>44923</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>45629</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33649,7 +33649,7 @@
         <v>45818</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>45107</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33795,7 +33795,7 @@
         <v>45195</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>45819</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33946,7 +33946,7 @@
         <v>45819</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34019,7 +34019,7 @@
         <v>45273</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34092,7 +34092,7 @@
         <v>45757</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34170,7 +34170,7 @@
         <v>45644</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34243,7 +34243,7 @@
         <v>45826</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34316,7 +34316,7 @@
         <v>45826</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34389,7 +34389,7 @@
         <v>45093</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>45184</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>45826</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34608,7 +34608,7 @@
         <v>45085</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34681,7 +34681,7 @@
         <v>45317</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34759,7 +34759,7 @@
         <v>44984</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34832,7 +34832,7 @@
         <v>45459</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>44984</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>44971</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35051,7 +35051,7 @@
         <v>45075</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>45153</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35197,7 +35197,7 @@
         <v>45174</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>45957</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>44496</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>45960</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>45960</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>44971</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>45230</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>45354</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35796,7 +35796,7 @@
         <v>45460</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35869,7 +35869,7 @@
         <v>45041</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35942,7 +35942,7 @@
         <v>45295</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>44757</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36098,7 +36098,7 @@
         <v>45547</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36171,7 +36171,7 @@
         <v>44523</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36244,7 +36244,7 @@
         <v>45475</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36317,7 +36317,7 @@
         <v>45230</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36395,7 +36395,7 @@
         <v>45769</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>45181</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36541,7 +36541,7 @@
         <v>45968</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>45357</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>45114</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>45615</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36833,7 +36833,7 @@
         <v>45155</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36906,7 +36906,7 @@
         <v>45243</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>44915</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>45973</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37125,7 +37125,7 @@
         <v>45118</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37198,7 +37198,7 @@
         <v>45336</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>45201</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37344,7 +37344,7 @@
         <v>45842</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37417,7 +37417,7 @@
         <v>45028</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37495,7 +37495,7 @@
         <v>44858</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>45792</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37641,7 +37641,7 @@
         <v>45865</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37714,7 +37714,7 @@
         <v>45692</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37787,7 +37787,7 @@
         <v>44924</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37860,7 +37860,7 @@
         <v>45230</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>45351</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38011,7 +38011,7 @@
         <v>45264</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>45637</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38157,7 +38157,7 @@
         <v>44939</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38230,7 +38230,7 @@
         <v>45224</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>44757</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>45324</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38459,7 +38459,7 @@
         <v>45981</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38537,7 +38537,7 @@
         <v>45279</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38610,7 +38610,7 @@
         <v>45155</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38683,7 +38683,7 @@
         <v>45981</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>45273</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>45273</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38907,7 +38907,7 @@
         <v>44603</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>45622</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>45233</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39126,7 +39126,7 @@
         <v>45981</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39204,7 +39204,7 @@
         <v>45745</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39277,7 +39277,7 @@
         <v>45749</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39355,7 +39355,7 @@
         <v>45028</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39428,7 +39428,7 @@
         <v>45244</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>45146</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>45146</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>45985</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>45985</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39793,7 +39793,7 @@
         <v>44881</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         <v>45764</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39939,7 +39939,7 @@
         <v>45985</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>46106</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>44924</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40163,7 +40163,7 @@
         <v>45012</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40236,7 +40236,7 @@
         <v>45308</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40309,7 +40309,7 @@
         <v>45988</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40382,7 +40382,7 @@
         <v>45547</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>45547</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40528,7 +40528,7 @@
         <v>46106</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40606,7 +40606,7 @@
         <v>45941</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40684,7 +40684,7 @@
         <v>45716</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40762,7 +40762,7 @@
         <v>45764</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>45941</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>45736</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45989</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>45973</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>44844</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41215,7 +41215,7 @@
         <v>45770</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41288,7 +41288,7 @@
         <v>45989</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41361,7 +41361,7 @@
         <v>44922</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>46114</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>45706</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41585,7 +41585,7 @@
         <v>45960</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41663,7 +41663,7 @@
         <v>45960</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>45085</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45583</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41887,7 +41887,7 @@
         <v>46114</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41965,7 +41965,7 @@
         <v>46114</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42043,7 +42043,7 @@
         <v>46114</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42121,7 +42121,7 @@
         <v>46114</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45597</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42277,7 +42277,7 @@
         <v>46122</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42350,7 +42350,7 @@
         <v>45995</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42428,7 +42428,7 @@
         <v>45995</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42501,7 +42501,7 @@
         <v>45338</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42579,7 +42579,7 @@
         <v>45995</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>45999</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42725,7 +42725,7 @@
         <v>46000</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>44897</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42871,7 +42871,7 @@
         <v>46132</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42944,7 +42944,7 @@
         <v>44951</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43017,7 +43017,7 @@
         <v>44946</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43090,7 +43090,7 @@
         <v>46002</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>46132</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43241,7 +43241,7 @@
         <v>46000</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43314,7 +43314,7 @@
         <v>45561</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>46002</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>44552</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43538,7 +43538,7 @@
         <v>44533</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43611,7 +43611,7 @@
         <v>46010</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>45219</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43762,7 +43762,7 @@
         <v>44638</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45973</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43908,7 +43908,7 @@
         <v>45642</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43986,7 +43986,7 @@
         <v>45230</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44064,7 +44064,7 @@
         <v>46007</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>45804</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44210,7 +44210,7 @@
         <v>45877</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44283,7 +44283,7 @@
         <v>44887</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45288</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44434,7 +44434,7 @@
         <v>45734</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
         <v>45824</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45897</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44653,7 +44653,7 @@
         <v>45923</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>45398</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44799,7 +44799,7 @@
         <v>45842</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44872,7 +44872,7 @@
         <v>45749</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>46013</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>45666</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>46013</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>45607</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45237,7 +45237,7 @@
         <v>45595</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45310,7 +45310,7 @@
         <v>45546</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45226</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45456,7 +45456,7 @@
         <v>45455</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>46029</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45607,7 +45607,7 @@
         <v>45232</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45680,7 +45680,7 @@
         <v>45568</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45758,7 +45758,7 @@
         <v>46029</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45831,7 +45831,7 @@
         <v>45275</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45904,7 +45904,7 @@
         <v>45245</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45977,7 +45977,7 @@
         <v>44711</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>44994</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45873</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>46133</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46269,7 +46269,7 @@
         <v>45474</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46342,7 +46342,7 @@
         <v>46033</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46415,7 +46415,7 @@
         <v>45174</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46488,7 +46488,7 @@
         <v>44908</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46566,7 +46566,7 @@
         <v>44697</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46644,7 +46644,7 @@
         <v>45069</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46717,7 +46717,7 @@
         <v>46139</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46790,7 +46790,7 @@
         <v>45842</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46863,7 +46863,7 @@
         <v>46040</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46936,7 +46936,7 @@
         <v>45204</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47009,7 +47009,7 @@
         <v>45668</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47082,7 +47082,7 @@
         <v>45260</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47155,7 +47155,7 @@
         <v>44865</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47228,7 +47228,7 @@
         <v>45747</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47306,7 +47306,7 @@
         <v>45915</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47379,7 +47379,7 @@
         <v>45156</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47452,7 +47452,7 @@
         <v>45369</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47525,7 +47525,7 @@
         <v>46048</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>45434</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>45375</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>45801</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47817,7 +47817,7 @@
         <v>45427</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47890,7 +47890,7 @@
         <v>46050</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47968,7 +47968,7 @@
         <v>45225</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48041,7 +48041,7 @@
         <v>45350</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>46050</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48192,7 +48192,7 @@
         <v>46052</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48270,7 +48270,7 @@
         <v>46052</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48348,7 +48348,7 @@
         <v>46052</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48426,7 +48426,7 @@
         <v>46052</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48504,7 +48504,7 @@
         <v>46052</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48582,7 +48582,7 @@
         <v>46058</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48660,7 +48660,7 @@
         <v>46058</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48733,7 +48733,7 @@
         <v>45149</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48806,7 +48806,7 @@
         <v>46071</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48879,7 +48879,7 @@
         <v>46071</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>46071</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49025,7 +49025,7 @@
         <v>46156</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49103,7 +49103,7 @@
         <v>46156</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49181,7 +49181,7 @@
         <v>46086</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49254,7 +49254,7 @@
         <v>46156</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49332,7 +49332,7 @@
         <v>46156</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49410,7 +49410,7 @@
         <v>46156</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49488,7 +49488,7 @@
         <v>45677</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49561,7 +49561,7 @@
         <v>46093</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49639,7 +49639,7 @@
         <v>46093</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>46093</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49795,7 +49795,7 @@
         <v>46093</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49873,7 +49873,7 @@
         <v>46093</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49951,7 +49951,7 @@
         <v>46093</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>46093</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
         <v>46163</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>46163</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50263,7 +50263,7 @@
         <v>46167</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50341,7 +50341,7 @@
         <v>46169</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50414,7 +50414,7 @@
         <v>46106</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50492,7 +50492,7 @@
         <v>46174</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50570,7 +50570,7 @@
         <v>46174</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50648,7 +50648,7 @@
         <v>46174</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50726,7 +50726,7 @@
         <v>46174</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50804,7 +50804,7 @@
         <v>46174</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50882,7 +50882,7 @@
         <v>46174</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50960,7 +50960,7 @@
         <v>46176</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51033,7 +51033,7 @@
         <v>46177</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51111,7 +51111,7 @@
         <v>46177</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51189,7 +51189,7 @@
         <v>46176</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51262,7 +51262,7 @@
         <v>46132</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51335,7 +51335,7 @@
         <v>46177</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51413,7 +51413,7 @@
         <v>46177</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51491,7 +51491,7 @@
         <v>46177</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>46177</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51647,7 +51647,7 @@
         <v>46177</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51725,7 +51725,7 @@
         <v>46177</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51803,7 +51803,7 @@
         <v>46058</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>46181</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51954,7 +51954,7 @@
         <v>46181</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52027,7 +52027,7 @@
         <v>46181</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52100,7 +52100,7 @@
         <v>46183</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>46185</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52251,7 +52251,7 @@
         <v>46185</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52324,7 +52324,7 @@
         <v>46191</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52397,7 +52397,7 @@
         <v>46027</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52470,7 +52470,7 @@
         <v>46195</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52543,7 +52543,7 @@
         <v>46199</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52616,7 +52616,7 @@
         <v>46203</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52694,7 +52694,7 @@
         <v>46203</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52772,7 +52772,7 @@
         <v>46203</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>46203</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52928,7 +52928,7 @@
         <v>46203</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53006,7 +53006,7 @@
         <v>46203</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53084,7 +53084,7 @@
         <v>46203</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53162,7 +53162,7 @@
         <v>46203</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53240,7 +53240,7 @@
         <v>46203</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53318,7 +53318,7 @@
         <v>46203</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53396,7 +53396,7 @@
         <v>46203</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53474,7 +53474,7 @@
         <v>46203</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53552,7 +53552,7 @@
         <v>46203</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53630,7 +53630,7 @@
         <v>46203</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53708,7 +53708,7 @@
         <v>46203</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53786,7 +53786,7 @@
         <v>46203</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53864,7 +53864,7 @@
         <v>46203</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53942,7 +53942,7 @@
         <v>46205</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54020,7 +54020,7 @@
         <v>46205</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54098,7 +54098,7 @@
         <v>46205</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54176,7 +54176,7 @@
         <v>46205</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54254,7 +54254,7 @@
         <v>46205</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54332,7 +54332,7 @@
         <v>46205</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54410,7 +54410,7 @@
         <v>46206</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54483,7 +54483,7 @@
         <v>46206</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54556,7 +54556,7 @@
         <v>46206</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54629,7 +54629,7 @@
         <v>46206</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54702,7 +54702,7 @@
         <v>45597</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54780,7 +54780,7 @@
         <v>46209</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54853,7 +54853,7 @@
         <v>46210</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54926,7 +54926,7 @@
         <v>46218</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54999,7 +54999,7 @@
         <v>46218</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55072,7 +55072,7 @@
         <v>46266</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55145,7 +55145,7 @@
         <v>46220</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55218,7 +55218,7 @@
         <v>46220</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>46226</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55364,7 +55364,7 @@
         <v>46274</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55437,7 +55437,7 @@
         <v>46237</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55515,7 +55515,7 @@
         <v>46237</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55588,7 +55588,7 @@
         <v>46237</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55661,7 +55661,7 @@
         <v>46237</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55739,7 +55739,7 @@
         <v>46237</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55817,7 +55817,7 @@
         <v>46280</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55890,7 +55890,7 @@
         <v>46240</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55963,7 +55963,7 @@
         <v>46242</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56036,7 +56036,7 @@
         <v>46242</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56109,7 +56109,7 @@
         <v>46242</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56182,7 +56182,7 @@
         <v>45972</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56255,7 +56255,7 @@
         <v>46241</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56328,7 +56328,7 @@
         <v>46241</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56401,7 +56401,7 @@
         <v>46241</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56474,7 +56474,7 @@
         <v>46287</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56547,7 +56547,7 @@
         <v>46287</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56620,7 +56620,7 @@
         <v>46139</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56693,7 +56693,7 @@
         <v>45688</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56766,7 +56766,7 @@
         <v>46293</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56839,7 +56839,7 @@
         <v>46293</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56912,7 +56912,7 @@
         <v>46293</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56985,7 +56985,7 @@
         <v>46294</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57058,7 +57058,7 @@
         <v>46293</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57131,7 +57131,7 @@
         <v>46293</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57204,7 +57204,7 @@
         <v>46293</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57277,7 +57277,7 @@
         <v>46247</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57355,7 +57355,7 @@
         <v>46293</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57428,7 +57428,7 @@
         <v>46293</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57501,7 +57501,7 @@
         <v>46293</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57574,7 +57574,7 @@
         <v>46296</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57647,7 +57647,7 @@
         <v>46253</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57720,7 +57720,7 @@
         <v>46293</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57793,7 +57793,7 @@
         <v>46293</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57866,7 +57866,7 @@
         <v>46253</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57939,7 +57939,7 @@
         <v>46295</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58012,7 +58012,7 @@
         <v>46253</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58085,7 +58085,7 @@
         <v>46295</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58158,7 +58158,7 @@
         <v>46293</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58231,7 +58231,7 @@
         <v>46293</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58304,7 +58304,7 @@
         <v>46293</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58377,7 +58377,7 @@
         <v>46295</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58450,7 +58450,7 @@
         <v>46253</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58523,7 +58523,7 @@
         <v>46293</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58596,7 +58596,7 @@
         <v>46300</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58669,7 +58669,7 @@
         <v>46153</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58742,7 +58742,7 @@
         <v>45459</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58815,7 +58815,7 @@
         <v>46191</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>46300</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58961,7 +58961,7 @@
         <v>46301</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59034,7 +59034,7 @@
         <v>46185</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59107,7 +59107,7 @@
         <v>46301</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59180,7 +59180,7 @@
         <v>45800</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59253,7 +59253,7 @@
         <v>46262</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59331,7 +59331,7 @@
         <v>46260</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59404,7 +59404,7 @@
         <v>46238</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59477,7 +59477,7 @@
         <v>46260</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59550,7 +59550,7 @@
         <v>46260</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59623,7 +59623,7 @@
         <v>46149</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59696,7 +59696,7 @@
         <v>46261</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59769,7 +59769,7 @@
         <v>46162</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59842,7 +59842,7 @@
         <v>46260</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59915,7 +59915,7 @@
         <v>46041</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59988,7 +59988,7 @@
         <v>44726</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60061,7 +60061,7 @@
         <v>44726</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60134,7 +60134,7 @@
         <v>44489</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60212,7 +60212,7 @@
         <v>44916</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60285,7 +60285,7 @@
         <v>45161</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60363,7 +60363,7 @@
         <v>45476</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60436,7 +60436,7 @@
         <v>44963</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60509,7 +60509,7 @@
         <v>44916</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60582,7 +60582,7 @@
         <v>45140</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60655,7 +60655,7 @@
         <v>44837</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60728,7 +60728,7 @@
         <v>45161</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60806,7 +60806,7 @@
         <v>44893</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60879,7 +60879,7 @@
         <v>44916</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60952,7 +60952,7 @@
         <v>45411</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         <v>45791</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61098,7 +61098,7 @@
         <v>45910</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61171,7 +61171,7 @@
         <v>46030</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61244,7 +61244,7 @@
         <v>46051</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61317,7 +61317,7 @@
         <v>46275</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61390,7 +61390,7 @@
         <v>46280</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>

--- a/Översikt UPPVIDINGE.xlsx
+++ b/Översikt UPPVIDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45174</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>44972</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>44972</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45442</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45789</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>46119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>46183</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>44980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>46183</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>44607</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45789</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>46119</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>46149</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>46119</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>45995</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44859</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>46066</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>46276</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>46183</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>45366</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>45313</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44972</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>45158</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>46066</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>44939</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>45604</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>45195</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>46247</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>45450</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>45840</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>44979</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>44833</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>45517</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45404</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>45604</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>44937</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>45205</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>45103</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>45320</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>46169</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>45604</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>46051</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>45117</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>46205</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>46218</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>45568</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>46297</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>46310</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44972</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>44972</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>45789</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44734</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>44827</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>44690</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>44788</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>45623</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>44858</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>44984</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44663</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>45982</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>44757</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>44676</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         <v>45939</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>46154</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>45981</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>44550</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>45320</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>44858</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>46185</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         <v>45897</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>46100</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>45105</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         <v>45435</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>44950</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>45688</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>46247</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>46247</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>46247</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>46162</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>46255</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>44998</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>45517</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>45534</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>45820</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>45825</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>45826</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>45840</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         <v>45440</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>44972</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>45810</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>46300</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>44865</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>44887</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>44887</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>44524</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>44613</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>44487</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
         <v>44552</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>44536</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>44574</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>44510</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>44812</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>44859</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>44574</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>44859</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>44676</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>44859</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>44859</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>44749</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44574</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>44602</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>44580</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>44602</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>44859</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>44795</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         <v>44757</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>44887</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>44588</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>44845</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13338,7 +13338,7 @@
         <v>44552</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>44503</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>44510</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>44803</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44887</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>44610</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>44609</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>44795</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>44795</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>44582</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>44601</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>44858</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>44711</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>44522</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         <v>44837</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>44859</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>44607</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>44607</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>44887</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>44887</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>44490</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>44676</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>44574</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>44603</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>44602</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>44524</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15241,7 +15241,7 @@
         <v>44721</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>44683</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>44686</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>44729</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>44705</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>44592</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>44602</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>45674</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>45736</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15908,7 +15908,7 @@
         <v>44922</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>45229</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>45389</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>45338</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>45338</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>45338</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>45338</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>45089</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>44610</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>45156</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>45098</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>45770</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>44524</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>45181</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>45385</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>44789</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>45697</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>45398</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>45384</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45389</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>45428</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>45428</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>45118</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>45338</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>45590</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         <v>45664</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>45320</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>45348</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>45714</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>45544</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>45471</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18201,7 +18201,7 @@
         <v>44942</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18274,7 +18274,7 @@
         <v>45408</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18347,7 +18347,7 @@
         <v>45226</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>45229</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>45745</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>44757</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>45223</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18717,7 +18717,7 @@
         <v>45668</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>45233</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>44524</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>44985</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>45273</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>45245</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>45153</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         <v>44566</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>45041</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>45041</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
         <v>44924</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>45469</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>45622</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>45174</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>45440</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>44924</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>45278</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>44984</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>45082</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>45459</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>45428</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>45369</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>45757</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>45085</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>44945</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>45230</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>44734</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
         <v>44734</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>45583</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20849,7 +20849,7 @@
         <v>45336</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20922,7 +20922,7 @@
         <v>44942</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20995,7 +20995,7 @@
         <v>44942</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>45230</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>45107</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45770</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>44951</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>45348</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>45973</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>45734</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>45804</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>45877</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>45547</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>45887</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>45547</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44497</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>45749</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>45666</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>45688</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22246,7 +22246,7 @@
         <v>45279</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22319,7 +22319,7 @@
         <v>45349</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>45093</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>44917</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>45204</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>45897</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>45428</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45428</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45428</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>46010</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45716</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>44902</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23132,7 +23132,7 @@
         <v>44552</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>45389</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>44757</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44984</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>45915</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>45229</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23575,7 +23575,7 @@
         <v>45642</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>44638</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>44865</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45112</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>45685</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>44603</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>45208</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>45894</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>44503</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24237,7 +24237,7 @@
         <v>45923</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24310,7 +24310,7 @@
         <v>45873</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>45637</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>45028</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>45552</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24602,7 +24602,7 @@
         <v>44994</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24675,7 +24675,7 @@
         <v>45801</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>45842</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>46133</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24894,7 +24894,7 @@
         <v>45901</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24967,7 +24967,7 @@
         <v>45901</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>45232</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25113,7 +25113,7 @@
         <v>45428</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25186,7 +25186,7 @@
         <v>45840</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>45567</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25332,7 +25332,7 @@
         <v>45838</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25405,7 +25405,7 @@
         <v>45910</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>45338</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>45338</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>45910</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>45910</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25780,7 +25780,7 @@
         <v>45910</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>45428</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25926,7 +25926,7 @@
         <v>45597</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>44711</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>45749</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26155,7 +26155,7 @@
         <v>45338</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26233,7 +26233,7 @@
         <v>45923</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26306,7 +26306,7 @@
         <v>45923</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>45149</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>45729</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>44659</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         <v>45013</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         <v>44971</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>44971</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26817,7 +26817,7 @@
         <v>44533</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26890,7 +26890,7 @@
         <v>45933</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>45934</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27036,7 +27036,7 @@
         <v>45455</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27114,7 +27114,7 @@
         <v>45934</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>45091</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>45934</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>44881</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>45940</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>45229</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>45225</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>45317</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>45041</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>45146</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>45357</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>45716</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>45716</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>45341</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28161,7 +28161,7 @@
         <v>45957</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>45233</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>46156</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         <v>46156</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28463,7 +28463,7 @@
         <v>46156</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28541,7 +28541,7 @@
         <v>46156</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28619,7 +28619,7 @@
         <v>46156</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28697,7 +28697,7 @@
         <v>45960</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>45677</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>45118</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>45169</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>45960</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>45720</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29145,7 +29145,7 @@
         <v>45273</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         <v>45273</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>44887</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>45085</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>44882</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>45407</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29583,7 +29583,7 @@
         <v>45154</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>45530</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>45968</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29802,7 +29802,7 @@
         <v>45012</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29875,7 +29875,7 @@
         <v>45973</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29948,7 +29948,7 @@
         <v>46163</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30026,7 +30026,7 @@
         <v>45642</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30099,7 +30099,7 @@
         <v>45324</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>44946</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>45085</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>46163</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>45369</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>45981</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30547,7 +30547,7 @@
         <v>44599</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30620,7 +30620,7 @@
         <v>45981</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>45981</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30776,7 +30776,7 @@
         <v>44757</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>44757</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>45001</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31005,7 +31005,7 @@
         <v>46167</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>45264</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>45561</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>45985</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>45985</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>45604</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>45604</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>45985</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>45764</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>45941</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>45747</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31828,7 +31828,7 @@
         <v>45989</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31901,7 +31901,7 @@
         <v>45941</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>45989</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32052,7 +32052,7 @@
         <v>45988</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32125,7 +32125,7 @@
         <v>45190</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>45427</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>45973</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>45960</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>45146</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>44524</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>45960</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32646,7 +32646,7 @@
         <v>45995</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>45428</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>46169</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>45995</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>45995</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33016,7 +33016,7 @@
         <v>45009</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>45999</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33162,7 +33162,7 @@
         <v>45275</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33235,7 +33235,7 @@
         <v>46000</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>46000</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>46106</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>45708</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>44697</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33610,7 +33610,7 @@
         <v>44897</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33683,7 +33683,7 @@
         <v>45607</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>46174</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33834,7 +33834,7 @@
         <v>46002</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>46002</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33990,7 +33990,7 @@
         <v>46174</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>46007</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>44915</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>44790</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34292,7 +34292,7 @@
         <v>46174</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>46174</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34448,7 +34448,7 @@
         <v>45454</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34521,7 +34521,7 @@
         <v>45590</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34594,7 +34594,7 @@
         <v>46174</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34672,7 +34672,7 @@
         <v>46174</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>45057</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>46013</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>46013</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34969,7 +34969,7 @@
         <v>45610</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>45404</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>45165</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>45336</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
         <v>45722</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35334,7 +35334,7 @@
         <v>45568</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35412,7 +35412,7 @@
         <v>45391</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35485,7 +35485,7 @@
         <v>46029</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45475</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35631,7 +35631,7 @@
         <v>46029</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45639</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35777,7 +35777,7 @@
         <v>45688</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>44523</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35928,7 +35928,7 @@
         <v>45279</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36001,7 +36001,7 @@
         <v>46033</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36074,7 +36074,7 @@
         <v>46132</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>46177</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>46176</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36298,7 +36298,7 @@
         <v>46177</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>46177</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36454,7 +36454,7 @@
         <v>46177</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>46177</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>46176</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>46177</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>46040</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>46177</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>46177</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>45069</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>45440</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>46048</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>45181</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>46050</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>45389</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>46050</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37511,7 +37511,7 @@
         <v>46058</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37589,7 +37589,7 @@
         <v>45190</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37662,7 +37662,7 @@
         <v>46052</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37740,7 +37740,7 @@
         <v>46181</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>46181</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37886,7 +37886,7 @@
         <v>46181</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37959,7 +37959,7 @@
         <v>46052</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>46052</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38115,7 +38115,7 @@
         <v>46052</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>45575</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38266,7 +38266,7 @@
         <v>46052</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38344,7 +38344,7 @@
         <v>46058</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>46183</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>46058</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>45098</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>45019</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>46071</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>46071</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>46071</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>46185</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39011,7 +39011,7 @@
         <v>45140</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39084,7 +39084,7 @@
         <v>45769</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>46185</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>44496</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>45155</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39376,7 +39376,7 @@
         <v>46086</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>45350</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45348</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>45434</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>44552</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39741,7 +39741,7 @@
         <v>45629</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>44971</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>46093</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39970,7 +39970,7 @@
         <v>46093</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>46093</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>46027</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>46093</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>46093</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40355,7 +40355,7 @@
         <v>46093</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40433,7 +40433,7 @@
         <v>46093</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40511,7 +40511,7 @@
         <v>46191</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>44757</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40662,7 +40662,7 @@
         <v>45049</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>45140</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40808,7 +40808,7 @@
         <v>45308</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40881,7 +40881,7 @@
         <v>46195</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>46106</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41032,7 +41032,7 @@
         <v>46106</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41110,7 +41110,7 @@
         <v>45093</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41183,7 +41183,7 @@
         <v>45595</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>45174</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41329,7 +41329,7 @@
         <v>46114</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41407,7 +41407,7 @@
         <v>46114</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41485,7 +41485,7 @@
         <v>45547</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>45547</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41631,7 +41631,7 @@
         <v>46114</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>46114</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41787,7 +41787,7 @@
         <v>46114</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45355</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41938,7 +41938,7 @@
         <v>45597</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42016,7 +42016,7 @@
         <v>46122</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>45615</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>45085</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>46199</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42308,7 +42308,7 @@
         <v>45351</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42381,7 +42381,7 @@
         <v>45642</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>45706</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>46203</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42610,7 +42610,7 @@
         <v>46203</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>46203</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>46203</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42844,7 +42844,7 @@
         <v>46203</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>46203</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43000,7 +43000,7 @@
         <v>46132</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43073,7 +43073,7 @@
         <v>46132</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>46203</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43224,7 +43224,7 @@
         <v>46205</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43302,7 +43302,7 @@
         <v>46205</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43380,7 +43380,7 @@
         <v>46203</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43458,7 +43458,7 @@
         <v>46203</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43536,7 +43536,7 @@
         <v>46203</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43614,7 +43614,7 @@
         <v>46205</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>46203</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43770,7 +43770,7 @@
         <v>46203</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43848,7 +43848,7 @@
         <v>46203</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43926,7 +43926,7 @@
         <v>45224</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>46205</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44082,7 +44082,7 @@
         <v>46205</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44160,7 +44160,7 @@
         <v>46205</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44238,7 +44238,7 @@
         <v>45211</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44311,7 +44311,7 @@
         <v>45154</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44384,7 +44384,7 @@
         <v>45219</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44457,7 +44457,7 @@
         <v>45162</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44530,7 +44530,7 @@
         <v>46203</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44608,7 +44608,7 @@
         <v>45547</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44681,7 +44681,7 @@
         <v>45164</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44754,7 +44754,7 @@
         <v>46203</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>46203</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44910,7 +44910,7 @@
         <v>45596</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>46203</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45061,7 +45061,7 @@
         <v>45824</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45134,7 +45134,7 @@
         <v>45615</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>46206</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>46206</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45353,7 +45353,7 @@
         <v>45597</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45431,7 +45431,7 @@
         <v>45474</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>45288</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45582,7 +45582,7 @@
         <v>45842</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45655,7 +45655,7 @@
         <v>46139</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45728,7 +45728,7 @@
         <v>45375</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>46206</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>45747</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45454</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>44858</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46098,7 +46098,7 @@
         <v>45404</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46171,7 +46171,7 @@
         <v>46206</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46244,7 +46244,7 @@
         <v>46210</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46317,7 +46317,7 @@
         <v>45476</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46390,7 +46390,7 @@
         <v>46209</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>44592</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46536,7 +46536,7 @@
         <v>45546</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         <v>45082</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46682,7 +46682,7 @@
         <v>45604</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46760,7 +46760,7 @@
         <v>45604</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46838,7 +46838,7 @@
         <v>45604</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>44838</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>45204</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47062,7 +47062,7 @@
         <v>45692</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47135,7 +47135,7 @@
         <v>45568</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47213,7 +47213,7 @@
         <v>46218</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47286,7 +47286,7 @@
         <v>46218</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>45091</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47437,7 +47437,7 @@
         <v>45118</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45005</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47583,7 +47583,7 @@
         <v>46220</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47656,7 +47656,7 @@
         <v>46220</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47729,7 +47729,7 @@
         <v>45705</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47802,7 +47802,7 @@
         <v>44994</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47875,7 +47875,7 @@
         <v>46226</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47948,7 +47948,7 @@
         <v>45370</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>45434</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48094,7 +48094,7 @@
         <v>45770</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48167,7 +48167,7 @@
         <v>45223</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48240,7 +48240,7 @@
         <v>45372</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>45547</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48386,7 +48386,7 @@
         <v>46274</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48459,7 +48459,7 @@
         <v>45201</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45184</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45211</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>44923</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48751,7 +48751,7 @@
         <v>45103</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48824,7 +48824,7 @@
         <v>45338</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48902,7 +48902,7 @@
         <v>44844</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48975,7 +48975,7 @@
         <v>45590</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49048,7 +49048,7 @@
         <v>46237</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49121,7 +49121,7 @@
         <v>46237</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49199,7 +49199,7 @@
         <v>45218</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>46237</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49345,7 +49345,7 @@
         <v>45028</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49423,7 +49423,7 @@
         <v>45105</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49496,7 +49496,7 @@
         <v>45386</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45688</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49652,7 +49652,7 @@
         <v>45544</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49725,7 +49725,7 @@
         <v>46280</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         <v>46237</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49876,7 +49876,7 @@
         <v>46237</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49954,7 +49954,7 @@
         <v>45155</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50027,7 +50027,7 @@
         <v>45749</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50105,7 +50105,7 @@
         <v>45354</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50178,7 +50178,7 @@
         <v>45243</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50251,7 +50251,7 @@
         <v>44844</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50324,7 +50324,7 @@
         <v>46240</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50397,7 +50397,7 @@
         <v>44908</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50475,7 +50475,7 @@
         <v>45972</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50548,7 +50548,7 @@
         <v>46242</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50621,7 +50621,7 @@
         <v>45372</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50694,7 +50694,7 @@
         <v>45196</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50767,7 +50767,7 @@
         <v>46287</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50840,7 +50840,7 @@
         <v>46241</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50913,7 +50913,7 @@
         <v>46241</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50986,7 +50986,7 @@
         <v>44833</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51064,7 +51064,7 @@
         <v>46287</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51137,7 +51137,7 @@
         <v>45244</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51210,7 +51210,7 @@
         <v>46241</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51283,7 +51283,7 @@
         <v>46242</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51356,7 +51356,7 @@
         <v>45063</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51429,7 +51429,7 @@
         <v>45245</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51502,7 +51502,7 @@
         <v>45692</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51575,7 +51575,7 @@
         <v>46242</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51648,7 +51648,7 @@
         <v>45260</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51721,7 +51721,7 @@
         <v>44592</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51794,7 +51794,7 @@
         <v>44593</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         <v>45230</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51945,7 +51945,7 @@
         <v>45075</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52018,7 +52018,7 @@
         <v>44939</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52091,7 +52091,7 @@
         <v>46139</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52164,7 +52164,7 @@
         <v>45692</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52237,7 +52237,7 @@
         <v>45702</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52310,7 +52310,7 @@
         <v>45688</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52383,7 +52383,7 @@
         <v>45338</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52461,7 +52461,7 @@
         <v>44937</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52534,7 +52534,7 @@
         <v>44937</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>45195</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52680,7 +52680,7 @@
         <v>45146</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52753,7 +52753,7 @@
         <v>45146</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52826,7 +52826,7 @@
         <v>45460</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52899,7 +52899,7 @@
         <v>45561</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45764</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53050,7 +53050,7 @@
         <v>44593</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>45181</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53201,7 +53201,7 @@
         <v>46247</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53279,7 +53279,7 @@
         <v>46294</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53352,7 +53352,7 @@
         <v>46293</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53425,7 +53425,7 @@
         <v>46293</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53498,7 +53498,7 @@
         <v>45279</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53571,7 +53571,7 @@
         <v>45153</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53644,7 +53644,7 @@
         <v>46295</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53717,7 +53717,7 @@
         <v>45244</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53790,7 +53790,7 @@
         <v>45154</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53863,7 +53863,7 @@
         <v>46293</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53936,7 +53936,7 @@
         <v>46293</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54009,7 +54009,7 @@
         <v>46293</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54082,7 +54082,7 @@
         <v>46293</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54155,7 +54155,7 @@
         <v>46293</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54228,7 +54228,7 @@
         <v>46293</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54301,7 +54301,7 @@
         <v>44998</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>46293</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54467,7 +54467,7 @@
         <v>46293</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54540,7 +54540,7 @@
         <v>45057</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54613,7 +54613,7 @@
         <v>46293</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54686,7 +54686,7 @@
         <v>46293</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54759,7 +54759,7 @@
         <v>46293</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54832,7 +54832,7 @@
         <v>46293</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54905,7 +54905,7 @@
         <v>46293</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54978,7 +54978,7 @@
         <v>45427</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55051,7 +55051,7 @@
         <v>44610</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55124,7 +55124,7 @@
         <v>46253</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55197,7 +55197,7 @@
         <v>45649</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55270,7 +55270,7 @@
         <v>44998</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55348,7 +55348,7 @@
         <v>46296</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55421,7 +55421,7 @@
         <v>46153</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55494,7 +55494,7 @@
         <v>45459</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55567,7 +55567,7 @@
         <v>46253</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55640,7 +55640,7 @@
         <v>46253</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55713,7 +55713,7 @@
         <v>46191</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55786,7 +55786,7 @@
         <v>46253</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55859,7 +55859,7 @@
         <v>44496</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55932,7 +55932,7 @@
         <v>45600</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56005,7 +56005,7 @@
         <v>45601</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56078,7 +56078,7 @@
         <v>45273</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56151,7 +56151,7 @@
         <v>45391</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56224,7 +56224,7 @@
         <v>45516</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56297,7 +56297,7 @@
         <v>44526</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56375,7 +56375,7 @@
         <v>46185</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56448,7 +56448,7 @@
         <v>46301</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56521,7 +56521,7 @@
         <v>46300</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56594,7 +56594,7 @@
         <v>46301</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56667,7 +56667,7 @@
         <v>46300</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56740,7 +56740,7 @@
         <v>45476</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56813,7 +56813,7 @@
         <v>45502</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56891,7 +56891,7 @@
         <v>46260</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56964,7 +56964,7 @@
         <v>46260</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57037,7 +57037,7 @@
         <v>45786</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57110,7 +57110,7 @@
         <v>45604</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57183,7 +57183,7 @@
         <v>45552</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57256,7 +57256,7 @@
         <v>45800</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57329,7 +57329,7 @@
         <v>45742</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57402,7 +57402,7 @@
         <v>46162</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57475,7 +57475,7 @@
         <v>46041</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57548,7 +57548,7 @@
         <v>46149</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57621,7 +57621,7 @@
         <v>46260</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57694,7 +57694,7 @@
         <v>46307</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57767,7 +57767,7 @@
         <v>46262</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57845,7 +57845,7 @@
         <v>46260</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57918,7 +57918,7 @@
         <v>45720</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57991,7 +57991,7 @@
         <v>46261</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58064,7 +58064,7 @@
         <v>45801</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58137,7 +58137,7 @@
         <v>46295</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58210,7 +58210,7 @@
         <v>45801</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58283,7 +58283,7 @@
         <v>45804</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58356,7 +58356,7 @@
         <v>46309</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58429,7 +58429,7 @@
         <v>46309</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58502,7 +58502,7 @@
         <v>46266</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58575,7 +58575,7 @@
         <v>45804</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58648,7 +58648,7 @@
         <v>45764</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58726,7 +58726,7 @@
         <v>45807</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58799,7 +58799,7 @@
         <v>46308</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58872,7 +58872,7 @@
         <v>46295</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>46308</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59018,7 +59018,7 @@
         <v>46238</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59091,7 +59091,7 @@
         <v>45818</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59164,7 +59164,7 @@
         <v>45777</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59242,7 +59242,7 @@
         <v>45819</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59320,7 +59320,7 @@
         <v>45819</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59393,7 +59393,7 @@
         <v>46310</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59466,7 +59466,7 @@
         <v>45644</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59539,7 +59539,7 @@
         <v>45826</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59612,7 +59612,7 @@
         <v>45826</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59685,7 +59685,7 @@
         <v>45826</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59758,7 +59758,7 @@
         <v>45230</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59836,7 +59836,7 @@
         <v>45295</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59914,7 +59914,7 @@
         <v>45114</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59987,7 +59987,7 @@
         <v>45842</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60060,7 +60060,7 @@
         <v>45865</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60133,7 +60133,7 @@
         <v>45792</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60206,7 +60206,7 @@
         <v>44489</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60284,7 +60284,7 @@
         <v>44726</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60357,7 +60357,7 @@
         <v>44916</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60430,7 +60430,7 @@
         <v>45161</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60508,7 +60508,7 @@
         <v>45476</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60581,7 +60581,7 @@
         <v>44963</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60654,7 +60654,7 @@
         <v>44916</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60727,7 +60727,7 @@
         <v>45140</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60800,7 +60800,7 @@
         <v>44837</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60873,7 +60873,7 @@
         <v>45161</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60951,7 +60951,7 @@
         <v>44893</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61024,7 +61024,7 @@
         <v>44916</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61097,7 +61097,7 @@
         <v>44726</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61170,7 +61170,7 @@
         <v>45411</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61243,7 +61243,7 @@
         <v>45791</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61316,7 +61316,7 @@
         <v>45910</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61389,7 +61389,7 @@
         <v>46030</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61462,7 +61462,7 @@
         <v>46051</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61535,7 +61535,7 @@
         <v>46275</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61608,7 +61608,7 @@
         <v>46280</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>

--- a/Översikt UPPVIDINGE.xlsx
+++ b/Översikt UPPVIDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45174</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>44972</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>44972</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45442</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45789</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>46119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>46183</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>44980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>46183</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>44607</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45789</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>46119</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>46149</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>46119</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>45995</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44859</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>46066</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>46276</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>46183</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>45366</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>45313</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44972</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>45158</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>46066</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>44939</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>45604</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>45195</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>46247</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>45450</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>45840</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>44979</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>44833</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>45517</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45404</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>45604</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>44937</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>45205</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>45103</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>45320</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>46169</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>45604</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>46051</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>45117</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>46205</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>46218</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>45568</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>46297</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>46310</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44972</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>44972</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>45789</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44734</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>44827</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>44690</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>44788</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>45623</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>44858</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>44984</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44663</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>45982</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>44757</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>44676</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         <v>45939</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>46154</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>45981</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>44550</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>45320</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>44858</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>46185</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         <v>45897</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>46100</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>45105</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         <v>45435</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>44950</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>45688</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>46247</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>46247</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>46247</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>46162</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>46255</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>44998</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>45517</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>45534</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>45820</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>45825</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>45826</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>45840</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         <v>45440</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>44972</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>45810</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>46300</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>44865</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>44887</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>44887</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>44524</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>44613</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>44487</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
         <v>44552</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>44536</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>44574</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>44510</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>44812</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>44859</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>44574</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>44859</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>44676</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>44859</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>44859</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>44749</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44574</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>44602</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>44580</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>44602</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>44859</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>44795</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         <v>44757</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>44887</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>44588</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>44845</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13338,7 +13338,7 @@
         <v>44552</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>44503</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>44510</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>44803</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44887</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>44610</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>44609</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>44795</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>44795</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>44582</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>44601</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>44858</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>44711</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>44522</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         <v>44837</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>44859</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>44607</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>44607</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>44887</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>44887</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>44490</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>44676</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>44574</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>44603</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>44602</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>44524</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15241,7 +15241,7 @@
         <v>44721</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>44683</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>44686</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>44729</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>44705</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>44592</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>44602</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>45674</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>45736</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15908,7 +15908,7 @@
         <v>44922</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>45229</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>45389</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>45338</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>45338</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>45338</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>45338</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>45089</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>44610</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>45156</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>45098</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>45770</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>44524</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>45181</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>45385</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>44789</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>45697</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>45398</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>45384</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45389</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>45428</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>45428</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>45118</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>45338</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>45590</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         <v>45664</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>45320</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>45348</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>45714</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>45544</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>45471</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18201,7 +18201,7 @@
         <v>44942</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18274,7 +18274,7 @@
         <v>45408</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18347,7 +18347,7 @@
         <v>45226</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>45229</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>45745</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>44757</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>45223</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18717,7 +18717,7 @@
         <v>45668</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>45233</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>44524</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>44985</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>45273</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>45245</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>45153</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         <v>44566</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>45041</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>45041</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
         <v>44924</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>45469</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>45622</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>45174</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>45440</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>44924</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>45278</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>44984</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>45082</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>45459</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>45428</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>45369</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>45757</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>45085</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>44945</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>45230</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>44734</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
         <v>44734</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>45583</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20849,7 +20849,7 @@
         <v>45336</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20922,7 +20922,7 @@
         <v>44942</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20995,7 +20995,7 @@
         <v>44942</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>45230</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>45107</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45770</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>44951</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>45348</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>45973</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>45734</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>45804</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>45877</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>45547</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>45887</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>45547</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44497</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>45749</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>45666</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>45688</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22246,7 +22246,7 @@
         <v>45279</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22319,7 +22319,7 @@
         <v>45349</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>45093</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>44917</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>45204</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>45897</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>45428</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45428</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45428</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>46010</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45716</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>44902</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23132,7 +23132,7 @@
         <v>44552</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>45389</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>44757</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44984</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23429,7 +23429,7 @@
         <v>45915</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>45229</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23575,7 +23575,7 @@
         <v>45642</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>44638</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>44865</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45112</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>45685</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>44603</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>45208</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>45894</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>44503</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24237,7 +24237,7 @@
         <v>45923</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24310,7 +24310,7 @@
         <v>45873</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>45637</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>45028</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>45552</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24602,7 +24602,7 @@
         <v>44994</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24675,7 +24675,7 @@
         <v>45801</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>45842</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>46133</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24894,7 +24894,7 @@
         <v>45901</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24967,7 +24967,7 @@
         <v>45901</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>45232</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25113,7 +25113,7 @@
         <v>45428</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25186,7 +25186,7 @@
         <v>45840</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>45567</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25332,7 +25332,7 @@
         <v>45838</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25405,7 +25405,7 @@
         <v>45910</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>45338</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>45338</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>45910</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>45910</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25780,7 +25780,7 @@
         <v>45910</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>45428</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25926,7 +25926,7 @@
         <v>45597</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>44711</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>45749</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26155,7 +26155,7 @@
         <v>45338</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26233,7 +26233,7 @@
         <v>45923</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26306,7 +26306,7 @@
         <v>45923</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>45149</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>45729</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>44659</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         <v>45013</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         <v>44971</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>44971</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26817,7 +26817,7 @@
         <v>44533</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26890,7 +26890,7 @@
         <v>45933</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>45934</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27036,7 +27036,7 @@
         <v>45455</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27114,7 +27114,7 @@
         <v>45934</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>45091</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>45934</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>44881</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>45940</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>45229</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>45225</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>45317</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>45041</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>45146</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>45357</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>45716</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>45716</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>45341</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28161,7 +28161,7 @@
         <v>45957</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>45233</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>46156</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         <v>46156</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28463,7 +28463,7 @@
         <v>46156</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28541,7 +28541,7 @@
         <v>46156</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28619,7 +28619,7 @@
         <v>46156</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28697,7 +28697,7 @@
         <v>45960</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>45677</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>45118</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>45169</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>45960</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>45720</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29145,7 +29145,7 @@
         <v>45273</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         <v>45273</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>44887</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>45085</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>44882</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>45407</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29583,7 +29583,7 @@
         <v>45154</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>45530</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>45968</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29802,7 +29802,7 @@
         <v>45012</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29875,7 +29875,7 @@
         <v>45973</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29948,7 +29948,7 @@
         <v>46163</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30026,7 +30026,7 @@
         <v>45642</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30099,7 +30099,7 @@
         <v>45324</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>44946</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>45085</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>46163</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>45369</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>45981</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30547,7 +30547,7 @@
         <v>44599</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30620,7 +30620,7 @@
         <v>45981</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>45981</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30776,7 +30776,7 @@
         <v>44757</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>44757</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>45001</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31005,7 +31005,7 @@
         <v>46167</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>45264</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>45561</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>45985</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>45985</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>45604</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>45604</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>45985</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>45764</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>45941</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31755,7 +31755,7 @@
         <v>45747</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31828,7 +31828,7 @@
         <v>45989</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31901,7 +31901,7 @@
         <v>45941</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>45989</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32052,7 +32052,7 @@
         <v>45988</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32125,7 +32125,7 @@
         <v>45190</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>45427</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>45973</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>45960</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>45146</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>44524</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>45960</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32646,7 +32646,7 @@
         <v>45995</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>45428</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>46169</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>45995</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>45995</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33016,7 +33016,7 @@
         <v>45009</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>45999</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33162,7 +33162,7 @@
         <v>45275</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33235,7 +33235,7 @@
         <v>46000</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>46000</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>46106</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>45708</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>44697</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33610,7 +33610,7 @@
         <v>44897</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33683,7 +33683,7 @@
         <v>45607</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>46174</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33834,7 +33834,7 @@
         <v>46002</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>46002</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33990,7 +33990,7 @@
         <v>46174</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>46007</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>44915</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>44790</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34292,7 +34292,7 @@
         <v>46174</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>46174</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34448,7 +34448,7 @@
         <v>45454</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34521,7 +34521,7 @@
         <v>45590</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34594,7 +34594,7 @@
         <v>46174</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34672,7 +34672,7 @@
         <v>46174</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>45057</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>46013</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>46013</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34969,7 +34969,7 @@
         <v>45610</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>45404</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>45165</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>45336</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
         <v>45722</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35334,7 +35334,7 @@
         <v>45568</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35412,7 +35412,7 @@
         <v>45391</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35485,7 +35485,7 @@
         <v>46029</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45475</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35631,7 +35631,7 @@
         <v>46029</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45639</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35777,7 +35777,7 @@
         <v>45688</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>44523</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35928,7 +35928,7 @@
         <v>45279</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36001,7 +36001,7 @@
         <v>46033</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36074,7 +36074,7 @@
         <v>46132</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>46177</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>46176</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36298,7 +36298,7 @@
         <v>46177</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>46177</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36454,7 +36454,7 @@
         <v>46177</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>46177</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>46176</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>46177</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>46040</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>46177</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>46177</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>45069</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>45440</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>46048</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>45181</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>46050</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>45389</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>46050</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37511,7 +37511,7 @@
         <v>46058</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37589,7 +37589,7 @@
         <v>45190</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37662,7 +37662,7 @@
         <v>46052</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37740,7 +37740,7 @@
         <v>46181</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>46181</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37886,7 +37886,7 @@
         <v>46181</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37959,7 +37959,7 @@
         <v>46052</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>46052</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38115,7 +38115,7 @@
         <v>46052</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>45575</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38266,7 +38266,7 @@
         <v>46052</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38344,7 +38344,7 @@
         <v>46058</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>46183</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>46058</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>45098</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>45019</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>46071</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>46071</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>46071</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>46185</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39011,7 +39011,7 @@
         <v>45140</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39084,7 +39084,7 @@
         <v>45769</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>46185</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>44496</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>45155</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39376,7 +39376,7 @@
         <v>46086</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>45350</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45348</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>45434</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>44552</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39741,7 +39741,7 @@
         <v>45629</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>44971</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>46093</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39970,7 +39970,7 @@
         <v>46093</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>46093</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>46027</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>46093</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>46093</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40355,7 +40355,7 @@
         <v>46093</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40433,7 +40433,7 @@
         <v>46093</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40511,7 +40511,7 @@
         <v>46191</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>44757</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40662,7 +40662,7 @@
         <v>45049</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>45140</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40808,7 +40808,7 @@
         <v>45308</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40881,7 +40881,7 @@
         <v>46195</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>46106</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41032,7 +41032,7 @@
         <v>46106</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41110,7 +41110,7 @@
         <v>45093</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41183,7 +41183,7 @@
         <v>45595</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>45174</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41329,7 +41329,7 @@
         <v>46114</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41407,7 +41407,7 @@
         <v>46114</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41485,7 +41485,7 @@
         <v>45547</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>45547</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41631,7 +41631,7 @@
         <v>46114</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>46114</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41787,7 +41787,7 @@
         <v>46114</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45355</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41938,7 +41938,7 @@
         <v>45597</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42016,7 +42016,7 @@
         <v>46122</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>45615</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>45085</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>46199</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42308,7 +42308,7 @@
         <v>45351</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42381,7 +42381,7 @@
         <v>45642</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>45706</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>46203</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42610,7 +42610,7 @@
         <v>46203</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>46203</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>46203</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42844,7 +42844,7 @@
         <v>46203</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>46203</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43000,7 +43000,7 @@
         <v>46132</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43073,7 +43073,7 @@
         <v>46132</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>46203</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43224,7 +43224,7 @@
         <v>46205</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43302,7 +43302,7 @@
         <v>46205</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43380,7 +43380,7 @@
         <v>46203</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43458,7 +43458,7 @@
         <v>46203</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43536,7 +43536,7 @@
         <v>46203</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43614,7 +43614,7 @@
         <v>46205</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>46203</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43770,7 +43770,7 @@
         <v>46203</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43848,7 +43848,7 @@
         <v>46203</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43926,7 +43926,7 @@
         <v>45224</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>46205</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44082,7 +44082,7 @@
         <v>46205</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44160,7 +44160,7 @@
         <v>46205</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44238,7 +44238,7 @@
         <v>45211</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44311,7 +44311,7 @@
         <v>45154</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44384,7 +44384,7 @@
         <v>45219</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44457,7 +44457,7 @@
         <v>45162</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44530,7 +44530,7 @@
         <v>46203</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44608,7 +44608,7 @@
         <v>45547</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44681,7 +44681,7 @@
         <v>45164</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44754,7 +44754,7 @@
         <v>46203</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>46203</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44910,7 +44910,7 @@
         <v>45596</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>46203</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45061,7 +45061,7 @@
         <v>45824</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45134,7 +45134,7 @@
         <v>45615</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>46206</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>46206</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45353,7 +45353,7 @@
         <v>45597</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45431,7 +45431,7 @@
         <v>45474</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>45288</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45582,7 +45582,7 @@
         <v>45842</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45655,7 +45655,7 @@
         <v>46139</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45728,7 +45728,7 @@
         <v>45375</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>46206</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>45747</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45454</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>44858</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46098,7 +46098,7 @@
         <v>45404</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46171,7 +46171,7 @@
         <v>46206</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46244,7 +46244,7 @@
         <v>46210</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46317,7 +46317,7 @@
         <v>45476</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46390,7 +46390,7 @@
         <v>46209</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>44592</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46536,7 +46536,7 @@
         <v>45546</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         <v>45082</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46682,7 +46682,7 @@
         <v>45604</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46760,7 +46760,7 @@
         <v>45604</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46838,7 +46838,7 @@
         <v>45604</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>44838</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>45204</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47062,7 +47062,7 @@
         <v>45692</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47135,7 +47135,7 @@
         <v>45568</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47213,7 +47213,7 @@
         <v>46218</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47286,7 +47286,7 @@
         <v>46218</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>45091</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47437,7 +47437,7 @@
         <v>45118</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45005</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47583,7 +47583,7 @@
         <v>46220</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47656,7 +47656,7 @@
         <v>46220</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47729,7 +47729,7 @@
         <v>45705</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47802,7 +47802,7 @@
         <v>44994</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47875,7 +47875,7 @@
         <v>46226</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47948,7 +47948,7 @@
         <v>45370</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>45434</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48094,7 +48094,7 @@
         <v>45770</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48167,7 +48167,7 @@
         <v>45223</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48240,7 +48240,7 @@
         <v>45372</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>45547</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48386,7 +48386,7 @@
         <v>46274</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48459,7 +48459,7 @@
         <v>45201</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45184</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45211</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>44923</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48751,7 +48751,7 @@
         <v>45103</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48824,7 +48824,7 @@
         <v>45338</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48902,7 +48902,7 @@
         <v>44844</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48975,7 +48975,7 @@
         <v>45590</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49048,7 +49048,7 @@
         <v>46237</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49121,7 +49121,7 @@
         <v>46237</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49199,7 +49199,7 @@
         <v>45218</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>46237</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49345,7 +49345,7 @@
         <v>45028</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49423,7 +49423,7 @@
         <v>45105</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49496,7 +49496,7 @@
         <v>45386</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45688</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49652,7 +49652,7 @@
         <v>45544</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49725,7 +49725,7 @@
         <v>46280</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         <v>46237</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49876,7 +49876,7 @@
         <v>46237</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49954,7 +49954,7 @@
         <v>45155</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50027,7 +50027,7 @@
         <v>45749</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50105,7 +50105,7 @@
         <v>45354</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50178,7 +50178,7 @@
         <v>45243</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50251,7 +50251,7 @@
         <v>44844</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50324,7 +50324,7 @@
         <v>46240</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50397,7 +50397,7 @@
         <v>44908</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50475,7 +50475,7 @@
         <v>45972</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50548,7 +50548,7 @@
         <v>46242</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50621,7 +50621,7 @@
         <v>45372</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50694,7 +50694,7 @@
         <v>45196</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50767,7 +50767,7 @@
         <v>46287</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50840,7 +50840,7 @@
         <v>46241</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50913,7 +50913,7 @@
         <v>46241</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50986,7 +50986,7 @@
         <v>44833</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51064,7 +51064,7 @@
         <v>46287</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51137,7 +51137,7 @@
         <v>45244</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51210,7 +51210,7 @@
         <v>46241</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51283,7 +51283,7 @@
         <v>46242</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51356,7 +51356,7 @@
         <v>45063</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51429,7 +51429,7 @@
         <v>45245</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51502,7 +51502,7 @@
         <v>45692</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51575,7 +51575,7 @@
         <v>46242</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51648,7 +51648,7 @@
         <v>45260</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51721,7 +51721,7 @@
         <v>44592</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51794,7 +51794,7 @@
         <v>44593</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         <v>45230</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51945,7 +51945,7 @@
         <v>45075</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52018,7 +52018,7 @@
         <v>44939</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52091,7 +52091,7 @@
         <v>46139</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52164,7 +52164,7 @@
         <v>45692</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52237,7 +52237,7 @@
         <v>45702</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52310,7 +52310,7 @@
         <v>45688</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52383,7 +52383,7 @@
         <v>45338</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52461,7 +52461,7 @@
         <v>44937</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52534,7 +52534,7 @@
         <v>44937</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>45195</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52680,7 +52680,7 @@
         <v>45146</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52753,7 +52753,7 @@
         <v>45146</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52826,7 +52826,7 @@
         <v>45460</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52899,7 +52899,7 @@
         <v>45561</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45764</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53050,7 +53050,7 @@
         <v>44593</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>45181</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53201,7 +53201,7 @@
         <v>46247</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53279,7 +53279,7 @@
         <v>46294</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53352,7 +53352,7 @@
         <v>46293</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53425,7 +53425,7 @@
         <v>46293</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53498,7 +53498,7 @@
         <v>45279</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53571,7 +53571,7 @@
         <v>45153</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53644,7 +53644,7 @@
         <v>46295</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53717,7 +53717,7 @@
         <v>45244</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53790,7 +53790,7 @@
         <v>45154</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53863,7 +53863,7 @@
         <v>46293</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53936,7 +53936,7 @@
         <v>46293</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54009,7 +54009,7 @@
         <v>46293</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54082,7 +54082,7 @@
         <v>46293</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54155,7 +54155,7 @@
         <v>46293</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54228,7 +54228,7 @@
         <v>46293</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54301,7 +54301,7 @@
         <v>44998</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>46293</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54467,7 +54467,7 @@
         <v>46293</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54540,7 +54540,7 @@
         <v>45057</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54613,7 +54613,7 @@
         <v>46293</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54686,7 +54686,7 @@
         <v>46293</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54759,7 +54759,7 @@
         <v>46293</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54832,7 +54832,7 @@
         <v>46293</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54905,7 +54905,7 @@
         <v>46293</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54978,7 +54978,7 @@
         <v>45427</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55051,7 +55051,7 @@
         <v>44610</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55124,7 +55124,7 @@
         <v>46253</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55197,7 +55197,7 @@
         <v>45649</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55270,7 +55270,7 @@
         <v>44998</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55348,7 +55348,7 @@
         <v>46296</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55421,7 +55421,7 @@
         <v>46153</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55494,7 +55494,7 @@
         <v>45459</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55567,7 +55567,7 @@
         <v>46253</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55640,7 +55640,7 @@
         <v>46253</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55713,7 +55713,7 @@
         <v>46191</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55786,7 +55786,7 @@
         <v>46253</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55859,7 +55859,7 @@
         <v>44496</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55932,7 +55932,7 @@
         <v>45600</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56005,7 +56005,7 @@
         <v>45601</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56078,7 +56078,7 @@
         <v>45273</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56151,7 +56151,7 @@
         <v>45391</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56224,7 +56224,7 @@
         <v>45516</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56297,7 +56297,7 @@
         <v>44526</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56375,7 +56375,7 @@
         <v>46185</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56448,7 +56448,7 @@
         <v>46301</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56521,7 +56521,7 @@
         <v>46300</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56594,7 +56594,7 @@
         <v>46301</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56667,7 +56667,7 @@
         <v>46300</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56740,7 +56740,7 @@
         <v>45476</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56813,7 +56813,7 @@
         <v>45502</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56891,7 +56891,7 @@
         <v>46260</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56964,7 +56964,7 @@
         <v>46260</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57037,7 +57037,7 @@
         <v>45786</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57110,7 +57110,7 @@
         <v>45604</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57183,7 +57183,7 @@
         <v>45552</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57256,7 +57256,7 @@
         <v>45800</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57329,7 +57329,7 @@
         <v>45742</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57402,7 +57402,7 @@
         <v>46162</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57475,7 +57475,7 @@
         <v>46041</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57548,7 +57548,7 @@
         <v>46149</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57621,7 +57621,7 @@
         <v>46260</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57694,7 +57694,7 @@
         <v>46307</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57767,7 +57767,7 @@
         <v>46262</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57845,7 +57845,7 @@
         <v>46260</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57918,7 +57918,7 @@
         <v>45720</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57991,7 +57991,7 @@
         <v>46261</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58064,7 +58064,7 @@
         <v>45801</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58137,7 +58137,7 @@
         <v>46295</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58210,7 +58210,7 @@
         <v>45801</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58283,7 +58283,7 @@
         <v>45804</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58356,7 +58356,7 @@
         <v>46309</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58429,7 +58429,7 @@
         <v>46309</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58502,7 +58502,7 @@
         <v>46266</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58575,7 +58575,7 @@
         <v>45804</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58648,7 +58648,7 @@
         <v>45764</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58726,7 +58726,7 @@
         <v>45807</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58799,7 +58799,7 @@
         <v>46308</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58872,7 +58872,7 @@
         <v>46295</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>46308</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59018,7 +59018,7 @@
         <v>46238</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59091,7 +59091,7 @@
         <v>45818</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59164,7 +59164,7 @@
         <v>45777</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59242,7 +59242,7 @@
         <v>45819</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59320,7 +59320,7 @@
         <v>45819</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59393,7 +59393,7 @@
         <v>46310</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59466,7 +59466,7 @@
         <v>45644</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59539,7 +59539,7 @@
         <v>45826</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59612,7 +59612,7 @@
         <v>45826</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59685,7 +59685,7 @@
         <v>45826</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59758,7 +59758,7 @@
         <v>45230</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59836,7 +59836,7 @@
         <v>45295</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59914,7 +59914,7 @@
         <v>45114</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59987,7 +59987,7 @@
         <v>45842</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60060,7 +60060,7 @@
         <v>45865</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60133,7 +60133,7 @@
         <v>45792</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60206,7 +60206,7 @@
         <v>44489</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60284,7 +60284,7 @@
         <v>44726</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60357,7 +60357,7 @@
         <v>44916</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60430,7 +60430,7 @@
         <v>45161</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60508,7 +60508,7 @@
         <v>45476</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60581,7 +60581,7 @@
         <v>44963</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60654,7 +60654,7 @@
         <v>44916</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60727,7 +60727,7 @@
         <v>45140</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60800,7 +60800,7 @@
         <v>44837</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60873,7 +60873,7 @@
         <v>45161</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60951,7 +60951,7 @@
         <v>44893</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61024,7 +61024,7 @@
         <v>44916</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61097,7 +61097,7 @@
         <v>44726</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61170,7 +61170,7 @@
         <v>45411</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61243,7 +61243,7 @@
         <v>45791</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61316,7 +61316,7 @@
         <v>45910</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61389,7 +61389,7 @@
         <v>46030</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61462,7 +61462,7 @@
         <v>46051</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61535,7 +61535,7 @@
         <v>46275</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61608,7 +61608,7 @@
         <v>46280</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>

--- a/Översikt UPPVIDINGE.xlsx
+++ b/Översikt UPPVIDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45174</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>44972</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>44972</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45442</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45789</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>46119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>46183</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>44980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>46183</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>44607</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45789</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>46119</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>46149</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>46119</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>45995</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44859</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>46066</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>46183</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>46276</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>45313</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>45366</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44972</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>46066</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>45158</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>44939</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>45195</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>45450</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>46247</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>45840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>45604</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>44979</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>46169</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>45604</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>44833</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>46205</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>46218</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>46051</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>46297</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>46310</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>46316</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>45604</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>45205</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>45103</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>45568</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>45517</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>45404</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>45117</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>44937</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>45320</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>44972</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>44972</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>45789</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>44734</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>44827</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>44690</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>44788</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         <v>44858</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>45939</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>45105</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>46185</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>45897</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>45981</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>44950</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>45517</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>45688</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         <v>45534</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>46162</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>46247</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>46247</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>46247</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>45820</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>45826</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>45825</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         <v>46255</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>45840</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>46100</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>44550</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>45435</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>45623</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>45982</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>44676</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>46154</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>45320</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>44984</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>44858</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>44998</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>44663</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>44757</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>45440</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>44972</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>45810</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>46300</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>44865</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>44887</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>44887</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>44524</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>44613</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44552</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>44574</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>44536</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>44510</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         <v>44812</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>44859</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>44574</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>44859</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>44676</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>44859</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>44859</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>44749</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>44574</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>44602</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>44580</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>44602</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>44859</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>44795</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>44757</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>44887</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>44588</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>44845</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>44552</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>44503</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>44510</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>44803</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>44887</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>44609</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>44610</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>44795</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
         <v>44795</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14028,7 +14028,7 @@
         <v>44582</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>44601</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>44858</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>44711</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>44522</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>44837</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>44859</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>44607</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>44607</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>44887</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>44887</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>44676</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>44574</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>44603</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>44602</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>44524</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>44721</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>44683</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>44686</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>44729</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>44705</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>44533</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>44602</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>45349</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>44902</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>45112</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>44592</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45887</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>44757</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>45229</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>45389</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>45091</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>45190</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>45338</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>45338</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>45341</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>44638</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>45279</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>45697</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>45041</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>45041</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17051,7 +17051,7 @@
         <v>45894</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>45230</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>44552</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17275,7 +17275,7 @@
         <v>45338</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17353,7 +17353,7 @@
         <v>45338</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17431,7 +17431,7 @@
         <v>45338</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>44887</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>45208</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17655,7 +17655,7 @@
         <v>45391</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>45398</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>45901</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>44833</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>45840</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>45428</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         <v>45567</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         <v>45901</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>45607</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         <v>45595</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>44497</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>45546</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>45226</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18609,7 +18609,7 @@
         <v>45910</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>45910</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>45910</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>45838</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>45455</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>45910</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
         <v>45232</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>45568</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>45275</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>45245</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>44711</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>44994</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19495,7 +19495,7 @@
         <v>46163</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45174</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>46163</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>44908</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19802,7 +19802,7 @@
         <v>44697</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19880,7 +19880,7 @@
         <v>45069</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         <v>45923</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>45923</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>45668</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20172,7 +20172,7 @@
         <v>46167</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         <v>45260</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>44865</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>46169</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20469,7 +20469,7 @@
         <v>46106</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>45156</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>45369</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>45934</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20766,7 +20766,7 @@
         <v>45934</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>46174</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>45933</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>46174</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>45434</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>45375</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>45934</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21287,7 +21287,7 @@
         <v>45427</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>45225</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>45350</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21506,7 +21506,7 @@
         <v>46174</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>46174</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>46174</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>45940</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>46174</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>44998</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>46176</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22057,7 +22057,7 @@
         <v>45428</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>46177</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>46177</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>46176</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22359,7 +22359,7 @@
         <v>46132</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>46177</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>44757</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>44757</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22666,7 +22666,7 @@
         <v>46177</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>46177</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>46177</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>46177</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>46177</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23056,7 +23056,7 @@
         <v>45471</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>45454</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>45118</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>45389</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>46058</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>45140</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>46181</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>46181</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>44593</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>46181</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23791,7 +23791,7 @@
         <v>45105</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23864,7 +23864,7 @@
         <v>45440</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>45164</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>46183</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24083,7 +24083,7 @@
         <v>45957</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24156,7 +24156,7 @@
         <v>45615</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24229,7 +24229,7 @@
         <v>45244</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24302,7 +24302,7 @@
         <v>46185</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>46185</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>45749</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>45960</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24609,7 +24609,7 @@
         <v>45960</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24687,7 +24687,7 @@
         <v>45005</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>45098</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24833,7 +24833,7 @@
         <v>45590</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24906,7 +24906,7 @@
         <v>46191</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>45604</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>45604</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>45604</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>46027</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>45968</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
         <v>45190</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>45708</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25505,7 +25505,7 @@
         <v>46195</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25578,7 +25578,7 @@
         <v>45692</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25651,7 +25651,7 @@
         <v>45204</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>45229</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25797,7 +25797,7 @@
         <v>45091</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>45085</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25948,7 +25948,7 @@
         <v>45973</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26021,7 +26021,7 @@
         <v>44994</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26094,7 +26094,7 @@
         <v>46199</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>44610</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26240,7 +26240,7 @@
         <v>44942</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>46203</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26391,7 +26391,7 @@
         <v>46203</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26469,7 +26469,7 @@
         <v>46203</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>46203</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26625,7 +26625,7 @@
         <v>45386</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26703,7 +26703,7 @@
         <v>46203</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>46203</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>46203</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>46203</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27015,7 +27015,7 @@
         <v>46203</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27093,7 +27093,7 @@
         <v>46203</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>46203</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>46203</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>45981</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27405,7 +27405,7 @@
         <v>45981</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27483,7 +27483,7 @@
         <v>46203</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>44789</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>46203</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>46203</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>46203</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27868,7 +27868,7 @@
         <v>46203</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>45981</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28024,7 +28024,7 @@
         <v>45085</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>46205</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28175,7 +28175,7 @@
         <v>45427</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>46205</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>46205</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28404,7 +28404,7 @@
         <v>46205</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>46205</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>45338</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>45338</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>46205</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>45985</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>45716</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>45985</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29018,7 +29018,7 @@
         <v>45019</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29091,7 +29091,7 @@
         <v>45985</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29164,7 +29164,7 @@
         <v>45988</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29237,7 +29237,7 @@
         <v>46206</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29310,7 +29310,7 @@
         <v>46206</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29383,7 +29383,7 @@
         <v>45941</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29461,7 +29461,7 @@
         <v>46206</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29534,7 +29534,7 @@
         <v>46206</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>45941</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         <v>45642</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>45714</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         <v>45575</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29904,7 +29904,7 @@
         <v>45597</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29982,7 +29982,7 @@
         <v>45057</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>45154</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>46209</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>45722</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>45434</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30347,7 +30347,7 @@
         <v>46210</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>45989</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30493,7 +30493,7 @@
         <v>45229</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30566,7 +30566,7 @@
         <v>44734</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30639,7 +30639,7 @@
         <v>44734</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30712,7 +30712,7 @@
         <v>45165</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>45245</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>45973</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30931,7 +30931,7 @@
         <v>45989</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31004,7 +31004,7 @@
         <v>45960</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>45960</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>45140</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>45995</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31311,7 +31311,7 @@
         <v>45995</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>45279</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>45639</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>44790</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>45995</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>45999</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>45428</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31827,7 +31827,7 @@
         <v>45384</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31900,7 +31900,7 @@
         <v>46218</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31973,7 +31973,7 @@
         <v>46218</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>45391</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32119,7 +32119,7 @@
         <v>45600</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>45273</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32265,7 +32265,7 @@
         <v>45601</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>45516</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>46000</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>44526</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32562,7 +32562,7 @@
         <v>46220</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32635,7 +32635,7 @@
         <v>46220</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>46002</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32786,7 +32786,7 @@
         <v>46000</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32859,7 +32859,7 @@
         <v>46002</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>46226</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>46007</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>46237</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>46237</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33234,7 +33234,7 @@
         <v>46237</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>46013</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>46237</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>46237</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>45502</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>46013</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33687,7 +33687,7 @@
         <v>46280</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33760,7 +33760,7 @@
         <v>45742</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33833,7 +33833,7 @@
         <v>45476</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>45786</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33979,7 +33979,7 @@
         <v>45552</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34052,7 +34052,7 @@
         <v>45604</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34125,7 +34125,7 @@
         <v>46029</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34198,7 +34198,7 @@
         <v>46029</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>46033</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>46240</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34417,7 +34417,7 @@
         <v>46242</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34490,7 +34490,7 @@
         <v>46242</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34563,7 +34563,7 @@
         <v>46242</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34636,7 +34636,7 @@
         <v>45972</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34709,7 +34709,7 @@
         <v>46241</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>46241</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34855,7 +34855,7 @@
         <v>46241</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>46040</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>46287</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35074,7 +35074,7 @@
         <v>46048</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35147,7 +35147,7 @@
         <v>45154</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35220,7 +35220,7 @@
         <v>46287</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35293,7 +35293,7 @@
         <v>46050</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35371,7 +35371,7 @@
         <v>45720</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>46139</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35517,7 +35517,7 @@
         <v>46050</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>45801</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>46052</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>45804</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>46052</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>46052</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35975,7 +35975,7 @@
         <v>45804</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>46052</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36126,7 +36126,7 @@
         <v>46052</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36204,7 +36204,7 @@
         <v>45801</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36277,7 +36277,7 @@
         <v>45764</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36355,7 +36355,7 @@
         <v>46058</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>45688</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36506,7 +36506,7 @@
         <v>45807</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36579,7 +36579,7 @@
         <v>46058</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36652,7 +36652,7 @@
         <v>46293</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>46293</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36798,7 +36798,7 @@
         <v>46293</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45777</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>46294</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37022,7 +37022,7 @@
         <v>46293</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>46293</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>45818</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>46293</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37314,7 +37314,7 @@
         <v>46071</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>46247</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37465,7 +37465,7 @@
         <v>46071</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37538,7 +37538,7 @@
         <v>46293</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37611,7 +37611,7 @@
         <v>45819</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37689,7 +37689,7 @@
         <v>46071</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>45819</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37835,7 +37835,7 @@
         <v>46293</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37908,7 +37908,7 @@
         <v>46293</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37981,7 +37981,7 @@
         <v>46296</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38054,7 +38054,7 @@
         <v>46253</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>46293</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>46293</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38273,7 +38273,7 @@
         <v>46253</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38346,7 +38346,7 @@
         <v>45644</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38419,7 +38419,7 @@
         <v>46253</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38492,7 +38492,7 @@
         <v>45826</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>45826</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38638,7 +38638,7 @@
         <v>45826</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38711,7 +38711,7 @@
         <v>46293</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38784,7 +38784,7 @@
         <v>46293</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         <v>46293</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38930,7 +38930,7 @@
         <v>46295</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>46253</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39076,7 +39076,7 @@
         <v>46293</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39149,7 +39149,7 @@
         <v>46300</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39222,7 +39222,7 @@
         <v>46086</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>46153</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39368,7 +39368,7 @@
         <v>46093</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39446,7 +39446,7 @@
         <v>46093</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>46093</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39602,7 +39602,7 @@
         <v>46093</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39680,7 +39680,7 @@
         <v>45295</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39758,7 +39758,7 @@
         <v>46093</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39836,7 +39836,7 @@
         <v>46093</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>46093</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39992,7 +39992,7 @@
         <v>45544</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40065,7 +40065,7 @@
         <v>45459</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>45428</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>45230</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>46191</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>45428</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40435,7 +40435,7 @@
         <v>45428</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
         <v>45428</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45114</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40654,7 +40654,7 @@
         <v>46300</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40727,7 +40727,7 @@
         <v>45544</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40800,7 +40800,7 @@
         <v>46106</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40878,7 +40878,7 @@
         <v>46301</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>46106</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41029,7 +41029,7 @@
         <v>46185</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41102,7 +41102,7 @@
         <v>46301</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41175,7 +41175,7 @@
         <v>45336</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>45842</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41321,7 +41321,7 @@
         <v>45792</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>45865</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41467,7 +41467,7 @@
         <v>45428</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41540,7 +41540,7 @@
         <v>46114</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>46114</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41696,7 +41696,7 @@
         <v>45800</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>46114</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41847,7 +41847,7 @@
         <v>46114</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>46114</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42003,7 +42003,7 @@
         <v>46262</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>45597</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42159,7 +42159,7 @@
         <v>46260</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>46122</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>46260</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42378,7 +42378,7 @@
         <v>46260</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>46149</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>46261</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42597,7 +42597,7 @@
         <v>46162</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42670,7 +42670,7 @@
         <v>46260</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42743,7 +42743,7 @@
         <v>45089</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42816,7 +42816,7 @@
         <v>46041</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>46132</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42962,7 +42962,7 @@
         <v>46308</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43035,7 +43035,7 @@
         <v>46132</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43108,7 +43108,7 @@
         <v>46308</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43181,7 +43181,7 @@
         <v>44592</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>45685</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43327,7 +43327,7 @@
         <v>46010</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43405,7 +43405,7 @@
         <v>45674</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43483,7 +43483,7 @@
         <v>45049</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>45219</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>46307</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43702,7 +43702,7 @@
         <v>45973</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43775,7 +43775,7 @@
         <v>44599</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43848,7 +43848,7 @@
         <v>45642</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43926,7 +43926,7 @@
         <v>45476</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43999,7 +43999,7 @@
         <v>45804</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44072,7 +44072,7 @@
         <v>45877</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>46309</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>46309</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44291,7 +44291,7 @@
         <v>46310</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44364,7 +44364,7 @@
         <v>45288</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44442,7 +44442,7 @@
         <v>45734</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44515,7 +44515,7 @@
         <v>45824</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44588,7 +44588,7 @@
         <v>45897</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>45923</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>45842</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45749</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>45098</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44953,7 +44953,7 @@
         <v>46295</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45026,7 +45026,7 @@
         <v>45666</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45099,7 +45099,7 @@
         <v>46266</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45172,7 +45172,7 @@
         <v>45604</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45250,7 +45250,7 @@
         <v>45604</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45328,7 +45328,7 @@
         <v>45552</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45401,7 +45401,7 @@
         <v>45873</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45474,7 +45474,7 @@
         <v>46133</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45547,7 +45547,7 @@
         <v>45747</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45620,7 +45620,7 @@
         <v>45474</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>46238</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45766,7 +45766,7 @@
         <v>45013</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>44942</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45912,7 +45912,7 @@
         <v>46139</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45985,7 +45985,7 @@
         <v>45842</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46058,7 +46058,7 @@
         <v>45692</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46131,7 +46131,7 @@
         <v>45204</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46204,7 +46204,7 @@
         <v>45233</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46277,7 +46277,7 @@
         <v>45211</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46350,7 +46350,7 @@
         <v>45747</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
         <v>45915</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>45146</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46574,7 +46574,7 @@
         <v>45649</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46647,7 +46647,7 @@
         <v>46315</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46720,7 +46720,7 @@
         <v>46315</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46793,7 +46793,7 @@
         <v>44942</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46866,7 +46866,7 @@
         <v>45320</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46939,7 +46939,7 @@
         <v>46315</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47012,7 +47012,7 @@
         <v>46315</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47085,7 +47085,7 @@
         <v>44592</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47158,7 +47158,7 @@
         <v>45688</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>45688</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47314,7 +47314,7 @@
         <v>45408</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>45338</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45338</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47543,7 +47543,7 @@
         <v>45801</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47616,7 +47616,7 @@
         <v>44985</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47689,7 +47689,7 @@
         <v>46318</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47762,7 +47762,7 @@
         <v>45404</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47835,7 +47835,7 @@
         <v>46274</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>46295</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47981,7 +47981,7 @@
         <v>45702</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48054,7 +48054,7 @@
         <v>46317</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48127,7 +48127,7 @@
         <v>45389</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48200,7 +48200,7 @@
         <v>45149</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48273,7 +48273,7 @@
         <v>45223</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48346,7 +48346,7 @@
         <v>44945</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48419,7 +48419,7 @@
         <v>45063</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48492,7 +48492,7 @@
         <v>45770</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48565,7 +48565,7 @@
         <v>45770</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48638,7 +48638,7 @@
         <v>46156</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48716,7 +48716,7 @@
         <v>46156</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>45278</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48867,7 +48867,7 @@
         <v>46156</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48945,7 +48945,7 @@
         <v>46156</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49023,7 +49023,7 @@
         <v>46156</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>45009</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49174,7 +49174,7 @@
         <v>45677</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49247,7 +49247,7 @@
         <v>44923</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>45629</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49398,7 +49398,7 @@
         <v>45273</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49471,7 +49471,7 @@
         <v>45093</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49544,7 +49544,7 @@
         <v>45317</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49622,7 +49622,7 @@
         <v>44984</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49695,7 +49695,7 @@
         <v>44984</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49768,7 +49768,7 @@
         <v>44971</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49841,7 +49841,7 @@
         <v>45075</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49914,7 +49914,7 @@
         <v>44496</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49987,7 +49987,7 @@
         <v>44971</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50060,7 +50060,7 @@
         <v>45354</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50133,7 +50133,7 @@
         <v>45460</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>45041</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50279,7 +50279,7 @@
         <v>45547</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>44523</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50425,7 +50425,7 @@
         <v>45475</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50498,7 +50498,7 @@
         <v>45181</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50571,7 +50571,7 @@
         <v>45357</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>45615</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50717,7 +50717,7 @@
         <v>45118</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50790,7 +50790,7 @@
         <v>45201</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50863,7 +50863,7 @@
         <v>45028</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>45692</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51014,7 +51014,7 @@
         <v>44924</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51087,7 +51087,7 @@
         <v>45637</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51160,7 +51160,7 @@
         <v>45224</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>44757</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51316,7 +51316,7 @@
         <v>45155</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51389,7 +51389,7 @@
         <v>45273</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>45273</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51535,7 +51535,7 @@
         <v>45622</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51608,7 +51608,7 @@
         <v>45233</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51681,7 +51681,7 @@
         <v>45745</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51754,7 +51754,7 @@
         <v>45749</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51832,7 +51832,7 @@
         <v>45028</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>45244</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51978,7 +51978,7 @@
         <v>44881</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52051,7 +52051,7 @@
         <v>44924</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52124,7 +52124,7 @@
         <v>45012</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52197,7 +52197,7 @@
         <v>45716</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52275,7 +52275,7 @@
         <v>44844</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52348,7 +52348,7 @@
         <v>45706</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52421,7 +52421,7 @@
         <v>45085</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>45583</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52567,7 +52567,7 @@
         <v>44882</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52640,7 +52640,7 @@
         <v>44971</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52713,7 +52713,7 @@
         <v>45705</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52786,7 +52786,7 @@
         <v>45082</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52859,7 +52859,7 @@
         <v>45181</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52937,7 +52937,7 @@
         <v>45407</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53010,7 +53010,7 @@
         <v>45385</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53088,7 +53088,7 @@
         <v>44937</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53161,7 +53161,7 @@
         <v>44937</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>44917</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53307,7 +53307,7 @@
         <v>45547</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53380,7 +53380,7 @@
         <v>45547</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53453,7 +53453,7 @@
         <v>44838</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53526,7 +53526,7 @@
         <v>45093</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45596</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53672,7 +53672,7 @@
         <v>45716</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53750,7 +53750,7 @@
         <v>45590</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53823,7 +53823,7 @@
         <v>45369</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53896,7 +53896,7 @@
         <v>44524</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53969,7 +53969,7 @@
         <v>44503</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54042,7 +54042,7 @@
         <v>45348</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54115,7 +54115,7 @@
         <v>45348</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54188,7 +54188,7 @@
         <v>45001</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54261,7 +54261,7 @@
         <v>45082</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54334,7 +54334,7 @@
         <v>44496</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54407,7 +54407,7 @@
         <v>45561</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54480,7 +54480,7 @@
         <v>45568</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54558,7 +54558,7 @@
         <v>45454</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54631,7 +54631,7 @@
         <v>45348</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54704,7 +54704,7 @@
         <v>44998</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54782,7 +54782,7 @@
         <v>45103</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>45181</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54928,7 +54928,7 @@
         <v>45469</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>45428</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55074,7 +55074,7 @@
         <v>45153</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55147,7 +55147,7 @@
         <v>45530</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55220,7 +55220,7 @@
         <v>45720</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55293,7 +55293,7 @@
         <v>45229</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55366,7 +55366,7 @@
         <v>45389</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55439,7 +55439,7 @@
         <v>45162</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55512,7 +55512,7 @@
         <v>45154</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55585,7 +55585,7 @@
         <v>44524</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55663,7 +55663,7 @@
         <v>44524</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55736,7 +55736,7 @@
         <v>45146</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55809,7 +55809,7 @@
         <v>45590</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55882,7 +55882,7 @@
         <v>45118</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55955,7 +55955,7 @@
         <v>45355</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56028,7 +56028,7 @@
         <v>45370</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56101,7 +56101,7 @@
         <v>45610</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56174,7 +56174,7 @@
         <v>44659</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56247,7 +56247,7 @@
         <v>44610</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56320,7 +56320,7 @@
         <v>45642</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56398,7 +56398,7 @@
         <v>45597</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56476,7 +56476,7 @@
         <v>44844</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56549,7 +56549,7 @@
         <v>45372</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56622,7 +56622,7 @@
         <v>45440</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56695,7 +56695,7 @@
         <v>45169</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56768,7 +56768,7 @@
         <v>45218</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56841,7 +56841,7 @@
         <v>45729</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56914,7 +56914,7 @@
         <v>45372</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56987,7 +56987,7 @@
         <v>44593</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57060,7 +57060,7 @@
         <v>45196</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57133,7 +57133,7 @@
         <v>45404</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57206,7 +57206,7 @@
         <v>45547</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57279,7 +57279,7 @@
         <v>45223</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57352,7 +57352,7 @@
         <v>44566</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57425,7 +57425,7 @@
         <v>45664</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57498,7 +57498,7 @@
         <v>45057</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>45211</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57644,7 +57644,7 @@
         <v>45688</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57722,7 +57722,7 @@
         <v>45107</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57795,7 +57795,7 @@
         <v>45195</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57868,7 +57868,7 @@
         <v>45757</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57946,7 +57946,7 @@
         <v>45184</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58019,7 +58019,7 @@
         <v>45085</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58092,7 +58092,7 @@
         <v>45459</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58165,7 +58165,7 @@
         <v>45153</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>45174</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58311,7 +58311,7 @@
         <v>45230</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58389,7 +58389,7 @@
         <v>44757</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58467,7 +58467,7 @@
         <v>45769</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58540,7 +58540,7 @@
         <v>45155</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58613,7 +58613,7 @@
         <v>45243</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58686,7 +58686,7 @@
         <v>44915</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58759,7 +58759,7 @@
         <v>45336</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58832,7 +58832,7 @@
         <v>44858</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58905,7 +58905,7 @@
         <v>45230</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58983,7 +58983,7 @@
         <v>45351</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59056,7 +59056,7 @@
         <v>45264</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59129,7 +59129,7 @@
         <v>44939</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59202,7 +59202,7 @@
         <v>45324</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59275,7 +59275,7 @@
         <v>45279</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59348,7 +59348,7 @@
         <v>44603</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59421,7 +59421,7 @@
         <v>45146</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59494,7 +59494,7 @@
         <v>45146</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59567,7 +59567,7 @@
         <v>45764</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59640,7 +59640,7 @@
         <v>45308</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59713,7 +59713,7 @@
         <v>45547</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59786,7 +59786,7 @@
         <v>45547</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59859,7 +59859,7 @@
         <v>45764</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59937,7 +59937,7 @@
         <v>45736</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60015,7 +60015,7 @@
         <v>45770</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60088,7 +60088,7 @@
         <v>44922</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60161,7 +60161,7 @@
         <v>45338</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60239,7 +60239,7 @@
         <v>44897</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60312,7 +60312,7 @@
         <v>44951</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60385,7 +60385,7 @@
         <v>44946</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60458,7 +60458,7 @@
         <v>45561</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60531,7 +60531,7 @@
         <v>44552</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60604,7 +60604,7 @@
         <v>44726</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60677,7 +60677,7 @@
         <v>44726</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60750,7 +60750,7 @@
         <v>44916</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60823,7 +60823,7 @@
         <v>45161</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60901,7 +60901,7 @@
         <v>45476</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60974,7 +60974,7 @@
         <v>44963</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61047,7 +61047,7 @@
         <v>44916</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61120,7 +61120,7 @@
         <v>45140</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61193,7 +61193,7 @@
         <v>44837</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61266,7 +61266,7 @@
         <v>45161</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61344,7 +61344,7 @@
         <v>44893</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61417,7 +61417,7 @@
         <v>44916</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61490,7 +61490,7 @@
         <v>45411</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61563,7 +61563,7 @@
         <v>45791</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61636,7 +61636,7 @@
         <v>45910</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61709,7 +61709,7 @@
         <v>46030</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61782,7 +61782,7 @@
         <v>46051</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61855,7 +61855,7 @@
         <v>46280</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61933,7 +61933,7 @@
         <v>46275</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>

--- a/Översikt UPPVIDINGE.xlsx
+++ b/Översikt UPPVIDINGE.xlsx
@@ -601,7 +601,7 @@
         <v>44607</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45174</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>44972</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>44972</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45442</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45789</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>46119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>46183</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>44980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>46183</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>44607</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45789</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>46119</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>46149</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>46119</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>45995</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44859</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>46066</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>46183</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>46276</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>45313</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>45366</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44972</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>46066</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>45158</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>44939</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>45195</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>45450</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>46247</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>45840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>45604</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>44979</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>46169</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>45604</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>44833</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>46205</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>46218</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>46051</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>46297</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>46310</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>46316</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>45604</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>45205</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>45103</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>45568</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>45517</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>45404</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>45117</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>44937</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>45320</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>44972</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>44972</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>45789</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>44734</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>44827</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>44690</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>44788</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         <v>44858</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>45939</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>45105</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>46185</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>45897</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>45981</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>44950</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>45517</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>45688</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         <v>45534</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>46162</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>46247</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>46247</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>46247</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>45820</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>45826</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>45825</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         <v>46255</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>45840</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>46100</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>44550</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>45435</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>45623</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>45982</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>44676</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>46154</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>45320</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>44984</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>44858</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>44998</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>44663</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>44757</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>45440</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>44972</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>45810</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>46300</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>44865</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>44887</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>44887</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>44524</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>44613</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44552</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>44574</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>44536</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>44510</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         <v>44812</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>44859</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>44574</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>44859</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>44676</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>44859</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>44859</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>44749</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>44574</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>44602</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>44580</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>44602</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>44859</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>44795</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>44757</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>44887</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>44588</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>44845</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>44552</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>44503</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>44510</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>44803</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>44887</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>44609</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>44610</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>44795</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
         <v>44795</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14028,7 +14028,7 @@
         <v>44582</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>44601</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>44858</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>44711</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>44522</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>44837</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>44859</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>44607</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>44607</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>44887</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>44887</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>44676</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>44574</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>44603</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>44602</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>44524</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>44721</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>44683</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>44686</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>44729</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>44705</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>44533</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>44602</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>45349</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>44902</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>45112</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>44592</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45887</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>44757</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>45229</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>45389</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>45091</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>45190</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>45338</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>45338</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>45341</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>44638</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>45279</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>45697</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>45041</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>45041</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17051,7 +17051,7 @@
         <v>45894</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>45230</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>44552</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17275,7 +17275,7 @@
         <v>45338</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17353,7 +17353,7 @@
         <v>45338</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17431,7 +17431,7 @@
         <v>45338</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>44887</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>45208</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17655,7 +17655,7 @@
         <v>45391</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>45398</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>45901</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>44833</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>45840</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>45428</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         <v>45567</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         <v>45901</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>45607</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18317,7 +18317,7 @@
         <v>45595</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>44497</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>45546</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>45226</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18609,7 +18609,7 @@
         <v>45910</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>45910</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>45910</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>45838</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>45455</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>45910</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
         <v>45232</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>45568</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>45275</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>45245</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>44711</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>44994</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19495,7 +19495,7 @@
         <v>46163</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45174</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>46163</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>44908</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19802,7 +19802,7 @@
         <v>44697</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19880,7 +19880,7 @@
         <v>45069</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         <v>45923</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>45923</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>45668</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20172,7 +20172,7 @@
         <v>46167</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         <v>45260</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>44865</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>46169</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20469,7 +20469,7 @@
         <v>46106</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>45156</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>45369</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>45934</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20766,7 +20766,7 @@
         <v>45934</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>46174</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>45933</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>46174</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>45434</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>45375</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>45934</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21287,7 +21287,7 @@
         <v>45427</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>45225</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>45350</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21506,7 +21506,7 @@
         <v>46174</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>46174</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>46174</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>45940</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>46174</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>44998</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>46176</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22057,7 +22057,7 @@
         <v>45428</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>46177</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>46177</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>46176</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22359,7 +22359,7 @@
         <v>46132</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>46177</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>44757</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>44757</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22666,7 +22666,7 @@
         <v>46177</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>46177</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>46177</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>46177</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>46177</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23056,7 +23056,7 @@
         <v>45471</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>45454</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>45118</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>45389</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>46058</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>45140</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>46181</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>46181</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>44593</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>46181</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23791,7 +23791,7 @@
         <v>45105</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23864,7 +23864,7 @@
         <v>45440</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>45164</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>46183</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24083,7 +24083,7 @@
         <v>45957</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24156,7 +24156,7 @@
         <v>45615</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24229,7 +24229,7 @@
         <v>45244</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24302,7 +24302,7 @@
         <v>46185</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>46185</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>45749</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>45960</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24609,7 +24609,7 @@
         <v>45960</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24687,7 +24687,7 @@
         <v>45005</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>45098</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24833,7 +24833,7 @@
         <v>45590</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24906,7 +24906,7 @@
         <v>46191</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>45604</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>45604</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>45604</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>46027</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>45968</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
         <v>45190</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>45708</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25505,7 +25505,7 @@
         <v>46195</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25578,7 +25578,7 @@
         <v>45692</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25651,7 +25651,7 @@
         <v>45204</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>45229</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25797,7 +25797,7 @@
         <v>45091</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>45085</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25948,7 +25948,7 @@
         <v>45973</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26021,7 +26021,7 @@
         <v>44994</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26094,7 +26094,7 @@
         <v>46199</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>44610</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26240,7 +26240,7 @@
         <v>44942</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>46203</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26391,7 +26391,7 @@
         <v>46203</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26469,7 +26469,7 @@
         <v>46203</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>46203</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26625,7 +26625,7 @@
         <v>45386</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26703,7 +26703,7 @@
         <v>46203</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>46203</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>46203</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>46203</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27015,7 +27015,7 @@
         <v>46203</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27093,7 +27093,7 @@
         <v>46203</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>46203</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>46203</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>45981</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27405,7 +27405,7 @@
         <v>45981</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27483,7 +27483,7 @@
         <v>46203</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>44789</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>46203</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>46203</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>46203</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27868,7 +27868,7 @@
         <v>46203</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>45981</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28024,7 +28024,7 @@
         <v>45085</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>46205</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28175,7 +28175,7 @@
         <v>45427</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>46205</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>46205</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28404,7 +28404,7 @@
         <v>46205</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>46205</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>45338</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>45338</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>46205</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>45985</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>45716</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>45985</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29018,7 +29018,7 @@
         <v>45019</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29091,7 +29091,7 @@
         <v>45985</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29164,7 +29164,7 @@
         <v>45988</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29237,7 +29237,7 @@
         <v>46206</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29310,7 +29310,7 @@
         <v>46206</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29383,7 +29383,7 @@
         <v>45941</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29461,7 +29461,7 @@
         <v>46206</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29534,7 +29534,7 @@
         <v>46206</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>45941</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         <v>45642</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>45714</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         <v>45575</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29904,7 +29904,7 @@
         <v>45597</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29982,7 +29982,7 @@
         <v>45057</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>45154</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>46209</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>45722</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>45434</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30347,7 +30347,7 @@
         <v>46210</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>45989</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30493,7 +30493,7 @@
         <v>45229</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30566,7 +30566,7 @@
         <v>44734</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30639,7 +30639,7 @@
         <v>44734</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30712,7 +30712,7 @@
         <v>45165</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>45245</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>45973</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30931,7 +30931,7 @@
         <v>45989</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31004,7 +31004,7 @@
         <v>45960</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>45960</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>45140</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>45995</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31311,7 +31311,7 @@
         <v>45995</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>45279</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>45639</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>44790</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>45995</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>45999</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>45428</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31827,7 +31827,7 @@
         <v>45384</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31900,7 +31900,7 @@
         <v>46218</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31973,7 +31973,7 @@
         <v>46218</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>45391</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32119,7 +32119,7 @@
         <v>45600</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>45273</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32265,7 +32265,7 @@
         <v>45601</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>45516</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>46000</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>44526</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32562,7 +32562,7 @@
         <v>46220</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32635,7 +32635,7 @@
         <v>46220</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>46002</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32786,7 +32786,7 @@
         <v>46000</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32859,7 +32859,7 @@
         <v>46002</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>46226</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>46007</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>46237</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>46237</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33234,7 +33234,7 @@
         <v>46237</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>46013</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>46237</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>46237</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>45502</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>46013</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33687,7 +33687,7 @@
         <v>46280</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33760,7 +33760,7 @@
         <v>45742</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33833,7 +33833,7 @@
         <v>45476</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>45786</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33979,7 +33979,7 @@
         <v>45552</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34052,7 +34052,7 @@
         <v>45604</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34125,7 +34125,7 @@
         <v>46029</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34198,7 +34198,7 @@
         <v>46029</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>46033</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>46240</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34417,7 +34417,7 @@
         <v>46242</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34490,7 +34490,7 @@
         <v>46242</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34563,7 +34563,7 @@
         <v>46242</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34636,7 +34636,7 @@
         <v>45972</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34709,7 +34709,7 @@
         <v>46241</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>46241</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34855,7 +34855,7 @@
         <v>46241</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>46040</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>46287</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35074,7 +35074,7 @@
         <v>46048</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35147,7 +35147,7 @@
         <v>45154</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35220,7 +35220,7 @@
         <v>46287</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35293,7 +35293,7 @@
         <v>46050</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35371,7 +35371,7 @@
         <v>45720</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>46139</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35517,7 +35517,7 @@
         <v>46050</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>45801</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>46052</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>45804</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>46052</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>46052</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35975,7 +35975,7 @@
         <v>45804</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>46052</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36126,7 +36126,7 @@
         <v>46052</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36204,7 +36204,7 @@
         <v>45801</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36277,7 +36277,7 @@
         <v>45764</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36355,7 +36355,7 @@
         <v>46058</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>45688</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36506,7 +36506,7 @@
         <v>45807</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36579,7 +36579,7 @@
         <v>46058</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36652,7 +36652,7 @@
         <v>46293</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>46293</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36798,7 +36798,7 @@
         <v>46293</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45777</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>46294</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37022,7 +37022,7 @@
         <v>46293</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>46293</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>45818</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>46293</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37314,7 +37314,7 @@
         <v>46071</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>46247</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37465,7 +37465,7 @@
         <v>46071</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37538,7 +37538,7 @@
         <v>46293</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37611,7 +37611,7 @@
         <v>45819</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37689,7 +37689,7 @@
         <v>46071</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>45819</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37835,7 +37835,7 @@
         <v>46293</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37908,7 +37908,7 @@
         <v>46293</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37981,7 +37981,7 @@
         <v>46296</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38054,7 +38054,7 @@
         <v>46253</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>46293</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>46293</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38273,7 +38273,7 @@
         <v>46253</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38346,7 +38346,7 @@
         <v>45644</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38419,7 +38419,7 @@
         <v>46253</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38492,7 +38492,7 @@
         <v>45826</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>45826</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38638,7 +38638,7 @@
         <v>45826</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38711,7 +38711,7 @@
         <v>46293</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38784,7 +38784,7 @@
         <v>46293</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         <v>46293</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38930,7 +38930,7 @@
         <v>46295</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>46253</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39076,7 +39076,7 @@
         <v>46293</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39149,7 +39149,7 @@
         <v>46300</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39222,7 +39222,7 @@
         <v>46086</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>46153</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39368,7 +39368,7 @@
         <v>46093</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39446,7 +39446,7 @@
         <v>46093</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>46093</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39602,7 +39602,7 @@
         <v>46093</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39680,7 +39680,7 @@
         <v>45295</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39758,7 +39758,7 @@
         <v>46093</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39836,7 +39836,7 @@
         <v>46093</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>46093</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39992,7 +39992,7 @@
         <v>45544</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40065,7 +40065,7 @@
         <v>45459</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>45428</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>45230</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>46191</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>45428</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40435,7 +40435,7 @@
         <v>45428</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
         <v>45428</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45114</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40654,7 +40654,7 @@
         <v>46300</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40727,7 +40727,7 @@
         <v>45544</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40800,7 +40800,7 @@
         <v>46106</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40878,7 +40878,7 @@
         <v>46301</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>46106</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41029,7 +41029,7 @@
         <v>46185</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41102,7 +41102,7 @@
         <v>46301</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41175,7 +41175,7 @@
         <v>45336</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>45842</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41321,7 +41321,7 @@
         <v>45792</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>45865</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41467,7 +41467,7 @@
         <v>45428</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41540,7 +41540,7 @@
         <v>46114</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>46114</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41696,7 +41696,7 @@
         <v>45800</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>46114</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41847,7 +41847,7 @@
         <v>46114</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>46114</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42003,7 +42003,7 @@
         <v>46262</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>45597</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42159,7 +42159,7 @@
         <v>46260</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>46122</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>46260</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42378,7 +42378,7 @@
         <v>46260</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>46149</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>46261</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42597,7 +42597,7 @@
         <v>46162</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42670,7 +42670,7 @@
         <v>46260</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42743,7 +42743,7 @@
         <v>45089</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42816,7 +42816,7 @@
         <v>46041</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>46132</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42962,7 +42962,7 @@
         <v>46308</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43035,7 +43035,7 @@
         <v>46132</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43108,7 +43108,7 @@
         <v>46308</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43181,7 +43181,7 @@
         <v>44592</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>45685</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43327,7 +43327,7 @@
         <v>46010</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43405,7 +43405,7 @@
         <v>45674</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43483,7 +43483,7 @@
         <v>45049</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>45219</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>46307</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43702,7 +43702,7 @@
         <v>45973</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43775,7 +43775,7 @@
         <v>44599</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43848,7 +43848,7 @@
         <v>45642</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43926,7 +43926,7 @@
         <v>45476</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43999,7 +43999,7 @@
         <v>45804</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44072,7 +44072,7 @@
         <v>45877</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>46309</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>46309</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44291,7 +44291,7 @@
         <v>46310</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44364,7 +44364,7 @@
         <v>45288</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44442,7 +44442,7 @@
         <v>45734</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44515,7 +44515,7 @@
         <v>45824</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44588,7 +44588,7 @@
         <v>45897</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>45923</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>45842</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45749</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>45098</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44953,7 +44953,7 @@
         <v>46295</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45026,7 +45026,7 @@
         <v>45666</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45099,7 +45099,7 @@
         <v>46266</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45172,7 +45172,7 @@
         <v>45604</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45250,7 +45250,7 @@
         <v>45604</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45328,7 +45328,7 @@
         <v>45552</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45401,7 +45401,7 @@
         <v>45873</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45474,7 +45474,7 @@
         <v>46133</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45547,7 +45547,7 @@
         <v>45747</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45620,7 +45620,7 @@
         <v>45474</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>46238</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45766,7 +45766,7 @@
         <v>45013</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>44942</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45912,7 +45912,7 @@
         <v>46139</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45985,7 +45985,7 @@
         <v>45842</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46058,7 +46058,7 @@
         <v>45692</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46131,7 +46131,7 @@
         <v>45204</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46204,7 +46204,7 @@
         <v>45233</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46277,7 +46277,7 @@
         <v>45211</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46350,7 +46350,7 @@
         <v>45747</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
         <v>45915</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>45146</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46574,7 +46574,7 @@
         <v>45649</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46647,7 +46647,7 @@
         <v>46315</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46720,7 +46720,7 @@
         <v>46315</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46793,7 +46793,7 @@
         <v>44942</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46866,7 +46866,7 @@
         <v>45320</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46939,7 +46939,7 @@
         <v>46315</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47012,7 +47012,7 @@
         <v>46315</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47085,7 +47085,7 @@
         <v>44592</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47158,7 +47158,7 @@
         <v>45688</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>45688</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47314,7 +47314,7 @@
         <v>45408</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>45338</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45338</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47543,7 +47543,7 @@
         <v>45801</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47616,7 +47616,7 @@
         <v>44985</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47689,7 +47689,7 @@
         <v>46318</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47762,7 +47762,7 @@
         <v>45404</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47835,7 +47835,7 @@
         <v>46274</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>46295</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47981,7 +47981,7 @@
         <v>45702</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48054,7 +48054,7 @@
         <v>46317</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48127,7 +48127,7 @@
         <v>45389</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48200,7 +48200,7 @@
         <v>45149</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48273,7 +48273,7 @@
         <v>45223</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48346,7 +48346,7 @@
         <v>44945</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48419,7 +48419,7 @@
         <v>45063</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48492,7 +48492,7 @@
         <v>45770</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48565,7 +48565,7 @@
         <v>45770</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48638,7 +48638,7 @@
         <v>46156</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48716,7 +48716,7 @@
         <v>46156</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>45278</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48867,7 +48867,7 @@
         <v>46156</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48945,7 +48945,7 @@
         <v>46156</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49023,7 +49023,7 @@
         <v>46156</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>45009</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49174,7 +49174,7 @@
         <v>45677</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49247,7 +49247,7 @@
         <v>44923</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>45629</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49398,7 +49398,7 @@
         <v>45273</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49471,7 +49471,7 @@
         <v>45093</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49544,7 +49544,7 @@
         <v>45317</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49622,7 +49622,7 @@
         <v>44984</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49695,7 +49695,7 @@
         <v>44984</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49768,7 +49768,7 @@
         <v>44971</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49841,7 +49841,7 @@
         <v>45075</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49914,7 +49914,7 @@
         <v>44496</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49987,7 +49987,7 @@
         <v>44971</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50060,7 +50060,7 @@
         <v>45354</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50133,7 +50133,7 @@
         <v>45460</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>45041</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50279,7 +50279,7 @@
         <v>45547</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>44523</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50425,7 +50425,7 @@
         <v>45475</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50498,7 +50498,7 @@
         <v>45181</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50571,7 +50571,7 @@
         <v>45357</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>45615</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50717,7 +50717,7 @@
         <v>45118</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50790,7 +50790,7 @@
         <v>45201</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50863,7 +50863,7 @@
         <v>45028</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>45692</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51014,7 +51014,7 @@
         <v>44924</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51087,7 +51087,7 @@
         <v>45637</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51160,7 +51160,7 @@
         <v>45224</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>44757</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51316,7 +51316,7 @@
         <v>45155</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51389,7 +51389,7 @@
         <v>45273</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>45273</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51535,7 +51535,7 @@
         <v>45622</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51608,7 +51608,7 @@
         <v>45233</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51681,7 +51681,7 @@
         <v>45745</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51754,7 +51754,7 @@
         <v>45749</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51832,7 +51832,7 @@
         <v>45028</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>45244</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51978,7 +51978,7 @@
         <v>44881</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52051,7 +52051,7 @@
         <v>44924</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52124,7 +52124,7 @@
         <v>45012</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52197,7 +52197,7 @@
         <v>45716</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52275,7 +52275,7 @@
         <v>44844</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52348,7 +52348,7 @@
         <v>45706</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52421,7 +52421,7 @@
         <v>45085</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>45583</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52567,7 +52567,7 @@
         <v>44882</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52640,7 +52640,7 @@
         <v>44971</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52713,7 +52713,7 @@
         <v>45705</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52786,7 +52786,7 @@
         <v>45082</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52859,7 +52859,7 @@
         <v>45181</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52937,7 +52937,7 @@
         <v>45407</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53010,7 +53010,7 @@
         <v>45385</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53088,7 +53088,7 @@
         <v>44937</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53161,7 +53161,7 @@
         <v>44937</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>44917</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53307,7 +53307,7 @@
         <v>45547</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53380,7 +53380,7 @@
         <v>45547</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53453,7 +53453,7 @@
         <v>44838</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53526,7 +53526,7 @@
         <v>45093</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45596</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53672,7 +53672,7 @@
         <v>45716</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53750,7 +53750,7 @@
         <v>45590</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53823,7 +53823,7 @@
         <v>45369</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53896,7 +53896,7 @@
         <v>44524</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53969,7 +53969,7 @@
         <v>44503</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54042,7 +54042,7 @@
         <v>45348</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54115,7 +54115,7 @@
         <v>45348</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54188,7 +54188,7 @@
         <v>45001</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54261,7 +54261,7 @@
         <v>45082</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54334,7 +54334,7 @@
         <v>44496</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54407,7 +54407,7 @@
         <v>45561</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54480,7 +54480,7 @@
         <v>45568</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54558,7 +54558,7 @@
         <v>45454</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54631,7 +54631,7 @@
         <v>45348</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54704,7 +54704,7 @@
         <v>44998</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54782,7 +54782,7 @@
         <v>45103</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>45181</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54928,7 +54928,7 @@
         <v>45469</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>45428</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55074,7 +55074,7 @@
         <v>45153</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55147,7 +55147,7 @@
         <v>45530</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55220,7 +55220,7 @@
         <v>45720</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55293,7 +55293,7 @@
         <v>45229</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55366,7 +55366,7 @@
         <v>45389</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55439,7 +55439,7 @@
         <v>45162</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55512,7 +55512,7 @@
         <v>45154</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55585,7 +55585,7 @@
         <v>44524</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55663,7 +55663,7 @@
         <v>44524</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55736,7 +55736,7 @@
         <v>45146</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55809,7 +55809,7 @@
         <v>45590</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55882,7 +55882,7 @@
         <v>45118</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55955,7 +55955,7 @@
         <v>45355</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56028,7 +56028,7 @@
         <v>45370</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56101,7 +56101,7 @@
         <v>45610</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56174,7 +56174,7 @@
         <v>44659</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56247,7 +56247,7 @@
         <v>44610</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56320,7 +56320,7 @@
         <v>45642</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56398,7 +56398,7 @@
         <v>45597</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56476,7 +56476,7 @@
         <v>44844</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56549,7 +56549,7 @@
         <v>45372</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56622,7 +56622,7 @@
         <v>45440</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56695,7 +56695,7 @@
         <v>45169</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56768,7 +56768,7 @@
         <v>45218</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56841,7 +56841,7 @@
         <v>45729</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56914,7 +56914,7 @@
         <v>45372</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56987,7 +56987,7 @@
         <v>44593</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57060,7 +57060,7 @@
         <v>45196</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57133,7 +57133,7 @@
         <v>45404</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57206,7 +57206,7 @@
         <v>45547</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57279,7 +57279,7 @@
         <v>45223</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57352,7 +57352,7 @@
         <v>44566</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57425,7 +57425,7 @@
         <v>45664</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57498,7 +57498,7 @@
         <v>45057</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>45211</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57644,7 +57644,7 @@
         <v>45688</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57722,7 +57722,7 @@
         <v>45107</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57795,7 +57795,7 @@
         <v>45195</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57868,7 +57868,7 @@
         <v>45757</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57946,7 +57946,7 @@
         <v>45184</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58019,7 +58019,7 @@
         <v>45085</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58092,7 +58092,7 @@
         <v>45459</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58165,7 +58165,7 @@
         <v>45153</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>45174</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58311,7 +58311,7 @@
         <v>45230</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58389,7 +58389,7 @@
         <v>44757</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58467,7 +58467,7 @@
         <v>45769</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58540,7 +58540,7 @@
         <v>45155</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58613,7 +58613,7 @@
         <v>45243</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58686,7 +58686,7 @@
         <v>44915</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58759,7 +58759,7 @@
         <v>45336</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58832,7 +58832,7 @@
         <v>44858</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58905,7 +58905,7 @@
         <v>45230</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58983,7 +58983,7 @@
         <v>45351</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59056,7 +59056,7 @@
         <v>45264</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59129,7 +59129,7 @@
         <v>44939</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59202,7 +59202,7 @@
         <v>45324</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59275,7 +59275,7 @@
         <v>45279</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59348,7 +59348,7 @@
         <v>44603</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59421,7 +59421,7 @@
         <v>45146</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59494,7 +59494,7 @@
         <v>45146</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59567,7 +59567,7 @@
         <v>45764</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59640,7 +59640,7 @@
         <v>45308</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59713,7 +59713,7 @@
         <v>45547</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59786,7 +59786,7 @@
         <v>45547</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59859,7 +59859,7 @@
         <v>45764</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59937,7 +59937,7 @@
         <v>45736</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60015,7 +60015,7 @@
         <v>45770</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60088,7 +60088,7 @@
         <v>44922</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60161,7 +60161,7 @@
         <v>45338</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60239,7 +60239,7 @@
         <v>44897</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60312,7 +60312,7 @@
         <v>44951</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60385,7 +60385,7 @@
         <v>44946</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60458,7 +60458,7 @@
         <v>45561</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60531,7 +60531,7 @@
         <v>44552</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60604,7 +60604,7 @@
         <v>44726</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60677,7 +60677,7 @@
         <v>44726</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60750,7 +60750,7 @@
         <v>44916</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60823,7 +60823,7 @@
         <v>45161</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60901,7 +60901,7 @@
         <v>45476</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60974,7 +60974,7 @@
         <v>44963</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61047,7 +61047,7 @@
         <v>44916</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61120,7 +61120,7 @@
         <v>45140</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61193,7 +61193,7 @@
         <v>44837</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61266,7 +61266,7 @@
         <v>45161</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61344,7 +61344,7 @@
         <v>44893</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61417,7 +61417,7 @@
         <v>44916</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61490,7 +61490,7 @@
         <v>45411</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61563,7 +61563,7 @@
         <v>45791</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61636,7 +61636,7 @@
         <v>45910</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61709,7 +61709,7 @@
         <v>46030</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61782,7 +61782,7 @@
         <v>46051</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61855,7 +61855,7 @@
         <v>46280</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61933,7 +61933,7 @@
         <v>46275</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
